--- a/outputs/01a0775c-925e-7713-9822-42450cb2f4b6/Hope-Sojourns-Trip-Bulk-Import-Template.xlsx
+++ b/outputs/01a0775c-925e-7713-9822-42450cb2f4b6/Hope-Sojourns-Trip-Bulk-Import-Template.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Rd4509487ce164cf6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="2" r:id="Rbe8b7342caa84492"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ministries" sheetId="3" r:id="Rf1743e34b6284365"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team" sheetId="4" r:id="R66d0887aea914af3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partners" sheetId="5" r:id="R32bc8231db9b4fde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Content" sheetId="6" r:id="R50650eecdd944302"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accounts" sheetId="7" r:id="R689c2a4272f648e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="8" r:id="R1c6baac7152b4969"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Allocations" sheetId="9" r:id="R7c39436e0c9949b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charges" sheetId="10" r:id="Ra145f308538741b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support" sheetId="11" r:id="Rf1b7f2afb49f4ea7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments" sheetId="12" r:id="Ra931fa22eb38474e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invites" sheetId="13" r:id="R897172b2b705412e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R59db7b4751bb48b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="2" r:id="R53a25dc4a7b74481"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ministries" sheetId="3" r:id="R9c24e96e6b604bdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team" sheetId="4" r:id="R3369965932114a18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partners" sheetId="5" r:id="Rffc2827c1f4340e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Content" sheetId="6" r:id="R66a71fa3cde74b15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accounts" sheetId="7" r:id="R6e9750fa9815400e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="8" r:id="Rf6dd2bc808fc432f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Allocations" sheetId="9" r:id="R5b701354c3794b3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charges" sheetId="10" r:id="R7e169865e0cb4888"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support" sheetId="11" r:id="Re54d9ce3368f44ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments" sheetId="12" r:id="R9c5ebf93349e47bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invites" sheetId="13" r:id="Rfea516d75d904692"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -25,11 +25,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="5">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="0"/>
-    <x:numFmt numFmtId="202" formatCode="0.00"/>
-    <x:numFmt numFmtId="203" formatCode="$#,##0.00"/>
+    <x:numFmt numFmtId="202" formatCode="0.000"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
+    <x:numFmt numFmtId="204" formatCode="$#,##0.00"/>
   </x:numFmts>
   <x:fonts count="9">
     <x:font>
@@ -136,7 +137,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="43">
+  <x:cellXfs count="44">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -222,6 +223,9 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="203" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -438,30 +442,32 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="HsBudgetImport" displayName="HsBudgetImport" ref="A4:U104" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:U104"/>
-  <x:tableColumns count="21">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="HsBudgetImport" displayName="HsBudgetImport" ref="A4:W104" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:W104"/>
+  <x:tableColumns count="23">
     <x:tableColumn id="1" name="Import Ref"/>
     <x:tableColumn id="2" name="Category Name"/>
     <x:tableColumn id="3" name="Description"/>
     <x:tableColumn id="4" name="Expense Scope"/>
     <x:tableColumn id="5" name="Account Ref"/>
-    <x:tableColumn id="6" name="Quantity"/>
-    <x:tableColumn id="7" name="Estimated Unit Cost"/>
-    <x:tableColumn id="8" name="Estimated Total"/>
-    <x:tableColumn id="9" name="Actual Total"/>
-    <x:tableColumn id="10" name="Vendor Name"/>
-    <x:tableColumn id="11" name="Vendor Organization Name"/>
-    <x:tableColumn id="12" name="Settlement Route"/>
-    <x:tableColumn id="13" name="Payment Status"/>
-    <x:tableColumn id="14" name="Payment Method"/>
-    <x:tableColumn id="15" name="External Reference"/>
-    <x:tableColumn id="16" name="Due Date"/>
-    <x:tableColumn id="17" name="Paid Date"/>
-    <x:tableColumn id="18" name="Notes"/>
-    <x:tableColumn id="19" name="Record ID"/>
-    <x:tableColumn id="20" name="Original Updated At"/>
-    <x:tableColumn id="21" name="Original Fingerprint"/>
+    <x:tableColumn id="6" name="Calculation Method"/>
+    <x:tableColumn id="7" name="Percentage Rate"/>
+    <x:tableColumn id="8" name="Quantity"/>
+    <x:tableColumn id="9" name="Estimated Unit Cost"/>
+    <x:tableColumn id="10" name="Estimated Total"/>
+    <x:tableColumn id="11" name="Actual Total"/>
+    <x:tableColumn id="12" name="Vendor Name"/>
+    <x:tableColumn id="13" name="Vendor Organization Name"/>
+    <x:tableColumn id="14" name="Settlement Route"/>
+    <x:tableColumn id="15" name="Payment Status"/>
+    <x:tableColumn id="16" name="Payment Method"/>
+    <x:tableColumn id="17" name="External Reference"/>
+    <x:tableColumn id="18" name="Due Date"/>
+    <x:tableColumn id="19" name="Paid Date"/>
+    <x:tableColumn id="20" name="Notes"/>
+    <x:tableColumn id="21" name="Record ID"/>
+    <x:tableColumn id="22" name="Original Updated At"/>
+    <x:tableColumn id="23" name="Original Fingerprint"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -979,7 +985,7 @@
       <x:c r="C5" s="37"/>
       <x:c r="D5" s="37"/>
       <x:c r="E5" s="37"/>
-      <x:c r="F5" s="42"/>
+      <x:c r="F5" s="43"/>
       <x:c r="G5" s="39"/>
       <x:c r="H5" s="37"/>
       <x:c r="I5" s="37"/>
@@ -993,7 +999,7 @@
       <x:c r="C6" s="37"/>
       <x:c r="D6" s="37"/>
       <x:c r="E6" s="37"/>
-      <x:c r="F6" s="42"/>
+      <x:c r="F6" s="43"/>
       <x:c r="G6" s="39"/>
       <x:c r="H6" s="37"/>
       <x:c r="I6" s="37"/>
@@ -1007,7 +1013,7 @@
       <x:c r="C7" s="37"/>
       <x:c r="D7" s="37"/>
       <x:c r="E7" s="37"/>
-      <x:c r="F7" s="42"/>
+      <x:c r="F7" s="43"/>
       <x:c r="G7" s="39"/>
       <x:c r="H7" s="37"/>
       <x:c r="I7" s="37"/>
@@ -1021,7 +1027,7 @@
       <x:c r="C8" s="37"/>
       <x:c r="D8" s="37"/>
       <x:c r="E8" s="37"/>
-      <x:c r="F8" s="42"/>
+      <x:c r="F8" s="43"/>
       <x:c r="G8" s="39"/>
       <x:c r="H8" s="37"/>
       <x:c r="I8" s="37"/>
@@ -1035,7 +1041,7 @@
       <x:c r="C9" s="37"/>
       <x:c r="D9" s="37"/>
       <x:c r="E9" s="37"/>
-      <x:c r="F9" s="42"/>
+      <x:c r="F9" s="43"/>
       <x:c r="G9" s="39"/>
       <x:c r="H9" s="37"/>
       <x:c r="I9" s="37"/>
@@ -1049,7 +1055,7 @@
       <x:c r="C10" s="37"/>
       <x:c r="D10" s="37"/>
       <x:c r="E10" s="37"/>
-      <x:c r="F10" s="42"/>
+      <x:c r="F10" s="43"/>
       <x:c r="G10" s="39"/>
       <x:c r="H10" s="37"/>
       <x:c r="I10" s="37"/>
@@ -1063,7 +1069,7 @@
       <x:c r="C11" s="37"/>
       <x:c r="D11" s="37"/>
       <x:c r="E11" s="37"/>
-      <x:c r="F11" s="42"/>
+      <x:c r="F11" s="43"/>
       <x:c r="G11" s="39"/>
       <x:c r="H11" s="37"/>
       <x:c r="I11" s="37"/>
@@ -1077,7 +1083,7 @@
       <x:c r="C12" s="37"/>
       <x:c r="D12" s="37"/>
       <x:c r="E12" s="37"/>
-      <x:c r="F12" s="42"/>
+      <x:c r="F12" s="43"/>
       <x:c r="G12" s="39"/>
       <x:c r="H12" s="37"/>
       <x:c r="I12" s="37"/>
@@ -1091,7 +1097,7 @@
       <x:c r="C13" s="37"/>
       <x:c r="D13" s="37"/>
       <x:c r="E13" s="37"/>
-      <x:c r="F13" s="42"/>
+      <x:c r="F13" s="43"/>
       <x:c r="G13" s="39"/>
       <x:c r="H13" s="37"/>
       <x:c r="I13" s="37"/>
@@ -1105,7 +1111,7 @@
       <x:c r="C14" s="37"/>
       <x:c r="D14" s="37"/>
       <x:c r="E14" s="37"/>
-      <x:c r="F14" s="42"/>
+      <x:c r="F14" s="43"/>
       <x:c r="G14" s="39"/>
       <x:c r="H14" s="37"/>
       <x:c r="I14" s="37"/>
@@ -1119,7 +1125,7 @@
       <x:c r="C15" s="37"/>
       <x:c r="D15" s="37"/>
       <x:c r="E15" s="37"/>
-      <x:c r="F15" s="42"/>
+      <x:c r="F15" s="43"/>
       <x:c r="G15" s="39"/>
       <x:c r="H15" s="37"/>
       <x:c r="I15" s="37"/>
@@ -1133,7 +1139,7 @@
       <x:c r="C16" s="37"/>
       <x:c r="D16" s="37"/>
       <x:c r="E16" s="37"/>
-      <x:c r="F16" s="42"/>
+      <x:c r="F16" s="43"/>
       <x:c r="G16" s="39"/>
       <x:c r="H16" s="37"/>
       <x:c r="I16" s="37"/>
@@ -1147,7 +1153,7 @@
       <x:c r="C17" s="37"/>
       <x:c r="D17" s="37"/>
       <x:c r="E17" s="37"/>
-      <x:c r="F17" s="42"/>
+      <x:c r="F17" s="43"/>
       <x:c r="G17" s="39"/>
       <x:c r="H17" s="37"/>
       <x:c r="I17" s="37"/>
@@ -1161,7 +1167,7 @@
       <x:c r="C18" s="37"/>
       <x:c r="D18" s="37"/>
       <x:c r="E18" s="37"/>
-      <x:c r="F18" s="42"/>
+      <x:c r="F18" s="43"/>
       <x:c r="G18" s="39"/>
       <x:c r="H18" s="37"/>
       <x:c r="I18" s="37"/>
@@ -1175,7 +1181,7 @@
       <x:c r="C19" s="37"/>
       <x:c r="D19" s="37"/>
       <x:c r="E19" s="37"/>
-      <x:c r="F19" s="42"/>
+      <x:c r="F19" s="43"/>
       <x:c r="G19" s="39"/>
       <x:c r="H19" s="37"/>
       <x:c r="I19" s="37"/>
@@ -1189,7 +1195,7 @@
       <x:c r="C20" s="37"/>
       <x:c r="D20" s="37"/>
       <x:c r="E20" s="37"/>
-      <x:c r="F20" s="42"/>
+      <x:c r="F20" s="43"/>
       <x:c r="G20" s="39"/>
       <x:c r="H20" s="37"/>
       <x:c r="I20" s="37"/>
@@ -1203,7 +1209,7 @@
       <x:c r="C21" s="37"/>
       <x:c r="D21" s="37"/>
       <x:c r="E21" s="37"/>
-      <x:c r="F21" s="42"/>
+      <x:c r="F21" s="43"/>
       <x:c r="G21" s="39"/>
       <x:c r="H21" s="37"/>
       <x:c r="I21" s="37"/>
@@ -1217,7 +1223,7 @@
       <x:c r="C22" s="37"/>
       <x:c r="D22" s="37"/>
       <x:c r="E22" s="37"/>
-      <x:c r="F22" s="42"/>
+      <x:c r="F22" s="43"/>
       <x:c r="G22" s="39"/>
       <x:c r="H22" s="37"/>
       <x:c r="I22" s="37"/>
@@ -1231,7 +1237,7 @@
       <x:c r="C23" s="37"/>
       <x:c r="D23" s="37"/>
       <x:c r="E23" s="37"/>
-      <x:c r="F23" s="42"/>
+      <x:c r="F23" s="43"/>
       <x:c r="G23" s="39"/>
       <x:c r="H23" s="37"/>
       <x:c r="I23" s="37"/>
@@ -1245,7 +1251,7 @@
       <x:c r="C24" s="37"/>
       <x:c r="D24" s="37"/>
       <x:c r="E24" s="37"/>
-      <x:c r="F24" s="42"/>
+      <x:c r="F24" s="43"/>
       <x:c r="G24" s="39"/>
       <x:c r="H24" s="37"/>
       <x:c r="I24" s="37"/>
@@ -1259,7 +1265,7 @@
       <x:c r="C25" s="37"/>
       <x:c r="D25" s="37"/>
       <x:c r="E25" s="37"/>
-      <x:c r="F25" s="42"/>
+      <x:c r="F25" s="43"/>
       <x:c r="G25" s="39"/>
       <x:c r="H25" s="37"/>
       <x:c r="I25" s="37"/>
@@ -1273,7 +1279,7 @@
       <x:c r="C26" s="37"/>
       <x:c r="D26" s="37"/>
       <x:c r="E26" s="37"/>
-      <x:c r="F26" s="42"/>
+      <x:c r="F26" s="43"/>
       <x:c r="G26" s="39"/>
       <x:c r="H26" s="37"/>
       <x:c r="I26" s="37"/>
@@ -1287,7 +1293,7 @@
       <x:c r="C27" s="37"/>
       <x:c r="D27" s="37"/>
       <x:c r="E27" s="37"/>
-      <x:c r="F27" s="42"/>
+      <x:c r="F27" s="43"/>
       <x:c r="G27" s="39"/>
       <x:c r="H27" s="37"/>
       <x:c r="I27" s="37"/>
@@ -1301,7 +1307,7 @@
       <x:c r="C28" s="37"/>
       <x:c r="D28" s="37"/>
       <x:c r="E28" s="37"/>
-      <x:c r="F28" s="42"/>
+      <x:c r="F28" s="43"/>
       <x:c r="G28" s="39"/>
       <x:c r="H28" s="37"/>
       <x:c r="I28" s="37"/>
@@ -1315,7 +1321,7 @@
       <x:c r="C29" s="37"/>
       <x:c r="D29" s="37"/>
       <x:c r="E29" s="37"/>
-      <x:c r="F29" s="42"/>
+      <x:c r="F29" s="43"/>
       <x:c r="G29" s="39"/>
       <x:c r="H29" s="37"/>
       <x:c r="I29" s="37"/>
@@ -1329,7 +1335,7 @@
       <x:c r="C30" s="37"/>
       <x:c r="D30" s="37"/>
       <x:c r="E30" s="37"/>
-      <x:c r="F30" s="42"/>
+      <x:c r="F30" s="43"/>
       <x:c r="G30" s="39"/>
       <x:c r="H30" s="37"/>
       <x:c r="I30" s="37"/>
@@ -1343,7 +1349,7 @@
       <x:c r="C31" s="37"/>
       <x:c r="D31" s="37"/>
       <x:c r="E31" s="37"/>
-      <x:c r="F31" s="42"/>
+      <x:c r="F31" s="43"/>
       <x:c r="G31" s="39"/>
       <x:c r="H31" s="37"/>
       <x:c r="I31" s="37"/>
@@ -1357,7 +1363,7 @@
       <x:c r="C32" s="37"/>
       <x:c r="D32" s="37"/>
       <x:c r="E32" s="37"/>
-      <x:c r="F32" s="42"/>
+      <x:c r="F32" s="43"/>
       <x:c r="G32" s="39"/>
       <x:c r="H32" s="37"/>
       <x:c r="I32" s="37"/>
@@ -1371,7 +1377,7 @@
       <x:c r="C33" s="37"/>
       <x:c r="D33" s="37"/>
       <x:c r="E33" s="37"/>
-      <x:c r="F33" s="42"/>
+      <x:c r="F33" s="43"/>
       <x:c r="G33" s="39"/>
       <x:c r="H33" s="37"/>
       <x:c r="I33" s="37"/>
@@ -1385,7 +1391,7 @@
       <x:c r="C34" s="37"/>
       <x:c r="D34" s="37"/>
       <x:c r="E34" s="37"/>
-      <x:c r="F34" s="42"/>
+      <x:c r="F34" s="43"/>
       <x:c r="G34" s="39"/>
       <x:c r="H34" s="37"/>
       <x:c r="I34" s="37"/>
@@ -1399,7 +1405,7 @@
       <x:c r="C35" s="37"/>
       <x:c r="D35" s="37"/>
       <x:c r="E35" s="37"/>
-      <x:c r="F35" s="42"/>
+      <x:c r="F35" s="43"/>
       <x:c r="G35" s="39"/>
       <x:c r="H35" s="37"/>
       <x:c r="I35" s="37"/>
@@ -1413,7 +1419,7 @@
       <x:c r="C36" s="37"/>
       <x:c r="D36" s="37"/>
       <x:c r="E36" s="37"/>
-      <x:c r="F36" s="42"/>
+      <x:c r="F36" s="43"/>
       <x:c r="G36" s="39"/>
       <x:c r="H36" s="37"/>
       <x:c r="I36" s="37"/>
@@ -1427,7 +1433,7 @@
       <x:c r="C37" s="37"/>
       <x:c r="D37" s="37"/>
       <x:c r="E37" s="37"/>
-      <x:c r="F37" s="42"/>
+      <x:c r="F37" s="43"/>
       <x:c r="G37" s="39"/>
       <x:c r="H37" s="37"/>
       <x:c r="I37" s="37"/>
@@ -1441,7 +1447,7 @@
       <x:c r="C38" s="37"/>
       <x:c r="D38" s="37"/>
       <x:c r="E38" s="37"/>
-      <x:c r="F38" s="42"/>
+      <x:c r="F38" s="43"/>
       <x:c r="G38" s="39"/>
       <x:c r="H38" s="37"/>
       <x:c r="I38" s="37"/>
@@ -1455,7 +1461,7 @@
       <x:c r="C39" s="37"/>
       <x:c r="D39" s="37"/>
       <x:c r="E39" s="37"/>
-      <x:c r="F39" s="42"/>
+      <x:c r="F39" s="43"/>
       <x:c r="G39" s="39"/>
       <x:c r="H39" s="37"/>
       <x:c r="I39" s="37"/>
@@ -1469,7 +1475,7 @@
       <x:c r="C40" s="37"/>
       <x:c r="D40" s="37"/>
       <x:c r="E40" s="37"/>
-      <x:c r="F40" s="42"/>
+      <x:c r="F40" s="43"/>
       <x:c r="G40" s="39"/>
       <x:c r="H40" s="37"/>
       <x:c r="I40" s="37"/>
@@ -1483,7 +1489,7 @@
       <x:c r="C41" s="37"/>
       <x:c r="D41" s="37"/>
       <x:c r="E41" s="37"/>
-      <x:c r="F41" s="42"/>
+      <x:c r="F41" s="43"/>
       <x:c r="G41" s="39"/>
       <x:c r="H41" s="37"/>
       <x:c r="I41" s="37"/>
@@ -1497,7 +1503,7 @@
       <x:c r="C42" s="37"/>
       <x:c r="D42" s="37"/>
       <x:c r="E42" s="37"/>
-      <x:c r="F42" s="42"/>
+      <x:c r="F42" s="43"/>
       <x:c r="G42" s="39"/>
       <x:c r="H42" s="37"/>
       <x:c r="I42" s="37"/>
@@ -1511,7 +1517,7 @@
       <x:c r="C43" s="37"/>
       <x:c r="D43" s="37"/>
       <x:c r="E43" s="37"/>
-      <x:c r="F43" s="42"/>
+      <x:c r="F43" s="43"/>
       <x:c r="G43" s="39"/>
       <x:c r="H43" s="37"/>
       <x:c r="I43" s="37"/>
@@ -1525,7 +1531,7 @@
       <x:c r="C44" s="37"/>
       <x:c r="D44" s="37"/>
       <x:c r="E44" s="37"/>
-      <x:c r="F44" s="42"/>
+      <x:c r="F44" s="43"/>
       <x:c r="G44" s="39"/>
       <x:c r="H44" s="37"/>
       <x:c r="I44" s="37"/>
@@ -1539,7 +1545,7 @@
       <x:c r="C45" s="37"/>
       <x:c r="D45" s="37"/>
       <x:c r="E45" s="37"/>
-      <x:c r="F45" s="42"/>
+      <x:c r="F45" s="43"/>
       <x:c r="G45" s="39"/>
       <x:c r="H45" s="37"/>
       <x:c r="I45" s="37"/>
@@ -1553,7 +1559,7 @@
       <x:c r="C46" s="37"/>
       <x:c r="D46" s="37"/>
       <x:c r="E46" s="37"/>
-      <x:c r="F46" s="42"/>
+      <x:c r="F46" s="43"/>
       <x:c r="G46" s="39"/>
       <x:c r="H46" s="37"/>
       <x:c r="I46" s="37"/>
@@ -1567,7 +1573,7 @@
       <x:c r="C47" s="37"/>
       <x:c r="D47" s="37"/>
       <x:c r="E47" s="37"/>
-      <x:c r="F47" s="42"/>
+      <x:c r="F47" s="43"/>
       <x:c r="G47" s="39"/>
       <x:c r="H47" s="37"/>
       <x:c r="I47" s="37"/>
@@ -1581,7 +1587,7 @@
       <x:c r="C48" s="37"/>
       <x:c r="D48" s="37"/>
       <x:c r="E48" s="37"/>
-      <x:c r="F48" s="42"/>
+      <x:c r="F48" s="43"/>
       <x:c r="G48" s="39"/>
       <x:c r="H48" s="37"/>
       <x:c r="I48" s="37"/>
@@ -1595,7 +1601,7 @@
       <x:c r="C49" s="37"/>
       <x:c r="D49" s="37"/>
       <x:c r="E49" s="37"/>
-      <x:c r="F49" s="42"/>
+      <x:c r="F49" s="43"/>
       <x:c r="G49" s="39"/>
       <x:c r="H49" s="37"/>
       <x:c r="I49" s="37"/>
@@ -1609,7 +1615,7 @@
       <x:c r="C50" s="37"/>
       <x:c r="D50" s="37"/>
       <x:c r="E50" s="37"/>
-      <x:c r="F50" s="42"/>
+      <x:c r="F50" s="43"/>
       <x:c r="G50" s="39"/>
       <x:c r="H50" s="37"/>
       <x:c r="I50" s="37"/>
@@ -1623,7 +1629,7 @@
       <x:c r="C51" s="37"/>
       <x:c r="D51" s="37"/>
       <x:c r="E51" s="37"/>
-      <x:c r="F51" s="42"/>
+      <x:c r="F51" s="43"/>
       <x:c r="G51" s="39"/>
       <x:c r="H51" s="37"/>
       <x:c r="I51" s="37"/>
@@ -1637,7 +1643,7 @@
       <x:c r="C52" s="37"/>
       <x:c r="D52" s="37"/>
       <x:c r="E52" s="37"/>
-      <x:c r="F52" s="42"/>
+      <x:c r="F52" s="43"/>
       <x:c r="G52" s="39"/>
       <x:c r="H52" s="37"/>
       <x:c r="I52" s="37"/>
@@ -1651,7 +1657,7 @@
       <x:c r="C53" s="37"/>
       <x:c r="D53" s="37"/>
       <x:c r="E53" s="37"/>
-      <x:c r="F53" s="42"/>
+      <x:c r="F53" s="43"/>
       <x:c r="G53" s="39"/>
       <x:c r="H53" s="37"/>
       <x:c r="I53" s="37"/>
@@ -1665,7 +1671,7 @@
       <x:c r="C54" s="37"/>
       <x:c r="D54" s="37"/>
       <x:c r="E54" s="37"/>
-      <x:c r="F54" s="42"/>
+      <x:c r="F54" s="43"/>
       <x:c r="G54" s="39"/>
       <x:c r="H54" s="37"/>
       <x:c r="I54" s="37"/>
@@ -1679,7 +1685,7 @@
       <x:c r="C55" s="37"/>
       <x:c r="D55" s="37"/>
       <x:c r="E55" s="37"/>
-      <x:c r="F55" s="42"/>
+      <x:c r="F55" s="43"/>
       <x:c r="G55" s="39"/>
       <x:c r="H55" s="37"/>
       <x:c r="I55" s="37"/>
@@ -1693,7 +1699,7 @@
       <x:c r="C56" s="37"/>
       <x:c r="D56" s="37"/>
       <x:c r="E56" s="37"/>
-      <x:c r="F56" s="42"/>
+      <x:c r="F56" s="43"/>
       <x:c r="G56" s="39"/>
       <x:c r="H56" s="37"/>
       <x:c r="I56" s="37"/>
@@ -1707,7 +1713,7 @@
       <x:c r="C57" s="37"/>
       <x:c r="D57" s="37"/>
       <x:c r="E57" s="37"/>
-      <x:c r="F57" s="42"/>
+      <x:c r="F57" s="43"/>
       <x:c r="G57" s="39"/>
       <x:c r="H57" s="37"/>
       <x:c r="I57" s="37"/>
@@ -1721,7 +1727,7 @@
       <x:c r="C58" s="37"/>
       <x:c r="D58" s="37"/>
       <x:c r="E58" s="37"/>
-      <x:c r="F58" s="42"/>
+      <x:c r="F58" s="43"/>
       <x:c r="G58" s="39"/>
       <x:c r="H58" s="37"/>
       <x:c r="I58" s="37"/>
@@ -1735,7 +1741,7 @@
       <x:c r="C59" s="37"/>
       <x:c r="D59" s="37"/>
       <x:c r="E59" s="37"/>
-      <x:c r="F59" s="42"/>
+      <x:c r="F59" s="43"/>
       <x:c r="G59" s="39"/>
       <x:c r="H59" s="37"/>
       <x:c r="I59" s="37"/>
@@ -1749,7 +1755,7 @@
       <x:c r="C60" s="37"/>
       <x:c r="D60" s="37"/>
       <x:c r="E60" s="37"/>
-      <x:c r="F60" s="42"/>
+      <x:c r="F60" s="43"/>
       <x:c r="G60" s="39"/>
       <x:c r="H60" s="37"/>
       <x:c r="I60" s="37"/>
@@ -1763,7 +1769,7 @@
       <x:c r="C61" s="37"/>
       <x:c r="D61" s="37"/>
       <x:c r="E61" s="37"/>
-      <x:c r="F61" s="42"/>
+      <x:c r="F61" s="43"/>
       <x:c r="G61" s="39"/>
       <x:c r="H61" s="37"/>
       <x:c r="I61" s="37"/>
@@ -1777,7 +1783,7 @@
       <x:c r="C62" s="37"/>
       <x:c r="D62" s="37"/>
       <x:c r="E62" s="37"/>
-      <x:c r="F62" s="42"/>
+      <x:c r="F62" s="43"/>
       <x:c r="G62" s="39"/>
       <x:c r="H62" s="37"/>
       <x:c r="I62" s="37"/>
@@ -1791,7 +1797,7 @@
       <x:c r="C63" s="37"/>
       <x:c r="D63" s="37"/>
       <x:c r="E63" s="37"/>
-      <x:c r="F63" s="42"/>
+      <x:c r="F63" s="43"/>
       <x:c r="G63" s="39"/>
       <x:c r="H63" s="37"/>
       <x:c r="I63" s="37"/>
@@ -1805,7 +1811,7 @@
       <x:c r="C64" s="37"/>
       <x:c r="D64" s="37"/>
       <x:c r="E64" s="37"/>
-      <x:c r="F64" s="42"/>
+      <x:c r="F64" s="43"/>
       <x:c r="G64" s="39"/>
       <x:c r="H64" s="37"/>
       <x:c r="I64" s="37"/>
@@ -1819,7 +1825,7 @@
       <x:c r="C65" s="37"/>
       <x:c r="D65" s="37"/>
       <x:c r="E65" s="37"/>
-      <x:c r="F65" s="42"/>
+      <x:c r="F65" s="43"/>
       <x:c r="G65" s="39"/>
       <x:c r="H65" s="37"/>
       <x:c r="I65" s="37"/>
@@ -1833,7 +1839,7 @@
       <x:c r="C66" s="37"/>
       <x:c r="D66" s="37"/>
       <x:c r="E66" s="37"/>
-      <x:c r="F66" s="42"/>
+      <x:c r="F66" s="43"/>
       <x:c r="G66" s="39"/>
       <x:c r="H66" s="37"/>
       <x:c r="I66" s="37"/>
@@ -1847,7 +1853,7 @@
       <x:c r="C67" s="37"/>
       <x:c r="D67" s="37"/>
       <x:c r="E67" s="37"/>
-      <x:c r="F67" s="42"/>
+      <x:c r="F67" s="43"/>
       <x:c r="G67" s="39"/>
       <x:c r="H67" s="37"/>
       <x:c r="I67" s="37"/>
@@ -1861,7 +1867,7 @@
       <x:c r="C68" s="37"/>
       <x:c r="D68" s="37"/>
       <x:c r="E68" s="37"/>
-      <x:c r="F68" s="42"/>
+      <x:c r="F68" s="43"/>
       <x:c r="G68" s="39"/>
       <x:c r="H68" s="37"/>
       <x:c r="I68" s="37"/>
@@ -1875,7 +1881,7 @@
       <x:c r="C69" s="37"/>
       <x:c r="D69" s="37"/>
       <x:c r="E69" s="37"/>
-      <x:c r="F69" s="42"/>
+      <x:c r="F69" s="43"/>
       <x:c r="G69" s="39"/>
       <x:c r="H69" s="37"/>
       <x:c r="I69" s="37"/>
@@ -1889,7 +1895,7 @@
       <x:c r="C70" s="37"/>
       <x:c r="D70" s="37"/>
       <x:c r="E70" s="37"/>
-      <x:c r="F70" s="42"/>
+      <x:c r="F70" s="43"/>
       <x:c r="G70" s="39"/>
       <x:c r="H70" s="37"/>
       <x:c r="I70" s="37"/>
@@ -1903,7 +1909,7 @@
       <x:c r="C71" s="37"/>
       <x:c r="D71" s="37"/>
       <x:c r="E71" s="37"/>
-      <x:c r="F71" s="42"/>
+      <x:c r="F71" s="43"/>
       <x:c r="G71" s="39"/>
       <x:c r="H71" s="37"/>
       <x:c r="I71" s="37"/>
@@ -1917,7 +1923,7 @@
       <x:c r="C72" s="37"/>
       <x:c r="D72" s="37"/>
       <x:c r="E72" s="37"/>
-      <x:c r="F72" s="42"/>
+      <x:c r="F72" s="43"/>
       <x:c r="G72" s="39"/>
       <x:c r="H72" s="37"/>
       <x:c r="I72" s="37"/>
@@ -1931,7 +1937,7 @@
       <x:c r="C73" s="37"/>
       <x:c r="D73" s="37"/>
       <x:c r="E73" s="37"/>
-      <x:c r="F73" s="42"/>
+      <x:c r="F73" s="43"/>
       <x:c r="G73" s="39"/>
       <x:c r="H73" s="37"/>
       <x:c r="I73" s="37"/>
@@ -1945,7 +1951,7 @@
       <x:c r="C74" s="37"/>
       <x:c r="D74" s="37"/>
       <x:c r="E74" s="37"/>
-      <x:c r="F74" s="42"/>
+      <x:c r="F74" s="43"/>
       <x:c r="G74" s="39"/>
       <x:c r="H74" s="37"/>
       <x:c r="I74" s="37"/>
@@ -1959,7 +1965,7 @@
       <x:c r="C75" s="37"/>
       <x:c r="D75" s="37"/>
       <x:c r="E75" s="37"/>
-      <x:c r="F75" s="42"/>
+      <x:c r="F75" s="43"/>
       <x:c r="G75" s="39"/>
       <x:c r="H75" s="37"/>
       <x:c r="I75" s="37"/>
@@ -1973,7 +1979,7 @@
       <x:c r="C76" s="37"/>
       <x:c r="D76" s="37"/>
       <x:c r="E76" s="37"/>
-      <x:c r="F76" s="42"/>
+      <x:c r="F76" s="43"/>
       <x:c r="G76" s="39"/>
       <x:c r="H76" s="37"/>
       <x:c r="I76" s="37"/>
@@ -1987,7 +1993,7 @@
       <x:c r="C77" s="37"/>
       <x:c r="D77" s="37"/>
       <x:c r="E77" s="37"/>
-      <x:c r="F77" s="42"/>
+      <x:c r="F77" s="43"/>
       <x:c r="G77" s="39"/>
       <x:c r="H77" s="37"/>
       <x:c r="I77" s="37"/>
@@ -2001,7 +2007,7 @@
       <x:c r="C78" s="37"/>
       <x:c r="D78" s="37"/>
       <x:c r="E78" s="37"/>
-      <x:c r="F78" s="42"/>
+      <x:c r="F78" s="43"/>
       <x:c r="G78" s="39"/>
       <x:c r="H78" s="37"/>
       <x:c r="I78" s="37"/>
@@ -2015,7 +2021,7 @@
       <x:c r="C79" s="37"/>
       <x:c r="D79" s="37"/>
       <x:c r="E79" s="37"/>
-      <x:c r="F79" s="42"/>
+      <x:c r="F79" s="43"/>
       <x:c r="G79" s="39"/>
       <x:c r="H79" s="37"/>
       <x:c r="I79" s="37"/>
@@ -2029,7 +2035,7 @@
       <x:c r="C80" s="37"/>
       <x:c r="D80" s="37"/>
       <x:c r="E80" s="37"/>
-      <x:c r="F80" s="42"/>
+      <x:c r="F80" s="43"/>
       <x:c r="G80" s="39"/>
       <x:c r="H80" s="37"/>
       <x:c r="I80" s="37"/>
@@ -2043,7 +2049,7 @@
       <x:c r="C81" s="37"/>
       <x:c r="D81" s="37"/>
       <x:c r="E81" s="37"/>
-      <x:c r="F81" s="42"/>
+      <x:c r="F81" s="43"/>
       <x:c r="G81" s="39"/>
       <x:c r="H81" s="37"/>
       <x:c r="I81" s="37"/>
@@ -2057,7 +2063,7 @@
       <x:c r="C82" s="37"/>
       <x:c r="D82" s="37"/>
       <x:c r="E82" s="37"/>
-      <x:c r="F82" s="42"/>
+      <x:c r="F82" s="43"/>
       <x:c r="G82" s="39"/>
       <x:c r="H82" s="37"/>
       <x:c r="I82" s="37"/>
@@ -2071,7 +2077,7 @@
       <x:c r="C83" s="37"/>
       <x:c r="D83" s="37"/>
       <x:c r="E83" s="37"/>
-      <x:c r="F83" s="42"/>
+      <x:c r="F83" s="43"/>
       <x:c r="G83" s="39"/>
       <x:c r="H83" s="37"/>
       <x:c r="I83" s="37"/>
@@ -2085,7 +2091,7 @@
       <x:c r="C84" s="37"/>
       <x:c r="D84" s="37"/>
       <x:c r="E84" s="37"/>
-      <x:c r="F84" s="42"/>
+      <x:c r="F84" s="43"/>
       <x:c r="G84" s="39"/>
       <x:c r="H84" s="37"/>
       <x:c r="I84" s="37"/>
@@ -2099,7 +2105,7 @@
       <x:c r="C85" s="37"/>
       <x:c r="D85" s="37"/>
       <x:c r="E85" s="37"/>
-      <x:c r="F85" s="42"/>
+      <x:c r="F85" s="43"/>
       <x:c r="G85" s="39"/>
       <x:c r="H85" s="37"/>
       <x:c r="I85" s="37"/>
@@ -2113,7 +2119,7 @@
       <x:c r="C86" s="37"/>
       <x:c r="D86" s="37"/>
       <x:c r="E86" s="37"/>
-      <x:c r="F86" s="42"/>
+      <x:c r="F86" s="43"/>
       <x:c r="G86" s="39"/>
       <x:c r="H86" s="37"/>
       <x:c r="I86" s="37"/>
@@ -2127,7 +2133,7 @@
       <x:c r="C87" s="37"/>
       <x:c r="D87" s="37"/>
       <x:c r="E87" s="37"/>
-      <x:c r="F87" s="42"/>
+      <x:c r="F87" s="43"/>
       <x:c r="G87" s="39"/>
       <x:c r="H87" s="37"/>
       <x:c r="I87" s="37"/>
@@ -2141,7 +2147,7 @@
       <x:c r="C88" s="37"/>
       <x:c r="D88" s="37"/>
       <x:c r="E88" s="37"/>
-      <x:c r="F88" s="42"/>
+      <x:c r="F88" s="43"/>
       <x:c r="G88" s="39"/>
       <x:c r="H88" s="37"/>
       <x:c r="I88" s="37"/>
@@ -2155,7 +2161,7 @@
       <x:c r="C89" s="37"/>
       <x:c r="D89" s="37"/>
       <x:c r="E89" s="37"/>
-      <x:c r="F89" s="42"/>
+      <x:c r="F89" s="43"/>
       <x:c r="G89" s="39"/>
       <x:c r="H89" s="37"/>
       <x:c r="I89" s="37"/>
@@ -2169,7 +2175,7 @@
       <x:c r="C90" s="37"/>
       <x:c r="D90" s="37"/>
       <x:c r="E90" s="37"/>
-      <x:c r="F90" s="42"/>
+      <x:c r="F90" s="43"/>
       <x:c r="G90" s="39"/>
       <x:c r="H90" s="37"/>
       <x:c r="I90" s="37"/>
@@ -2183,7 +2189,7 @@
       <x:c r="C91" s="37"/>
       <x:c r="D91" s="37"/>
       <x:c r="E91" s="37"/>
-      <x:c r="F91" s="42"/>
+      <x:c r="F91" s="43"/>
       <x:c r="G91" s="39"/>
       <x:c r="H91" s="37"/>
       <x:c r="I91" s="37"/>
@@ -2197,7 +2203,7 @@
       <x:c r="C92" s="37"/>
       <x:c r="D92" s="37"/>
       <x:c r="E92" s="37"/>
-      <x:c r="F92" s="42"/>
+      <x:c r="F92" s="43"/>
       <x:c r="G92" s="39"/>
       <x:c r="H92" s="37"/>
       <x:c r="I92" s="37"/>
@@ -2211,7 +2217,7 @@
       <x:c r="C93" s="37"/>
       <x:c r="D93" s="37"/>
       <x:c r="E93" s="37"/>
-      <x:c r="F93" s="42"/>
+      <x:c r="F93" s="43"/>
       <x:c r="G93" s="39"/>
       <x:c r="H93" s="37"/>
       <x:c r="I93" s="37"/>
@@ -2225,7 +2231,7 @@
       <x:c r="C94" s="37"/>
       <x:c r="D94" s="37"/>
       <x:c r="E94" s="37"/>
-      <x:c r="F94" s="42"/>
+      <x:c r="F94" s="43"/>
       <x:c r="G94" s="39"/>
       <x:c r="H94" s="37"/>
       <x:c r="I94" s="37"/>
@@ -2239,7 +2245,7 @@
       <x:c r="C95" s="37"/>
       <x:c r="D95" s="37"/>
       <x:c r="E95" s="37"/>
-      <x:c r="F95" s="42"/>
+      <x:c r="F95" s="43"/>
       <x:c r="G95" s="39"/>
       <x:c r="H95" s="37"/>
       <x:c r="I95" s="37"/>
@@ -2253,7 +2259,7 @@
       <x:c r="C96" s="37"/>
       <x:c r="D96" s="37"/>
       <x:c r="E96" s="37"/>
-      <x:c r="F96" s="42"/>
+      <x:c r="F96" s="43"/>
       <x:c r="G96" s="39"/>
       <x:c r="H96" s="37"/>
       <x:c r="I96" s="37"/>
@@ -2267,7 +2273,7 @@
       <x:c r="C97" s="37"/>
       <x:c r="D97" s="37"/>
       <x:c r="E97" s="37"/>
-      <x:c r="F97" s="42"/>
+      <x:c r="F97" s="43"/>
       <x:c r="G97" s="39"/>
       <x:c r="H97" s="37"/>
       <x:c r="I97" s="37"/>
@@ -2281,7 +2287,7 @@
       <x:c r="C98" s="37"/>
       <x:c r="D98" s="37"/>
       <x:c r="E98" s="37"/>
-      <x:c r="F98" s="42"/>
+      <x:c r="F98" s="43"/>
       <x:c r="G98" s="39"/>
       <x:c r="H98" s="37"/>
       <x:c r="I98" s="37"/>
@@ -2295,7 +2301,7 @@
       <x:c r="C99" s="37"/>
       <x:c r="D99" s="37"/>
       <x:c r="E99" s="37"/>
-      <x:c r="F99" s="42"/>
+      <x:c r="F99" s="43"/>
       <x:c r="G99" s="39"/>
       <x:c r="H99" s="37"/>
       <x:c r="I99" s="37"/>
@@ -2309,7 +2315,7 @@
       <x:c r="C100" s="37"/>
       <x:c r="D100" s="37"/>
       <x:c r="E100" s="37"/>
-      <x:c r="F100" s="42"/>
+      <x:c r="F100" s="43"/>
       <x:c r="G100" s="39"/>
       <x:c r="H100" s="37"/>
       <x:c r="I100" s="37"/>
@@ -2323,7 +2329,7 @@
       <x:c r="C101" s="37"/>
       <x:c r="D101" s="37"/>
       <x:c r="E101" s="37"/>
-      <x:c r="F101" s="42"/>
+      <x:c r="F101" s="43"/>
       <x:c r="G101" s="39"/>
       <x:c r="H101" s="37"/>
       <x:c r="I101" s="37"/>
@@ -2337,7 +2343,7 @@
       <x:c r="C102" s="37"/>
       <x:c r="D102" s="37"/>
       <x:c r="E102" s="37"/>
-      <x:c r="F102" s="42"/>
+      <x:c r="F102" s="43"/>
       <x:c r="G102" s="39"/>
       <x:c r="H102" s="37"/>
       <x:c r="I102" s="37"/>
@@ -2351,7 +2357,7 @@
       <x:c r="C103" s="37"/>
       <x:c r="D103" s="37"/>
       <x:c r="E103" s="37"/>
-      <x:c r="F103" s="42"/>
+      <x:c r="F103" s="43"/>
       <x:c r="G103" s="39"/>
       <x:c r="H103" s="37"/>
       <x:c r="I103" s="37"/>
@@ -2365,7 +2371,7 @@
       <x:c r="C104" s="37"/>
       <x:c r="D104" s="37"/>
       <x:c r="E104" s="37"/>
-      <x:c r="F104" s="42"/>
+      <x:c r="F104" s="43"/>
       <x:c r="G104" s="39"/>
       <x:c r="H104" s="37"/>
       <x:c r="I104" s="37"/>
@@ -2389,7 +2395,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbcd29399bf484a40"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54fbee42fcdc4a6a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2499,7 +2505,7 @@
       <x:c r="B5" s="37"/>
       <x:c r="C5" s="37"/>
       <x:c r="D5" s="37"/>
-      <x:c r="E5" s="42"/>
+      <x:c r="E5" s="43"/>
       <x:c r="F5" s="39"/>
       <x:c r="G5" s="37"/>
       <x:c r="H5" s="37"/>
@@ -2512,7 +2518,7 @@
       <x:c r="B6" s="37"/>
       <x:c r="C6" s="37"/>
       <x:c r="D6" s="37"/>
-      <x:c r="E6" s="42"/>
+      <x:c r="E6" s="43"/>
       <x:c r="F6" s="39"/>
       <x:c r="G6" s="37"/>
       <x:c r="H6" s="37"/>
@@ -2525,7 +2531,7 @@
       <x:c r="B7" s="37"/>
       <x:c r="C7" s="37"/>
       <x:c r="D7" s="37"/>
-      <x:c r="E7" s="42"/>
+      <x:c r="E7" s="43"/>
       <x:c r="F7" s="39"/>
       <x:c r="G7" s="37"/>
       <x:c r="H7" s="37"/>
@@ -2538,7 +2544,7 @@
       <x:c r="B8" s="37"/>
       <x:c r="C8" s="37"/>
       <x:c r="D8" s="37"/>
-      <x:c r="E8" s="42"/>
+      <x:c r="E8" s="43"/>
       <x:c r="F8" s="39"/>
       <x:c r="G8" s="37"/>
       <x:c r="H8" s="37"/>
@@ -2551,7 +2557,7 @@
       <x:c r="B9" s="37"/>
       <x:c r="C9" s="37"/>
       <x:c r="D9" s="37"/>
-      <x:c r="E9" s="42"/>
+      <x:c r="E9" s="43"/>
       <x:c r="F9" s="39"/>
       <x:c r="G9" s="37"/>
       <x:c r="H9" s="37"/>
@@ -2564,7 +2570,7 @@
       <x:c r="B10" s="37"/>
       <x:c r="C10" s="37"/>
       <x:c r="D10" s="37"/>
-      <x:c r="E10" s="42"/>
+      <x:c r="E10" s="43"/>
       <x:c r="F10" s="39"/>
       <x:c r="G10" s="37"/>
       <x:c r="H10" s="37"/>
@@ -2577,7 +2583,7 @@
       <x:c r="B11" s="37"/>
       <x:c r="C11" s="37"/>
       <x:c r="D11" s="37"/>
-      <x:c r="E11" s="42"/>
+      <x:c r="E11" s="43"/>
       <x:c r="F11" s="39"/>
       <x:c r="G11" s="37"/>
       <x:c r="H11" s="37"/>
@@ -2590,7 +2596,7 @@
       <x:c r="B12" s="37"/>
       <x:c r="C12" s="37"/>
       <x:c r="D12" s="37"/>
-      <x:c r="E12" s="42"/>
+      <x:c r="E12" s="43"/>
       <x:c r="F12" s="39"/>
       <x:c r="G12" s="37"/>
       <x:c r="H12" s="37"/>
@@ -2603,7 +2609,7 @@
       <x:c r="B13" s="37"/>
       <x:c r="C13" s="37"/>
       <x:c r="D13" s="37"/>
-      <x:c r="E13" s="42"/>
+      <x:c r="E13" s="43"/>
       <x:c r="F13" s="39"/>
       <x:c r="G13" s="37"/>
       <x:c r="H13" s="37"/>
@@ -2616,7 +2622,7 @@
       <x:c r="B14" s="37"/>
       <x:c r="C14" s="37"/>
       <x:c r="D14" s="37"/>
-      <x:c r="E14" s="42"/>
+      <x:c r="E14" s="43"/>
       <x:c r="F14" s="39"/>
       <x:c r="G14" s="37"/>
       <x:c r="H14" s="37"/>
@@ -2629,7 +2635,7 @@
       <x:c r="B15" s="37"/>
       <x:c r="C15" s="37"/>
       <x:c r="D15" s="37"/>
-      <x:c r="E15" s="42"/>
+      <x:c r="E15" s="43"/>
       <x:c r="F15" s="39"/>
       <x:c r="G15" s="37"/>
       <x:c r="H15" s="37"/>
@@ -2642,7 +2648,7 @@
       <x:c r="B16" s="37"/>
       <x:c r="C16" s="37"/>
       <x:c r="D16" s="37"/>
-      <x:c r="E16" s="42"/>
+      <x:c r="E16" s="43"/>
       <x:c r="F16" s="39"/>
       <x:c r="G16" s="37"/>
       <x:c r="H16" s="37"/>
@@ -2655,7 +2661,7 @@
       <x:c r="B17" s="37"/>
       <x:c r="C17" s="37"/>
       <x:c r="D17" s="37"/>
-      <x:c r="E17" s="42"/>
+      <x:c r="E17" s="43"/>
       <x:c r="F17" s="39"/>
       <x:c r="G17" s="37"/>
       <x:c r="H17" s="37"/>
@@ -2668,7 +2674,7 @@
       <x:c r="B18" s="37"/>
       <x:c r="C18" s="37"/>
       <x:c r="D18" s="37"/>
-      <x:c r="E18" s="42"/>
+      <x:c r="E18" s="43"/>
       <x:c r="F18" s="39"/>
       <x:c r="G18" s="37"/>
       <x:c r="H18" s="37"/>
@@ -2681,7 +2687,7 @@
       <x:c r="B19" s="37"/>
       <x:c r="C19" s="37"/>
       <x:c r="D19" s="37"/>
-      <x:c r="E19" s="42"/>
+      <x:c r="E19" s="43"/>
       <x:c r="F19" s="39"/>
       <x:c r="G19" s="37"/>
       <x:c r="H19" s="37"/>
@@ -2694,7 +2700,7 @@
       <x:c r="B20" s="37"/>
       <x:c r="C20" s="37"/>
       <x:c r="D20" s="37"/>
-      <x:c r="E20" s="42"/>
+      <x:c r="E20" s="43"/>
       <x:c r="F20" s="39"/>
       <x:c r="G20" s="37"/>
       <x:c r="H20" s="37"/>
@@ -2707,7 +2713,7 @@
       <x:c r="B21" s="37"/>
       <x:c r="C21" s="37"/>
       <x:c r="D21" s="37"/>
-      <x:c r="E21" s="42"/>
+      <x:c r="E21" s="43"/>
       <x:c r="F21" s="39"/>
       <x:c r="G21" s="37"/>
       <x:c r="H21" s="37"/>
@@ -2720,7 +2726,7 @@
       <x:c r="B22" s="37"/>
       <x:c r="C22" s="37"/>
       <x:c r="D22" s="37"/>
-      <x:c r="E22" s="42"/>
+      <x:c r="E22" s="43"/>
       <x:c r="F22" s="39"/>
       <x:c r="G22" s="37"/>
       <x:c r="H22" s="37"/>
@@ -2733,7 +2739,7 @@
       <x:c r="B23" s="37"/>
       <x:c r="C23" s="37"/>
       <x:c r="D23" s="37"/>
-      <x:c r="E23" s="42"/>
+      <x:c r="E23" s="43"/>
       <x:c r="F23" s="39"/>
       <x:c r="G23" s="37"/>
       <x:c r="H23" s="37"/>
@@ -2746,7 +2752,7 @@
       <x:c r="B24" s="37"/>
       <x:c r="C24" s="37"/>
       <x:c r="D24" s="37"/>
-      <x:c r="E24" s="42"/>
+      <x:c r="E24" s="43"/>
       <x:c r="F24" s="39"/>
       <x:c r="G24" s="37"/>
       <x:c r="H24" s="37"/>
@@ -2759,7 +2765,7 @@
       <x:c r="B25" s="37"/>
       <x:c r="C25" s="37"/>
       <x:c r="D25" s="37"/>
-      <x:c r="E25" s="42"/>
+      <x:c r="E25" s="43"/>
       <x:c r="F25" s="39"/>
       <x:c r="G25" s="37"/>
       <x:c r="H25" s="37"/>
@@ -2772,7 +2778,7 @@
       <x:c r="B26" s="37"/>
       <x:c r="C26" s="37"/>
       <x:c r="D26" s="37"/>
-      <x:c r="E26" s="42"/>
+      <x:c r="E26" s="43"/>
       <x:c r="F26" s="39"/>
       <x:c r="G26" s="37"/>
       <x:c r="H26" s="37"/>
@@ -2785,7 +2791,7 @@
       <x:c r="B27" s="37"/>
       <x:c r="C27" s="37"/>
       <x:c r="D27" s="37"/>
-      <x:c r="E27" s="42"/>
+      <x:c r="E27" s="43"/>
       <x:c r="F27" s="39"/>
       <x:c r="G27" s="37"/>
       <x:c r="H27" s="37"/>
@@ -2798,7 +2804,7 @@
       <x:c r="B28" s="37"/>
       <x:c r="C28" s="37"/>
       <x:c r="D28" s="37"/>
-      <x:c r="E28" s="42"/>
+      <x:c r="E28" s="43"/>
       <x:c r="F28" s="39"/>
       <x:c r="G28" s="37"/>
       <x:c r="H28" s="37"/>
@@ -2811,7 +2817,7 @@
       <x:c r="B29" s="37"/>
       <x:c r="C29" s="37"/>
       <x:c r="D29" s="37"/>
-      <x:c r="E29" s="42"/>
+      <x:c r="E29" s="43"/>
       <x:c r="F29" s="39"/>
       <x:c r="G29" s="37"/>
       <x:c r="H29" s="37"/>
@@ -2824,7 +2830,7 @@
       <x:c r="B30" s="37"/>
       <x:c r="C30" s="37"/>
       <x:c r="D30" s="37"/>
-      <x:c r="E30" s="42"/>
+      <x:c r="E30" s="43"/>
       <x:c r="F30" s="39"/>
       <x:c r="G30" s="37"/>
       <x:c r="H30" s="37"/>
@@ -2837,7 +2843,7 @@
       <x:c r="B31" s="37"/>
       <x:c r="C31" s="37"/>
       <x:c r="D31" s="37"/>
-      <x:c r="E31" s="42"/>
+      <x:c r="E31" s="43"/>
       <x:c r="F31" s="39"/>
       <x:c r="G31" s="37"/>
       <x:c r="H31" s="37"/>
@@ -2850,7 +2856,7 @@
       <x:c r="B32" s="37"/>
       <x:c r="C32" s="37"/>
       <x:c r="D32" s="37"/>
-      <x:c r="E32" s="42"/>
+      <x:c r="E32" s="43"/>
       <x:c r="F32" s="39"/>
       <x:c r="G32" s="37"/>
       <x:c r="H32" s="37"/>
@@ -2863,7 +2869,7 @@
       <x:c r="B33" s="37"/>
       <x:c r="C33" s="37"/>
       <x:c r="D33" s="37"/>
-      <x:c r="E33" s="42"/>
+      <x:c r="E33" s="43"/>
       <x:c r="F33" s="39"/>
       <x:c r="G33" s="37"/>
       <x:c r="H33" s="37"/>
@@ -2876,7 +2882,7 @@
       <x:c r="B34" s="37"/>
       <x:c r="C34" s="37"/>
       <x:c r="D34" s="37"/>
-      <x:c r="E34" s="42"/>
+      <x:c r="E34" s="43"/>
       <x:c r="F34" s="39"/>
       <x:c r="G34" s="37"/>
       <x:c r="H34" s="37"/>
@@ -2889,7 +2895,7 @@
       <x:c r="B35" s="37"/>
       <x:c r="C35" s="37"/>
       <x:c r="D35" s="37"/>
-      <x:c r="E35" s="42"/>
+      <x:c r="E35" s="43"/>
       <x:c r="F35" s="39"/>
       <x:c r="G35" s="37"/>
       <x:c r="H35" s="37"/>
@@ -2902,7 +2908,7 @@
       <x:c r="B36" s="37"/>
       <x:c r="C36" s="37"/>
       <x:c r="D36" s="37"/>
-      <x:c r="E36" s="42"/>
+      <x:c r="E36" s="43"/>
       <x:c r="F36" s="39"/>
       <x:c r="G36" s="37"/>
       <x:c r="H36" s="37"/>
@@ -2915,7 +2921,7 @@
       <x:c r="B37" s="37"/>
       <x:c r="C37" s="37"/>
       <x:c r="D37" s="37"/>
-      <x:c r="E37" s="42"/>
+      <x:c r="E37" s="43"/>
       <x:c r="F37" s="39"/>
       <x:c r="G37" s="37"/>
       <x:c r="H37" s="37"/>
@@ -2928,7 +2934,7 @@
       <x:c r="B38" s="37"/>
       <x:c r="C38" s="37"/>
       <x:c r="D38" s="37"/>
-      <x:c r="E38" s="42"/>
+      <x:c r="E38" s="43"/>
       <x:c r="F38" s="39"/>
       <x:c r="G38" s="37"/>
       <x:c r="H38" s="37"/>
@@ -2941,7 +2947,7 @@
       <x:c r="B39" s="37"/>
       <x:c r="C39" s="37"/>
       <x:c r="D39" s="37"/>
-      <x:c r="E39" s="42"/>
+      <x:c r="E39" s="43"/>
       <x:c r="F39" s="39"/>
       <x:c r="G39" s="37"/>
       <x:c r="H39" s="37"/>
@@ -2954,7 +2960,7 @@
       <x:c r="B40" s="37"/>
       <x:c r="C40" s="37"/>
       <x:c r="D40" s="37"/>
-      <x:c r="E40" s="42"/>
+      <x:c r="E40" s="43"/>
       <x:c r="F40" s="39"/>
       <x:c r="G40" s="37"/>
       <x:c r="H40" s="37"/>
@@ -2967,7 +2973,7 @@
       <x:c r="B41" s="37"/>
       <x:c r="C41" s="37"/>
       <x:c r="D41" s="37"/>
-      <x:c r="E41" s="42"/>
+      <x:c r="E41" s="43"/>
       <x:c r="F41" s="39"/>
       <x:c r="G41" s="37"/>
       <x:c r="H41" s="37"/>
@@ -2980,7 +2986,7 @@
       <x:c r="B42" s="37"/>
       <x:c r="C42" s="37"/>
       <x:c r="D42" s="37"/>
-      <x:c r="E42" s="42"/>
+      <x:c r="E42" s="43"/>
       <x:c r="F42" s="39"/>
       <x:c r="G42" s="37"/>
       <x:c r="H42" s="37"/>
@@ -2993,7 +2999,7 @@
       <x:c r="B43" s="37"/>
       <x:c r="C43" s="37"/>
       <x:c r="D43" s="37"/>
-      <x:c r="E43" s="42"/>
+      <x:c r="E43" s="43"/>
       <x:c r="F43" s="39"/>
       <x:c r="G43" s="37"/>
       <x:c r="H43" s="37"/>
@@ -3006,7 +3012,7 @@
       <x:c r="B44" s="37"/>
       <x:c r="C44" s="37"/>
       <x:c r="D44" s="37"/>
-      <x:c r="E44" s="42"/>
+      <x:c r="E44" s="43"/>
       <x:c r="F44" s="39"/>
       <x:c r="G44" s="37"/>
       <x:c r="H44" s="37"/>
@@ -3019,7 +3025,7 @@
       <x:c r="B45" s="37"/>
       <x:c r="C45" s="37"/>
       <x:c r="D45" s="37"/>
-      <x:c r="E45" s="42"/>
+      <x:c r="E45" s="43"/>
       <x:c r="F45" s="39"/>
       <x:c r="G45" s="37"/>
       <x:c r="H45" s="37"/>
@@ -3032,7 +3038,7 @@
       <x:c r="B46" s="37"/>
       <x:c r="C46" s="37"/>
       <x:c r="D46" s="37"/>
-      <x:c r="E46" s="42"/>
+      <x:c r="E46" s="43"/>
       <x:c r="F46" s="39"/>
       <x:c r="G46" s="37"/>
       <x:c r="H46" s="37"/>
@@ -3045,7 +3051,7 @@
       <x:c r="B47" s="37"/>
       <x:c r="C47" s="37"/>
       <x:c r="D47" s="37"/>
-      <x:c r="E47" s="42"/>
+      <x:c r="E47" s="43"/>
       <x:c r="F47" s="39"/>
       <x:c r="G47" s="37"/>
       <x:c r="H47" s="37"/>
@@ -3058,7 +3064,7 @@
       <x:c r="B48" s="37"/>
       <x:c r="C48" s="37"/>
       <x:c r="D48" s="37"/>
-      <x:c r="E48" s="42"/>
+      <x:c r="E48" s="43"/>
       <x:c r="F48" s="39"/>
       <x:c r="G48" s="37"/>
       <x:c r="H48" s="37"/>
@@ -3071,7 +3077,7 @@
       <x:c r="B49" s="37"/>
       <x:c r="C49" s="37"/>
       <x:c r="D49" s="37"/>
-      <x:c r="E49" s="42"/>
+      <x:c r="E49" s="43"/>
       <x:c r="F49" s="39"/>
       <x:c r="G49" s="37"/>
       <x:c r="H49" s="37"/>
@@ -3084,7 +3090,7 @@
       <x:c r="B50" s="37"/>
       <x:c r="C50" s="37"/>
       <x:c r="D50" s="37"/>
-      <x:c r="E50" s="42"/>
+      <x:c r="E50" s="43"/>
       <x:c r="F50" s="39"/>
       <x:c r="G50" s="37"/>
       <x:c r="H50" s="37"/>
@@ -3097,7 +3103,7 @@
       <x:c r="B51" s="37"/>
       <x:c r="C51" s="37"/>
       <x:c r="D51" s="37"/>
-      <x:c r="E51" s="42"/>
+      <x:c r="E51" s="43"/>
       <x:c r="F51" s="39"/>
       <x:c r="G51" s="37"/>
       <x:c r="H51" s="37"/>
@@ -3110,7 +3116,7 @@
       <x:c r="B52" s="37"/>
       <x:c r="C52" s="37"/>
       <x:c r="D52" s="37"/>
-      <x:c r="E52" s="42"/>
+      <x:c r="E52" s="43"/>
       <x:c r="F52" s="39"/>
       <x:c r="G52" s="37"/>
       <x:c r="H52" s="37"/>
@@ -3123,7 +3129,7 @@
       <x:c r="B53" s="37"/>
       <x:c r="C53" s="37"/>
       <x:c r="D53" s="37"/>
-      <x:c r="E53" s="42"/>
+      <x:c r="E53" s="43"/>
       <x:c r="F53" s="39"/>
       <x:c r="G53" s="37"/>
       <x:c r="H53" s="37"/>
@@ -3136,7 +3142,7 @@
       <x:c r="B54" s="37"/>
       <x:c r="C54" s="37"/>
       <x:c r="D54" s="37"/>
-      <x:c r="E54" s="42"/>
+      <x:c r="E54" s="43"/>
       <x:c r="F54" s="39"/>
       <x:c r="G54" s="37"/>
       <x:c r="H54" s="37"/>
@@ -3149,7 +3155,7 @@
       <x:c r="B55" s="37"/>
       <x:c r="C55" s="37"/>
       <x:c r="D55" s="37"/>
-      <x:c r="E55" s="42"/>
+      <x:c r="E55" s="43"/>
       <x:c r="F55" s="39"/>
       <x:c r="G55" s="37"/>
       <x:c r="H55" s="37"/>
@@ -3162,7 +3168,7 @@
       <x:c r="B56" s="37"/>
       <x:c r="C56" s="37"/>
       <x:c r="D56" s="37"/>
-      <x:c r="E56" s="42"/>
+      <x:c r="E56" s="43"/>
       <x:c r="F56" s="39"/>
       <x:c r="G56" s="37"/>
       <x:c r="H56" s="37"/>
@@ -3175,7 +3181,7 @@
       <x:c r="B57" s="37"/>
       <x:c r="C57" s="37"/>
       <x:c r="D57" s="37"/>
-      <x:c r="E57" s="42"/>
+      <x:c r="E57" s="43"/>
       <x:c r="F57" s="39"/>
       <x:c r="G57" s="37"/>
       <x:c r="H57" s="37"/>
@@ -3188,7 +3194,7 @@
       <x:c r="B58" s="37"/>
       <x:c r="C58" s="37"/>
       <x:c r="D58" s="37"/>
-      <x:c r="E58" s="42"/>
+      <x:c r="E58" s="43"/>
       <x:c r="F58" s="39"/>
       <x:c r="G58" s="37"/>
       <x:c r="H58" s="37"/>
@@ -3201,7 +3207,7 @@
       <x:c r="B59" s="37"/>
       <x:c r="C59" s="37"/>
       <x:c r="D59" s="37"/>
-      <x:c r="E59" s="42"/>
+      <x:c r="E59" s="43"/>
       <x:c r="F59" s="39"/>
       <x:c r="G59" s="37"/>
       <x:c r="H59" s="37"/>
@@ -3214,7 +3220,7 @@
       <x:c r="B60" s="37"/>
       <x:c r="C60" s="37"/>
       <x:c r="D60" s="37"/>
-      <x:c r="E60" s="42"/>
+      <x:c r="E60" s="43"/>
       <x:c r="F60" s="39"/>
       <x:c r="G60" s="37"/>
       <x:c r="H60" s="37"/>
@@ -3227,7 +3233,7 @@
       <x:c r="B61" s="37"/>
       <x:c r="C61" s="37"/>
       <x:c r="D61" s="37"/>
-      <x:c r="E61" s="42"/>
+      <x:c r="E61" s="43"/>
       <x:c r="F61" s="39"/>
       <x:c r="G61" s="37"/>
       <x:c r="H61" s="37"/>
@@ -3240,7 +3246,7 @@
       <x:c r="B62" s="37"/>
       <x:c r="C62" s="37"/>
       <x:c r="D62" s="37"/>
-      <x:c r="E62" s="42"/>
+      <x:c r="E62" s="43"/>
       <x:c r="F62" s="39"/>
       <x:c r="G62" s="37"/>
       <x:c r="H62" s="37"/>
@@ -3253,7 +3259,7 @@
       <x:c r="B63" s="37"/>
       <x:c r="C63" s="37"/>
       <x:c r="D63" s="37"/>
-      <x:c r="E63" s="42"/>
+      <x:c r="E63" s="43"/>
       <x:c r="F63" s="39"/>
       <x:c r="G63" s="37"/>
       <x:c r="H63" s="37"/>
@@ -3266,7 +3272,7 @@
       <x:c r="B64" s="37"/>
       <x:c r="C64" s="37"/>
       <x:c r="D64" s="37"/>
-      <x:c r="E64" s="42"/>
+      <x:c r="E64" s="43"/>
       <x:c r="F64" s="39"/>
       <x:c r="G64" s="37"/>
       <x:c r="H64" s="37"/>
@@ -3279,7 +3285,7 @@
       <x:c r="B65" s="37"/>
       <x:c r="C65" s="37"/>
       <x:c r="D65" s="37"/>
-      <x:c r="E65" s="42"/>
+      <x:c r="E65" s="43"/>
       <x:c r="F65" s="39"/>
       <x:c r="G65" s="37"/>
       <x:c r="H65" s="37"/>
@@ -3292,7 +3298,7 @@
       <x:c r="B66" s="37"/>
       <x:c r="C66" s="37"/>
       <x:c r="D66" s="37"/>
-      <x:c r="E66" s="42"/>
+      <x:c r="E66" s="43"/>
       <x:c r="F66" s="39"/>
       <x:c r="G66" s="37"/>
       <x:c r="H66" s="37"/>
@@ -3305,7 +3311,7 @@
       <x:c r="B67" s="37"/>
       <x:c r="C67" s="37"/>
       <x:c r="D67" s="37"/>
-      <x:c r="E67" s="42"/>
+      <x:c r="E67" s="43"/>
       <x:c r="F67" s="39"/>
       <x:c r="G67" s="37"/>
       <x:c r="H67" s="37"/>
@@ -3318,7 +3324,7 @@
       <x:c r="B68" s="37"/>
       <x:c r="C68" s="37"/>
       <x:c r="D68" s="37"/>
-      <x:c r="E68" s="42"/>
+      <x:c r="E68" s="43"/>
       <x:c r="F68" s="39"/>
       <x:c r="G68" s="37"/>
       <x:c r="H68" s="37"/>
@@ -3331,7 +3337,7 @@
       <x:c r="B69" s="37"/>
       <x:c r="C69" s="37"/>
       <x:c r="D69" s="37"/>
-      <x:c r="E69" s="42"/>
+      <x:c r="E69" s="43"/>
       <x:c r="F69" s="39"/>
       <x:c r="G69" s="37"/>
       <x:c r="H69" s="37"/>
@@ -3344,7 +3350,7 @@
       <x:c r="B70" s="37"/>
       <x:c r="C70" s="37"/>
       <x:c r="D70" s="37"/>
-      <x:c r="E70" s="42"/>
+      <x:c r="E70" s="43"/>
       <x:c r="F70" s="39"/>
       <x:c r="G70" s="37"/>
       <x:c r="H70" s="37"/>
@@ -3357,7 +3363,7 @@
       <x:c r="B71" s="37"/>
       <x:c r="C71" s="37"/>
       <x:c r="D71" s="37"/>
-      <x:c r="E71" s="42"/>
+      <x:c r="E71" s="43"/>
       <x:c r="F71" s="39"/>
       <x:c r="G71" s="37"/>
       <x:c r="H71" s="37"/>
@@ -3370,7 +3376,7 @@
       <x:c r="B72" s="37"/>
       <x:c r="C72" s="37"/>
       <x:c r="D72" s="37"/>
-      <x:c r="E72" s="42"/>
+      <x:c r="E72" s="43"/>
       <x:c r="F72" s="39"/>
       <x:c r="G72" s="37"/>
       <x:c r="H72" s="37"/>
@@ -3383,7 +3389,7 @@
       <x:c r="B73" s="37"/>
       <x:c r="C73" s="37"/>
       <x:c r="D73" s="37"/>
-      <x:c r="E73" s="42"/>
+      <x:c r="E73" s="43"/>
       <x:c r="F73" s="39"/>
       <x:c r="G73" s="37"/>
       <x:c r="H73" s="37"/>
@@ -3396,7 +3402,7 @@
       <x:c r="B74" s="37"/>
       <x:c r="C74" s="37"/>
       <x:c r="D74" s="37"/>
-      <x:c r="E74" s="42"/>
+      <x:c r="E74" s="43"/>
       <x:c r="F74" s="39"/>
       <x:c r="G74" s="37"/>
       <x:c r="H74" s="37"/>
@@ -3409,7 +3415,7 @@
       <x:c r="B75" s="37"/>
       <x:c r="C75" s="37"/>
       <x:c r="D75" s="37"/>
-      <x:c r="E75" s="42"/>
+      <x:c r="E75" s="43"/>
       <x:c r="F75" s="39"/>
       <x:c r="G75" s="37"/>
       <x:c r="H75" s="37"/>
@@ -3422,7 +3428,7 @@
       <x:c r="B76" s="37"/>
       <x:c r="C76" s="37"/>
       <x:c r="D76" s="37"/>
-      <x:c r="E76" s="42"/>
+      <x:c r="E76" s="43"/>
       <x:c r="F76" s="39"/>
       <x:c r="G76" s="37"/>
       <x:c r="H76" s="37"/>
@@ -3435,7 +3441,7 @@
       <x:c r="B77" s="37"/>
       <x:c r="C77" s="37"/>
       <x:c r="D77" s="37"/>
-      <x:c r="E77" s="42"/>
+      <x:c r="E77" s="43"/>
       <x:c r="F77" s="39"/>
       <x:c r="G77" s="37"/>
       <x:c r="H77" s="37"/>
@@ -3448,7 +3454,7 @@
       <x:c r="B78" s="37"/>
       <x:c r="C78" s="37"/>
       <x:c r="D78" s="37"/>
-      <x:c r="E78" s="42"/>
+      <x:c r="E78" s="43"/>
       <x:c r="F78" s="39"/>
       <x:c r="G78" s="37"/>
       <x:c r="H78" s="37"/>
@@ -3461,7 +3467,7 @@
       <x:c r="B79" s="37"/>
       <x:c r="C79" s="37"/>
       <x:c r="D79" s="37"/>
-      <x:c r="E79" s="42"/>
+      <x:c r="E79" s="43"/>
       <x:c r="F79" s="39"/>
       <x:c r="G79" s="37"/>
       <x:c r="H79" s="37"/>
@@ -3474,7 +3480,7 @@
       <x:c r="B80" s="37"/>
       <x:c r="C80" s="37"/>
       <x:c r="D80" s="37"/>
-      <x:c r="E80" s="42"/>
+      <x:c r="E80" s="43"/>
       <x:c r="F80" s="39"/>
       <x:c r="G80" s="37"/>
       <x:c r="H80" s="37"/>
@@ -3487,7 +3493,7 @@
       <x:c r="B81" s="37"/>
       <x:c r="C81" s="37"/>
       <x:c r="D81" s="37"/>
-      <x:c r="E81" s="42"/>
+      <x:c r="E81" s="43"/>
       <x:c r="F81" s="39"/>
       <x:c r="G81" s="37"/>
       <x:c r="H81" s="37"/>
@@ -3500,7 +3506,7 @@
       <x:c r="B82" s="37"/>
       <x:c r="C82" s="37"/>
       <x:c r="D82" s="37"/>
-      <x:c r="E82" s="42"/>
+      <x:c r="E82" s="43"/>
       <x:c r="F82" s="39"/>
       <x:c r="G82" s="37"/>
       <x:c r="H82" s="37"/>
@@ -3513,7 +3519,7 @@
       <x:c r="B83" s="37"/>
       <x:c r="C83" s="37"/>
       <x:c r="D83" s="37"/>
-      <x:c r="E83" s="42"/>
+      <x:c r="E83" s="43"/>
       <x:c r="F83" s="39"/>
       <x:c r="G83" s="37"/>
       <x:c r="H83" s="37"/>
@@ -3526,7 +3532,7 @@
       <x:c r="B84" s="37"/>
       <x:c r="C84" s="37"/>
       <x:c r="D84" s="37"/>
-      <x:c r="E84" s="42"/>
+      <x:c r="E84" s="43"/>
       <x:c r="F84" s="39"/>
       <x:c r="G84" s="37"/>
       <x:c r="H84" s="37"/>
@@ -3539,7 +3545,7 @@
       <x:c r="B85" s="37"/>
       <x:c r="C85" s="37"/>
       <x:c r="D85" s="37"/>
-      <x:c r="E85" s="42"/>
+      <x:c r="E85" s="43"/>
       <x:c r="F85" s="39"/>
       <x:c r="G85" s="37"/>
       <x:c r="H85" s="37"/>
@@ -3552,7 +3558,7 @@
       <x:c r="B86" s="37"/>
       <x:c r="C86" s="37"/>
       <x:c r="D86" s="37"/>
-      <x:c r="E86" s="42"/>
+      <x:c r="E86" s="43"/>
       <x:c r="F86" s="39"/>
       <x:c r="G86" s="37"/>
       <x:c r="H86" s="37"/>
@@ -3565,7 +3571,7 @@
       <x:c r="B87" s="37"/>
       <x:c r="C87" s="37"/>
       <x:c r="D87" s="37"/>
-      <x:c r="E87" s="42"/>
+      <x:c r="E87" s="43"/>
       <x:c r="F87" s="39"/>
       <x:c r="G87" s="37"/>
       <x:c r="H87" s="37"/>
@@ -3578,7 +3584,7 @@
       <x:c r="B88" s="37"/>
       <x:c r="C88" s="37"/>
       <x:c r="D88" s="37"/>
-      <x:c r="E88" s="42"/>
+      <x:c r="E88" s="43"/>
       <x:c r="F88" s="39"/>
       <x:c r="G88" s="37"/>
       <x:c r="H88" s="37"/>
@@ -3591,7 +3597,7 @@
       <x:c r="B89" s="37"/>
       <x:c r="C89" s="37"/>
       <x:c r="D89" s="37"/>
-      <x:c r="E89" s="42"/>
+      <x:c r="E89" s="43"/>
       <x:c r="F89" s="39"/>
       <x:c r="G89" s="37"/>
       <x:c r="H89" s="37"/>
@@ -3604,7 +3610,7 @@
       <x:c r="B90" s="37"/>
       <x:c r="C90" s="37"/>
       <x:c r="D90" s="37"/>
-      <x:c r="E90" s="42"/>
+      <x:c r="E90" s="43"/>
       <x:c r="F90" s="39"/>
       <x:c r="G90" s="37"/>
       <x:c r="H90" s="37"/>
@@ -3617,7 +3623,7 @@
       <x:c r="B91" s="37"/>
       <x:c r="C91" s="37"/>
       <x:c r="D91" s="37"/>
-      <x:c r="E91" s="42"/>
+      <x:c r="E91" s="43"/>
       <x:c r="F91" s="39"/>
       <x:c r="G91" s="37"/>
       <x:c r="H91" s="37"/>
@@ -3630,7 +3636,7 @@
       <x:c r="B92" s="37"/>
       <x:c r="C92" s="37"/>
       <x:c r="D92" s="37"/>
-      <x:c r="E92" s="42"/>
+      <x:c r="E92" s="43"/>
       <x:c r="F92" s="39"/>
       <x:c r="G92" s="37"/>
       <x:c r="H92" s="37"/>
@@ -3643,7 +3649,7 @@
       <x:c r="B93" s="37"/>
       <x:c r="C93" s="37"/>
       <x:c r="D93" s="37"/>
-      <x:c r="E93" s="42"/>
+      <x:c r="E93" s="43"/>
       <x:c r="F93" s="39"/>
       <x:c r="G93" s="37"/>
       <x:c r="H93" s="37"/>
@@ -3656,7 +3662,7 @@
       <x:c r="B94" s="37"/>
       <x:c r="C94" s="37"/>
       <x:c r="D94" s="37"/>
-      <x:c r="E94" s="42"/>
+      <x:c r="E94" s="43"/>
       <x:c r="F94" s="39"/>
       <x:c r="G94" s="37"/>
       <x:c r="H94" s="37"/>
@@ -3669,7 +3675,7 @@
       <x:c r="B95" s="37"/>
       <x:c r="C95" s="37"/>
       <x:c r="D95" s="37"/>
-      <x:c r="E95" s="42"/>
+      <x:c r="E95" s="43"/>
       <x:c r="F95" s="39"/>
       <x:c r="G95" s="37"/>
       <x:c r="H95" s="37"/>
@@ -3682,7 +3688,7 @@
       <x:c r="B96" s="37"/>
       <x:c r="C96" s="37"/>
       <x:c r="D96" s="37"/>
-      <x:c r="E96" s="42"/>
+      <x:c r="E96" s="43"/>
       <x:c r="F96" s="39"/>
       <x:c r="G96" s="37"/>
       <x:c r="H96" s="37"/>
@@ -3695,7 +3701,7 @@
       <x:c r="B97" s="37"/>
       <x:c r="C97" s="37"/>
       <x:c r="D97" s="37"/>
-      <x:c r="E97" s="42"/>
+      <x:c r="E97" s="43"/>
       <x:c r="F97" s="39"/>
       <x:c r="G97" s="37"/>
       <x:c r="H97" s="37"/>
@@ -3708,7 +3714,7 @@
       <x:c r="B98" s="37"/>
       <x:c r="C98" s="37"/>
       <x:c r="D98" s="37"/>
-      <x:c r="E98" s="42"/>
+      <x:c r="E98" s="43"/>
       <x:c r="F98" s="39"/>
       <x:c r="G98" s="37"/>
       <x:c r="H98" s="37"/>
@@ -3721,7 +3727,7 @@
       <x:c r="B99" s="37"/>
       <x:c r="C99" s="37"/>
       <x:c r="D99" s="37"/>
-      <x:c r="E99" s="42"/>
+      <x:c r="E99" s="43"/>
       <x:c r="F99" s="39"/>
       <x:c r="G99" s="37"/>
       <x:c r="H99" s="37"/>
@@ -3734,7 +3740,7 @@
       <x:c r="B100" s="37"/>
       <x:c r="C100" s="37"/>
       <x:c r="D100" s="37"/>
-      <x:c r="E100" s="42"/>
+      <x:c r="E100" s="43"/>
       <x:c r="F100" s="39"/>
       <x:c r="G100" s="37"/>
       <x:c r="H100" s="37"/>
@@ -3747,7 +3753,7 @@
       <x:c r="B101" s="37"/>
       <x:c r="C101" s="37"/>
       <x:c r="D101" s="37"/>
-      <x:c r="E101" s="42"/>
+      <x:c r="E101" s="43"/>
       <x:c r="F101" s="39"/>
       <x:c r="G101" s="37"/>
       <x:c r="H101" s="37"/>
@@ -3760,7 +3766,7 @@
       <x:c r="B102" s="37"/>
       <x:c r="C102" s="37"/>
       <x:c r="D102" s="37"/>
-      <x:c r="E102" s="42"/>
+      <x:c r="E102" s="43"/>
       <x:c r="F102" s="39"/>
       <x:c r="G102" s="37"/>
       <x:c r="H102" s="37"/>
@@ -3773,7 +3779,7 @@
       <x:c r="B103" s="37"/>
       <x:c r="C103" s="37"/>
       <x:c r="D103" s="37"/>
-      <x:c r="E103" s="42"/>
+      <x:c r="E103" s="43"/>
       <x:c r="F103" s="39"/>
       <x:c r="G103" s="37"/>
       <x:c r="H103" s="37"/>
@@ -3786,7 +3792,7 @@
       <x:c r="B104" s="37"/>
       <x:c r="C104" s="37"/>
       <x:c r="D104" s="37"/>
-      <x:c r="E104" s="42"/>
+      <x:c r="E104" s="43"/>
       <x:c r="F104" s="39"/>
       <x:c r="G104" s="37"/>
       <x:c r="H104" s="37"/>
@@ -3810,7 +3816,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce9a9bc384f349f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43777fdbb2c34600"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3983,7 +3989,7 @@
       <x:c r="B5" s="37"/>
       <x:c r="C5" s="37"/>
       <x:c r="D5" s="39"/>
-      <x:c r="E5" s="42"/>
+      <x:c r="E5" s="43"/>
       <x:c r="F5" s="37"/>
       <x:c r="G5" s="37"/>
       <x:c r="H5" s="37"/>
@@ -3992,9 +3998,9 @@
       <x:c r="K5" s="37"/>
       <x:c r="L5" s="37"/>
       <x:c r="M5" s="37"/>
-      <x:c r="N5" s="42"/>
+      <x:c r="N5" s="43"/>
       <x:c r="O5" s="37"/>
-      <x:c r="P5" s="42"/>
+      <x:c r="P5" s="43"/>
       <x:c r="Q5" s="37"/>
       <x:c r="R5" s="38"/>
       <x:c r="S5" s="38"/>
@@ -4005,7 +4011,7 @@
       <x:c r="B6" s="37"/>
       <x:c r="C6" s="37"/>
       <x:c r="D6" s="39"/>
-      <x:c r="E6" s="42"/>
+      <x:c r="E6" s="43"/>
       <x:c r="F6" s="37"/>
       <x:c r="G6" s="37"/>
       <x:c r="H6" s="37"/>
@@ -4014,9 +4020,9 @@
       <x:c r="K6" s="37"/>
       <x:c r="L6" s="37"/>
       <x:c r="M6" s="37"/>
-      <x:c r="N6" s="42"/>
+      <x:c r="N6" s="43"/>
       <x:c r="O6" s="37"/>
-      <x:c r="P6" s="42"/>
+      <x:c r="P6" s="43"/>
       <x:c r="Q6" s="37"/>
       <x:c r="R6" s="38"/>
       <x:c r="S6" s="38"/>
@@ -4027,7 +4033,7 @@
       <x:c r="B7" s="37"/>
       <x:c r="C7" s="37"/>
       <x:c r="D7" s="39"/>
-      <x:c r="E7" s="42"/>
+      <x:c r="E7" s="43"/>
       <x:c r="F7" s="37"/>
       <x:c r="G7" s="37"/>
       <x:c r="H7" s="37"/>
@@ -4036,9 +4042,9 @@
       <x:c r="K7" s="37"/>
       <x:c r="L7" s="37"/>
       <x:c r="M7" s="37"/>
-      <x:c r="N7" s="42"/>
+      <x:c r="N7" s="43"/>
       <x:c r="O7" s="37"/>
-      <x:c r="P7" s="42"/>
+      <x:c r="P7" s="43"/>
       <x:c r="Q7" s="37"/>
       <x:c r="R7" s="38"/>
       <x:c r="S7" s="38"/>
@@ -4049,7 +4055,7 @@
       <x:c r="B8" s="37"/>
       <x:c r="C8" s="37"/>
       <x:c r="D8" s="39"/>
-      <x:c r="E8" s="42"/>
+      <x:c r="E8" s="43"/>
       <x:c r="F8" s="37"/>
       <x:c r="G8" s="37"/>
       <x:c r="H8" s="37"/>
@@ -4058,9 +4064,9 @@
       <x:c r="K8" s="37"/>
       <x:c r="L8" s="37"/>
       <x:c r="M8" s="37"/>
-      <x:c r="N8" s="42"/>
+      <x:c r="N8" s="43"/>
       <x:c r="O8" s="37"/>
-      <x:c r="P8" s="42"/>
+      <x:c r="P8" s="43"/>
       <x:c r="Q8" s="37"/>
       <x:c r="R8" s="38"/>
       <x:c r="S8" s="38"/>
@@ -4071,7 +4077,7 @@
       <x:c r="B9" s="37"/>
       <x:c r="C9" s="37"/>
       <x:c r="D9" s="39"/>
-      <x:c r="E9" s="42"/>
+      <x:c r="E9" s="43"/>
       <x:c r="F9" s="37"/>
       <x:c r="G9" s="37"/>
       <x:c r="H9" s="37"/>
@@ -4080,9 +4086,9 @@
       <x:c r="K9" s="37"/>
       <x:c r="L9" s="37"/>
       <x:c r="M9" s="37"/>
-      <x:c r="N9" s="42"/>
+      <x:c r="N9" s="43"/>
       <x:c r="O9" s="37"/>
-      <x:c r="P9" s="42"/>
+      <x:c r="P9" s="43"/>
       <x:c r="Q9" s="37"/>
       <x:c r="R9" s="38"/>
       <x:c r="S9" s="38"/>
@@ -4093,7 +4099,7 @@
       <x:c r="B10" s="37"/>
       <x:c r="C10" s="37"/>
       <x:c r="D10" s="39"/>
-      <x:c r="E10" s="42"/>
+      <x:c r="E10" s="43"/>
       <x:c r="F10" s="37"/>
       <x:c r="G10" s="37"/>
       <x:c r="H10" s="37"/>
@@ -4102,9 +4108,9 @@
       <x:c r="K10" s="37"/>
       <x:c r="L10" s="37"/>
       <x:c r="M10" s="37"/>
-      <x:c r="N10" s="42"/>
+      <x:c r="N10" s="43"/>
       <x:c r="O10" s="37"/>
-      <x:c r="P10" s="42"/>
+      <x:c r="P10" s="43"/>
       <x:c r="Q10" s="37"/>
       <x:c r="R10" s="38"/>
       <x:c r="S10" s="38"/>
@@ -4115,7 +4121,7 @@
       <x:c r="B11" s="37"/>
       <x:c r="C11" s="37"/>
       <x:c r="D11" s="39"/>
-      <x:c r="E11" s="42"/>
+      <x:c r="E11" s="43"/>
       <x:c r="F11" s="37"/>
       <x:c r="G11" s="37"/>
       <x:c r="H11" s="37"/>
@@ -4124,9 +4130,9 @@
       <x:c r="K11" s="37"/>
       <x:c r="L11" s="37"/>
       <x:c r="M11" s="37"/>
-      <x:c r="N11" s="42"/>
+      <x:c r="N11" s="43"/>
       <x:c r="O11" s="37"/>
-      <x:c r="P11" s="42"/>
+      <x:c r="P11" s="43"/>
       <x:c r="Q11" s="37"/>
       <x:c r="R11" s="38"/>
       <x:c r="S11" s="38"/>
@@ -4137,7 +4143,7 @@
       <x:c r="B12" s="37"/>
       <x:c r="C12" s="37"/>
       <x:c r="D12" s="39"/>
-      <x:c r="E12" s="42"/>
+      <x:c r="E12" s="43"/>
       <x:c r="F12" s="37"/>
       <x:c r="G12" s="37"/>
       <x:c r="H12" s="37"/>
@@ -4146,9 +4152,9 @@
       <x:c r="K12" s="37"/>
       <x:c r="L12" s="37"/>
       <x:c r="M12" s="37"/>
-      <x:c r="N12" s="42"/>
+      <x:c r="N12" s="43"/>
       <x:c r="O12" s="37"/>
-      <x:c r="P12" s="42"/>
+      <x:c r="P12" s="43"/>
       <x:c r="Q12" s="37"/>
       <x:c r="R12" s="38"/>
       <x:c r="S12" s="38"/>
@@ -4159,7 +4165,7 @@
       <x:c r="B13" s="37"/>
       <x:c r="C13" s="37"/>
       <x:c r="D13" s="39"/>
-      <x:c r="E13" s="42"/>
+      <x:c r="E13" s="43"/>
       <x:c r="F13" s="37"/>
       <x:c r="G13" s="37"/>
       <x:c r="H13" s="37"/>
@@ -4168,9 +4174,9 @@
       <x:c r="K13" s="37"/>
       <x:c r="L13" s="37"/>
       <x:c r="M13" s="37"/>
-      <x:c r="N13" s="42"/>
+      <x:c r="N13" s="43"/>
       <x:c r="O13" s="37"/>
-      <x:c r="P13" s="42"/>
+      <x:c r="P13" s="43"/>
       <x:c r="Q13" s="37"/>
       <x:c r="R13" s="38"/>
       <x:c r="S13" s="38"/>
@@ -4181,7 +4187,7 @@
       <x:c r="B14" s="37"/>
       <x:c r="C14" s="37"/>
       <x:c r="D14" s="39"/>
-      <x:c r="E14" s="42"/>
+      <x:c r="E14" s="43"/>
       <x:c r="F14" s="37"/>
       <x:c r="G14" s="37"/>
       <x:c r="H14" s="37"/>
@@ -4190,9 +4196,9 @@
       <x:c r="K14" s="37"/>
       <x:c r="L14" s="37"/>
       <x:c r="M14" s="37"/>
-      <x:c r="N14" s="42"/>
+      <x:c r="N14" s="43"/>
       <x:c r="O14" s="37"/>
-      <x:c r="P14" s="42"/>
+      <x:c r="P14" s="43"/>
       <x:c r="Q14" s="37"/>
       <x:c r="R14" s="38"/>
       <x:c r="S14" s="38"/>
@@ -4203,7 +4209,7 @@
       <x:c r="B15" s="37"/>
       <x:c r="C15" s="37"/>
       <x:c r="D15" s="39"/>
-      <x:c r="E15" s="42"/>
+      <x:c r="E15" s="43"/>
       <x:c r="F15" s="37"/>
       <x:c r="G15" s="37"/>
       <x:c r="H15" s="37"/>
@@ -4212,9 +4218,9 @@
       <x:c r="K15" s="37"/>
       <x:c r="L15" s="37"/>
       <x:c r="M15" s="37"/>
-      <x:c r="N15" s="42"/>
+      <x:c r="N15" s="43"/>
       <x:c r="O15" s="37"/>
-      <x:c r="P15" s="42"/>
+      <x:c r="P15" s="43"/>
       <x:c r="Q15" s="37"/>
       <x:c r="R15" s="38"/>
       <x:c r="S15" s="38"/>
@@ -4225,7 +4231,7 @@
       <x:c r="B16" s="37"/>
       <x:c r="C16" s="37"/>
       <x:c r="D16" s="39"/>
-      <x:c r="E16" s="42"/>
+      <x:c r="E16" s="43"/>
       <x:c r="F16" s="37"/>
       <x:c r="G16" s="37"/>
       <x:c r="H16" s="37"/>
@@ -4234,9 +4240,9 @@
       <x:c r="K16" s="37"/>
       <x:c r="L16" s="37"/>
       <x:c r="M16" s="37"/>
-      <x:c r="N16" s="42"/>
+      <x:c r="N16" s="43"/>
       <x:c r="O16" s="37"/>
-      <x:c r="P16" s="42"/>
+      <x:c r="P16" s="43"/>
       <x:c r="Q16" s="37"/>
       <x:c r="R16" s="38"/>
       <x:c r="S16" s="38"/>
@@ -4247,7 +4253,7 @@
       <x:c r="B17" s="37"/>
       <x:c r="C17" s="37"/>
       <x:c r="D17" s="39"/>
-      <x:c r="E17" s="42"/>
+      <x:c r="E17" s="43"/>
       <x:c r="F17" s="37"/>
       <x:c r="G17" s="37"/>
       <x:c r="H17" s="37"/>
@@ -4256,9 +4262,9 @@
       <x:c r="K17" s="37"/>
       <x:c r="L17" s="37"/>
       <x:c r="M17" s="37"/>
-      <x:c r="N17" s="42"/>
+      <x:c r="N17" s="43"/>
       <x:c r="O17" s="37"/>
-      <x:c r="P17" s="42"/>
+      <x:c r="P17" s="43"/>
       <x:c r="Q17" s="37"/>
       <x:c r="R17" s="38"/>
       <x:c r="S17" s="38"/>
@@ -4269,7 +4275,7 @@
       <x:c r="B18" s="37"/>
       <x:c r="C18" s="37"/>
       <x:c r="D18" s="39"/>
-      <x:c r="E18" s="42"/>
+      <x:c r="E18" s="43"/>
       <x:c r="F18" s="37"/>
       <x:c r="G18" s="37"/>
       <x:c r="H18" s="37"/>
@@ -4278,9 +4284,9 @@
       <x:c r="K18" s="37"/>
       <x:c r="L18" s="37"/>
       <x:c r="M18" s="37"/>
-      <x:c r="N18" s="42"/>
+      <x:c r="N18" s="43"/>
       <x:c r="O18" s="37"/>
-      <x:c r="P18" s="42"/>
+      <x:c r="P18" s="43"/>
       <x:c r="Q18" s="37"/>
       <x:c r="R18" s="38"/>
       <x:c r="S18" s="38"/>
@@ -4291,7 +4297,7 @@
       <x:c r="B19" s="37"/>
       <x:c r="C19" s="37"/>
       <x:c r="D19" s="39"/>
-      <x:c r="E19" s="42"/>
+      <x:c r="E19" s="43"/>
       <x:c r="F19" s="37"/>
       <x:c r="G19" s="37"/>
       <x:c r="H19" s="37"/>
@@ -4300,9 +4306,9 @@
       <x:c r="K19" s="37"/>
       <x:c r="L19" s="37"/>
       <x:c r="M19" s="37"/>
-      <x:c r="N19" s="42"/>
+      <x:c r="N19" s="43"/>
       <x:c r="O19" s="37"/>
-      <x:c r="P19" s="42"/>
+      <x:c r="P19" s="43"/>
       <x:c r="Q19" s="37"/>
       <x:c r="R19" s="38"/>
       <x:c r="S19" s="38"/>
@@ -4313,7 +4319,7 @@
       <x:c r="B20" s="37"/>
       <x:c r="C20" s="37"/>
       <x:c r="D20" s="39"/>
-      <x:c r="E20" s="42"/>
+      <x:c r="E20" s="43"/>
       <x:c r="F20" s="37"/>
       <x:c r="G20" s="37"/>
       <x:c r="H20" s="37"/>
@@ -4322,9 +4328,9 @@
       <x:c r="K20" s="37"/>
       <x:c r="L20" s="37"/>
       <x:c r="M20" s="37"/>
-      <x:c r="N20" s="42"/>
+      <x:c r="N20" s="43"/>
       <x:c r="O20" s="37"/>
-      <x:c r="P20" s="42"/>
+      <x:c r="P20" s="43"/>
       <x:c r="Q20" s="37"/>
       <x:c r="R20" s="38"/>
       <x:c r="S20" s="38"/>
@@ -4335,7 +4341,7 @@
       <x:c r="B21" s="37"/>
       <x:c r="C21" s="37"/>
       <x:c r="D21" s="39"/>
-      <x:c r="E21" s="42"/>
+      <x:c r="E21" s="43"/>
       <x:c r="F21" s="37"/>
       <x:c r="G21" s="37"/>
       <x:c r="H21" s="37"/>
@@ -4344,9 +4350,9 @@
       <x:c r="K21" s="37"/>
       <x:c r="L21" s="37"/>
       <x:c r="M21" s="37"/>
-      <x:c r="N21" s="42"/>
+      <x:c r="N21" s="43"/>
       <x:c r="O21" s="37"/>
-      <x:c r="P21" s="42"/>
+      <x:c r="P21" s="43"/>
       <x:c r="Q21" s="37"/>
       <x:c r="R21" s="38"/>
       <x:c r="S21" s="38"/>
@@ -4357,7 +4363,7 @@
       <x:c r="B22" s="37"/>
       <x:c r="C22" s="37"/>
       <x:c r="D22" s="39"/>
-      <x:c r="E22" s="42"/>
+      <x:c r="E22" s="43"/>
       <x:c r="F22" s="37"/>
       <x:c r="G22" s="37"/>
       <x:c r="H22" s="37"/>
@@ -4366,9 +4372,9 @@
       <x:c r="K22" s="37"/>
       <x:c r="L22" s="37"/>
       <x:c r="M22" s="37"/>
-      <x:c r="N22" s="42"/>
+      <x:c r="N22" s="43"/>
       <x:c r="O22" s="37"/>
-      <x:c r="P22" s="42"/>
+      <x:c r="P22" s="43"/>
       <x:c r="Q22" s="37"/>
       <x:c r="R22" s="38"/>
       <x:c r="S22" s="38"/>
@@ -4379,7 +4385,7 @@
       <x:c r="B23" s="37"/>
       <x:c r="C23" s="37"/>
       <x:c r="D23" s="39"/>
-      <x:c r="E23" s="42"/>
+      <x:c r="E23" s="43"/>
       <x:c r="F23" s="37"/>
       <x:c r="G23" s="37"/>
       <x:c r="H23" s="37"/>
@@ -4388,9 +4394,9 @@
       <x:c r="K23" s="37"/>
       <x:c r="L23" s="37"/>
       <x:c r="M23" s="37"/>
-      <x:c r="N23" s="42"/>
+      <x:c r="N23" s="43"/>
       <x:c r="O23" s="37"/>
-      <x:c r="P23" s="42"/>
+      <x:c r="P23" s="43"/>
       <x:c r="Q23" s="37"/>
       <x:c r="R23" s="38"/>
       <x:c r="S23" s="38"/>
@@ -4401,7 +4407,7 @@
       <x:c r="B24" s="37"/>
       <x:c r="C24" s="37"/>
       <x:c r="D24" s="39"/>
-      <x:c r="E24" s="42"/>
+      <x:c r="E24" s="43"/>
       <x:c r="F24" s="37"/>
       <x:c r="G24" s="37"/>
       <x:c r="H24" s="37"/>
@@ -4410,9 +4416,9 @@
       <x:c r="K24" s="37"/>
       <x:c r="L24" s="37"/>
       <x:c r="M24" s="37"/>
-      <x:c r="N24" s="42"/>
+      <x:c r="N24" s="43"/>
       <x:c r="O24" s="37"/>
-      <x:c r="P24" s="42"/>
+      <x:c r="P24" s="43"/>
       <x:c r="Q24" s="37"/>
       <x:c r="R24" s="38"/>
       <x:c r="S24" s="38"/>
@@ -4423,7 +4429,7 @@
       <x:c r="B25" s="37"/>
       <x:c r="C25" s="37"/>
       <x:c r="D25" s="39"/>
-      <x:c r="E25" s="42"/>
+      <x:c r="E25" s="43"/>
       <x:c r="F25" s="37"/>
       <x:c r="G25" s="37"/>
       <x:c r="H25" s="37"/>
@@ -4432,9 +4438,9 @@
       <x:c r="K25" s="37"/>
       <x:c r="L25" s="37"/>
       <x:c r="M25" s="37"/>
-      <x:c r="N25" s="42"/>
+      <x:c r="N25" s="43"/>
       <x:c r="O25" s="37"/>
-      <x:c r="P25" s="42"/>
+      <x:c r="P25" s="43"/>
       <x:c r="Q25" s="37"/>
       <x:c r="R25" s="38"/>
       <x:c r="S25" s="38"/>
@@ -4445,7 +4451,7 @@
       <x:c r="B26" s="37"/>
       <x:c r="C26" s="37"/>
       <x:c r="D26" s="39"/>
-      <x:c r="E26" s="42"/>
+      <x:c r="E26" s="43"/>
       <x:c r="F26" s="37"/>
       <x:c r="G26" s="37"/>
       <x:c r="H26" s="37"/>
@@ -4454,9 +4460,9 @@
       <x:c r="K26" s="37"/>
       <x:c r="L26" s="37"/>
       <x:c r="M26" s="37"/>
-      <x:c r="N26" s="42"/>
+      <x:c r="N26" s="43"/>
       <x:c r="O26" s="37"/>
-      <x:c r="P26" s="42"/>
+      <x:c r="P26" s="43"/>
       <x:c r="Q26" s="37"/>
       <x:c r="R26" s="38"/>
       <x:c r="S26" s="38"/>
@@ -4467,7 +4473,7 @@
       <x:c r="B27" s="37"/>
       <x:c r="C27" s="37"/>
       <x:c r="D27" s="39"/>
-      <x:c r="E27" s="42"/>
+      <x:c r="E27" s="43"/>
       <x:c r="F27" s="37"/>
       <x:c r="G27" s="37"/>
       <x:c r="H27" s="37"/>
@@ -4476,9 +4482,9 @@
       <x:c r="K27" s="37"/>
       <x:c r="L27" s="37"/>
       <x:c r="M27" s="37"/>
-      <x:c r="N27" s="42"/>
+      <x:c r="N27" s="43"/>
       <x:c r="O27" s="37"/>
-      <x:c r="P27" s="42"/>
+      <x:c r="P27" s="43"/>
       <x:c r="Q27" s="37"/>
       <x:c r="R27" s="38"/>
       <x:c r="S27" s="38"/>
@@ -4489,7 +4495,7 @@
       <x:c r="B28" s="37"/>
       <x:c r="C28" s="37"/>
       <x:c r="D28" s="39"/>
-      <x:c r="E28" s="42"/>
+      <x:c r="E28" s="43"/>
       <x:c r="F28" s="37"/>
       <x:c r="G28" s="37"/>
       <x:c r="H28" s="37"/>
@@ -4498,9 +4504,9 @@
       <x:c r="K28" s="37"/>
       <x:c r="L28" s="37"/>
       <x:c r="M28" s="37"/>
-      <x:c r="N28" s="42"/>
+      <x:c r="N28" s="43"/>
       <x:c r="O28" s="37"/>
-      <x:c r="P28" s="42"/>
+      <x:c r="P28" s="43"/>
       <x:c r="Q28" s="37"/>
       <x:c r="R28" s="38"/>
       <x:c r="S28" s="38"/>
@@ -4511,7 +4517,7 @@
       <x:c r="B29" s="37"/>
       <x:c r="C29" s="37"/>
       <x:c r="D29" s="39"/>
-      <x:c r="E29" s="42"/>
+      <x:c r="E29" s="43"/>
       <x:c r="F29" s="37"/>
       <x:c r="G29" s="37"/>
       <x:c r="H29" s="37"/>
@@ -4520,9 +4526,9 @@
       <x:c r="K29" s="37"/>
       <x:c r="L29" s="37"/>
       <x:c r="M29" s="37"/>
-      <x:c r="N29" s="42"/>
+      <x:c r="N29" s="43"/>
       <x:c r="O29" s="37"/>
-      <x:c r="P29" s="42"/>
+      <x:c r="P29" s="43"/>
       <x:c r="Q29" s="37"/>
       <x:c r="R29" s="38"/>
       <x:c r="S29" s="38"/>
@@ -4533,7 +4539,7 @@
       <x:c r="B30" s="37"/>
       <x:c r="C30" s="37"/>
       <x:c r="D30" s="39"/>
-      <x:c r="E30" s="42"/>
+      <x:c r="E30" s="43"/>
       <x:c r="F30" s="37"/>
       <x:c r="G30" s="37"/>
       <x:c r="H30" s="37"/>
@@ -4542,9 +4548,9 @@
       <x:c r="K30" s="37"/>
       <x:c r="L30" s="37"/>
       <x:c r="M30" s="37"/>
-      <x:c r="N30" s="42"/>
+      <x:c r="N30" s="43"/>
       <x:c r="O30" s="37"/>
-      <x:c r="P30" s="42"/>
+      <x:c r="P30" s="43"/>
       <x:c r="Q30" s="37"/>
       <x:c r="R30" s="38"/>
       <x:c r="S30" s="38"/>
@@ -4555,7 +4561,7 @@
       <x:c r="B31" s="37"/>
       <x:c r="C31" s="37"/>
       <x:c r="D31" s="39"/>
-      <x:c r="E31" s="42"/>
+      <x:c r="E31" s="43"/>
       <x:c r="F31" s="37"/>
       <x:c r="G31" s="37"/>
       <x:c r="H31" s="37"/>
@@ -4564,9 +4570,9 @@
       <x:c r="K31" s="37"/>
       <x:c r="L31" s="37"/>
       <x:c r="M31" s="37"/>
-      <x:c r="N31" s="42"/>
+      <x:c r="N31" s="43"/>
       <x:c r="O31" s="37"/>
-      <x:c r="P31" s="42"/>
+      <x:c r="P31" s="43"/>
       <x:c r="Q31" s="37"/>
       <x:c r="R31" s="38"/>
       <x:c r="S31" s="38"/>
@@ -4577,7 +4583,7 @@
       <x:c r="B32" s="37"/>
       <x:c r="C32" s="37"/>
       <x:c r="D32" s="39"/>
-      <x:c r="E32" s="42"/>
+      <x:c r="E32" s="43"/>
       <x:c r="F32" s="37"/>
       <x:c r="G32" s="37"/>
       <x:c r="H32" s="37"/>
@@ -4586,9 +4592,9 @@
       <x:c r="K32" s="37"/>
       <x:c r="L32" s="37"/>
       <x:c r="M32" s="37"/>
-      <x:c r="N32" s="42"/>
+      <x:c r="N32" s="43"/>
       <x:c r="O32" s="37"/>
-      <x:c r="P32" s="42"/>
+      <x:c r="P32" s="43"/>
       <x:c r="Q32" s="37"/>
       <x:c r="R32" s="38"/>
       <x:c r="S32" s="38"/>
@@ -4599,7 +4605,7 @@
       <x:c r="B33" s="37"/>
       <x:c r="C33" s="37"/>
       <x:c r="D33" s="39"/>
-      <x:c r="E33" s="42"/>
+      <x:c r="E33" s="43"/>
       <x:c r="F33" s="37"/>
       <x:c r="G33" s="37"/>
       <x:c r="H33" s="37"/>
@@ -4608,9 +4614,9 @@
       <x:c r="K33" s="37"/>
       <x:c r="L33" s="37"/>
       <x:c r="M33" s="37"/>
-      <x:c r="N33" s="42"/>
+      <x:c r="N33" s="43"/>
       <x:c r="O33" s="37"/>
-      <x:c r="P33" s="42"/>
+      <x:c r="P33" s="43"/>
       <x:c r="Q33" s="37"/>
       <x:c r="R33" s="38"/>
       <x:c r="S33" s="38"/>
@@ -4621,7 +4627,7 @@
       <x:c r="B34" s="37"/>
       <x:c r="C34" s="37"/>
       <x:c r="D34" s="39"/>
-      <x:c r="E34" s="42"/>
+      <x:c r="E34" s="43"/>
       <x:c r="F34" s="37"/>
       <x:c r="G34" s="37"/>
       <x:c r="H34" s="37"/>
@@ -4630,9 +4636,9 @@
       <x:c r="K34" s="37"/>
       <x:c r="L34" s="37"/>
       <x:c r="M34" s="37"/>
-      <x:c r="N34" s="42"/>
+      <x:c r="N34" s="43"/>
       <x:c r="O34" s="37"/>
-      <x:c r="P34" s="42"/>
+      <x:c r="P34" s="43"/>
       <x:c r="Q34" s="37"/>
       <x:c r="R34" s="38"/>
       <x:c r="S34" s="38"/>
@@ -4643,7 +4649,7 @@
       <x:c r="B35" s="37"/>
       <x:c r="C35" s="37"/>
       <x:c r="D35" s="39"/>
-      <x:c r="E35" s="42"/>
+      <x:c r="E35" s="43"/>
       <x:c r="F35" s="37"/>
       <x:c r="G35" s="37"/>
       <x:c r="H35" s="37"/>
@@ -4652,9 +4658,9 @@
       <x:c r="K35" s="37"/>
       <x:c r="L35" s="37"/>
       <x:c r="M35" s="37"/>
-      <x:c r="N35" s="42"/>
+      <x:c r="N35" s="43"/>
       <x:c r="O35" s="37"/>
-      <x:c r="P35" s="42"/>
+      <x:c r="P35" s="43"/>
       <x:c r="Q35" s="37"/>
       <x:c r="R35" s="38"/>
       <x:c r="S35" s="38"/>
@@ -4665,7 +4671,7 @@
       <x:c r="B36" s="37"/>
       <x:c r="C36" s="37"/>
       <x:c r="D36" s="39"/>
-      <x:c r="E36" s="42"/>
+      <x:c r="E36" s="43"/>
       <x:c r="F36" s="37"/>
       <x:c r="G36" s="37"/>
       <x:c r="H36" s="37"/>
@@ -4674,9 +4680,9 @@
       <x:c r="K36" s="37"/>
       <x:c r="L36" s="37"/>
       <x:c r="M36" s="37"/>
-      <x:c r="N36" s="42"/>
+      <x:c r="N36" s="43"/>
       <x:c r="O36" s="37"/>
-      <x:c r="P36" s="42"/>
+      <x:c r="P36" s="43"/>
       <x:c r="Q36" s="37"/>
       <x:c r="R36" s="38"/>
       <x:c r="S36" s="38"/>
@@ -4687,7 +4693,7 @@
       <x:c r="B37" s="37"/>
       <x:c r="C37" s="37"/>
       <x:c r="D37" s="39"/>
-      <x:c r="E37" s="42"/>
+      <x:c r="E37" s="43"/>
       <x:c r="F37" s="37"/>
       <x:c r="G37" s="37"/>
       <x:c r="H37" s="37"/>
@@ -4696,9 +4702,9 @@
       <x:c r="K37" s="37"/>
       <x:c r="L37" s="37"/>
       <x:c r="M37" s="37"/>
-      <x:c r="N37" s="42"/>
+      <x:c r="N37" s="43"/>
       <x:c r="O37" s="37"/>
-      <x:c r="P37" s="42"/>
+      <x:c r="P37" s="43"/>
       <x:c r="Q37" s="37"/>
       <x:c r="R37" s="38"/>
       <x:c r="S37" s="38"/>
@@ -4709,7 +4715,7 @@
       <x:c r="B38" s="37"/>
       <x:c r="C38" s="37"/>
       <x:c r="D38" s="39"/>
-      <x:c r="E38" s="42"/>
+      <x:c r="E38" s="43"/>
       <x:c r="F38" s="37"/>
       <x:c r="G38" s="37"/>
       <x:c r="H38" s="37"/>
@@ -4718,9 +4724,9 @@
       <x:c r="K38" s="37"/>
       <x:c r="L38" s="37"/>
       <x:c r="M38" s="37"/>
-      <x:c r="N38" s="42"/>
+      <x:c r="N38" s="43"/>
       <x:c r="O38" s="37"/>
-      <x:c r="P38" s="42"/>
+      <x:c r="P38" s="43"/>
       <x:c r="Q38" s="37"/>
       <x:c r="R38" s="38"/>
       <x:c r="S38" s="38"/>
@@ -4731,7 +4737,7 @@
       <x:c r="B39" s="37"/>
       <x:c r="C39" s="37"/>
       <x:c r="D39" s="39"/>
-      <x:c r="E39" s="42"/>
+      <x:c r="E39" s="43"/>
       <x:c r="F39" s="37"/>
       <x:c r="G39" s="37"/>
       <x:c r="H39" s="37"/>
@@ -4740,9 +4746,9 @@
       <x:c r="K39" s="37"/>
       <x:c r="L39" s="37"/>
       <x:c r="M39" s="37"/>
-      <x:c r="N39" s="42"/>
+      <x:c r="N39" s="43"/>
       <x:c r="O39" s="37"/>
-      <x:c r="P39" s="42"/>
+      <x:c r="P39" s="43"/>
       <x:c r="Q39" s="37"/>
       <x:c r="R39" s="38"/>
       <x:c r="S39" s="38"/>
@@ -4753,7 +4759,7 @@
       <x:c r="B40" s="37"/>
       <x:c r="C40" s="37"/>
       <x:c r="D40" s="39"/>
-      <x:c r="E40" s="42"/>
+      <x:c r="E40" s="43"/>
       <x:c r="F40" s="37"/>
       <x:c r="G40" s="37"/>
       <x:c r="H40" s="37"/>
@@ -4762,9 +4768,9 @@
       <x:c r="K40" s="37"/>
       <x:c r="L40" s="37"/>
       <x:c r="M40" s="37"/>
-      <x:c r="N40" s="42"/>
+      <x:c r="N40" s="43"/>
       <x:c r="O40" s="37"/>
-      <x:c r="P40" s="42"/>
+      <x:c r="P40" s="43"/>
       <x:c r="Q40" s="37"/>
       <x:c r="R40" s="38"/>
       <x:c r="S40" s="38"/>
@@ -4775,7 +4781,7 @@
       <x:c r="B41" s="37"/>
       <x:c r="C41" s="37"/>
       <x:c r="D41" s="39"/>
-      <x:c r="E41" s="42"/>
+      <x:c r="E41" s="43"/>
       <x:c r="F41" s="37"/>
       <x:c r="G41" s="37"/>
       <x:c r="H41" s="37"/>
@@ -4784,9 +4790,9 @@
       <x:c r="K41" s="37"/>
       <x:c r="L41" s="37"/>
       <x:c r="M41" s="37"/>
-      <x:c r="N41" s="42"/>
+      <x:c r="N41" s="43"/>
       <x:c r="O41" s="37"/>
-      <x:c r="P41" s="42"/>
+      <x:c r="P41" s="43"/>
       <x:c r="Q41" s="37"/>
       <x:c r="R41" s="38"/>
       <x:c r="S41" s="38"/>
@@ -4797,7 +4803,7 @@
       <x:c r="B42" s="37"/>
       <x:c r="C42" s="37"/>
       <x:c r="D42" s="39"/>
-      <x:c r="E42" s="42"/>
+      <x:c r="E42" s="43"/>
       <x:c r="F42" s="37"/>
       <x:c r="G42" s="37"/>
       <x:c r="H42" s="37"/>
@@ -4806,9 +4812,9 @@
       <x:c r="K42" s="37"/>
       <x:c r="L42" s="37"/>
       <x:c r="M42" s="37"/>
-      <x:c r="N42" s="42"/>
+      <x:c r="N42" s="43"/>
       <x:c r="O42" s="37"/>
-      <x:c r="P42" s="42"/>
+      <x:c r="P42" s="43"/>
       <x:c r="Q42" s="37"/>
       <x:c r="R42" s="38"/>
       <x:c r="S42" s="38"/>
@@ -4819,7 +4825,7 @@
       <x:c r="B43" s="37"/>
       <x:c r="C43" s="37"/>
       <x:c r="D43" s="39"/>
-      <x:c r="E43" s="42"/>
+      <x:c r="E43" s="43"/>
       <x:c r="F43" s="37"/>
       <x:c r="G43" s="37"/>
       <x:c r="H43" s="37"/>
@@ -4828,9 +4834,9 @@
       <x:c r="K43" s="37"/>
       <x:c r="L43" s="37"/>
       <x:c r="M43" s="37"/>
-      <x:c r="N43" s="42"/>
+      <x:c r="N43" s="43"/>
       <x:c r="O43" s="37"/>
-      <x:c r="P43" s="42"/>
+      <x:c r="P43" s="43"/>
       <x:c r="Q43" s="37"/>
       <x:c r="R43" s="38"/>
       <x:c r="S43" s="38"/>
@@ -4841,7 +4847,7 @@
       <x:c r="B44" s="37"/>
       <x:c r="C44" s="37"/>
       <x:c r="D44" s="39"/>
-      <x:c r="E44" s="42"/>
+      <x:c r="E44" s="43"/>
       <x:c r="F44" s="37"/>
       <x:c r="G44" s="37"/>
       <x:c r="H44" s="37"/>
@@ -4850,9 +4856,9 @@
       <x:c r="K44" s="37"/>
       <x:c r="L44" s="37"/>
       <x:c r="M44" s="37"/>
-      <x:c r="N44" s="42"/>
+      <x:c r="N44" s="43"/>
       <x:c r="O44" s="37"/>
-      <x:c r="P44" s="42"/>
+      <x:c r="P44" s="43"/>
       <x:c r="Q44" s="37"/>
       <x:c r="R44" s="38"/>
       <x:c r="S44" s="38"/>
@@ -4863,7 +4869,7 @@
       <x:c r="B45" s="37"/>
       <x:c r="C45" s="37"/>
       <x:c r="D45" s="39"/>
-      <x:c r="E45" s="42"/>
+      <x:c r="E45" s="43"/>
       <x:c r="F45" s="37"/>
       <x:c r="G45" s="37"/>
       <x:c r="H45" s="37"/>
@@ -4872,9 +4878,9 @@
       <x:c r="K45" s="37"/>
       <x:c r="L45" s="37"/>
       <x:c r="M45" s="37"/>
-      <x:c r="N45" s="42"/>
+      <x:c r="N45" s="43"/>
       <x:c r="O45" s="37"/>
-      <x:c r="P45" s="42"/>
+      <x:c r="P45" s="43"/>
       <x:c r="Q45" s="37"/>
       <x:c r="R45" s="38"/>
       <x:c r="S45" s="38"/>
@@ -4885,7 +4891,7 @@
       <x:c r="B46" s="37"/>
       <x:c r="C46" s="37"/>
       <x:c r="D46" s="39"/>
-      <x:c r="E46" s="42"/>
+      <x:c r="E46" s="43"/>
       <x:c r="F46" s="37"/>
       <x:c r="G46" s="37"/>
       <x:c r="H46" s="37"/>
@@ -4894,9 +4900,9 @@
       <x:c r="K46" s="37"/>
       <x:c r="L46" s="37"/>
       <x:c r="M46" s="37"/>
-      <x:c r="N46" s="42"/>
+      <x:c r="N46" s="43"/>
       <x:c r="O46" s="37"/>
-      <x:c r="P46" s="42"/>
+      <x:c r="P46" s="43"/>
       <x:c r="Q46" s="37"/>
       <x:c r="R46" s="38"/>
       <x:c r="S46" s="38"/>
@@ -4907,7 +4913,7 @@
       <x:c r="B47" s="37"/>
       <x:c r="C47" s="37"/>
       <x:c r="D47" s="39"/>
-      <x:c r="E47" s="42"/>
+      <x:c r="E47" s="43"/>
       <x:c r="F47" s="37"/>
       <x:c r="G47" s="37"/>
       <x:c r="H47" s="37"/>
@@ -4916,9 +4922,9 @@
       <x:c r="K47" s="37"/>
       <x:c r="L47" s="37"/>
       <x:c r="M47" s="37"/>
-      <x:c r="N47" s="42"/>
+      <x:c r="N47" s="43"/>
       <x:c r="O47" s="37"/>
-      <x:c r="P47" s="42"/>
+      <x:c r="P47" s="43"/>
       <x:c r="Q47" s="37"/>
       <x:c r="R47" s="38"/>
       <x:c r="S47" s="38"/>
@@ -4929,7 +4935,7 @@
       <x:c r="B48" s="37"/>
       <x:c r="C48" s="37"/>
       <x:c r="D48" s="39"/>
-      <x:c r="E48" s="42"/>
+      <x:c r="E48" s="43"/>
       <x:c r="F48" s="37"/>
       <x:c r="G48" s="37"/>
       <x:c r="H48" s="37"/>
@@ -4938,9 +4944,9 @@
       <x:c r="K48" s="37"/>
       <x:c r="L48" s="37"/>
       <x:c r="M48" s="37"/>
-      <x:c r="N48" s="42"/>
+      <x:c r="N48" s="43"/>
       <x:c r="O48" s="37"/>
-      <x:c r="P48" s="42"/>
+      <x:c r="P48" s="43"/>
       <x:c r="Q48" s="37"/>
       <x:c r="R48" s="38"/>
       <x:c r="S48" s="38"/>
@@ -4951,7 +4957,7 @@
       <x:c r="B49" s="37"/>
       <x:c r="C49" s="37"/>
       <x:c r="D49" s="39"/>
-      <x:c r="E49" s="42"/>
+      <x:c r="E49" s="43"/>
       <x:c r="F49" s="37"/>
       <x:c r="G49" s="37"/>
       <x:c r="H49" s="37"/>
@@ -4960,9 +4966,9 @@
       <x:c r="K49" s="37"/>
       <x:c r="L49" s="37"/>
       <x:c r="M49" s="37"/>
-      <x:c r="N49" s="42"/>
+      <x:c r="N49" s="43"/>
       <x:c r="O49" s="37"/>
-      <x:c r="P49" s="42"/>
+      <x:c r="P49" s="43"/>
       <x:c r="Q49" s="37"/>
       <x:c r="R49" s="38"/>
       <x:c r="S49" s="38"/>
@@ -4973,7 +4979,7 @@
       <x:c r="B50" s="37"/>
       <x:c r="C50" s="37"/>
       <x:c r="D50" s="39"/>
-      <x:c r="E50" s="42"/>
+      <x:c r="E50" s="43"/>
       <x:c r="F50" s="37"/>
       <x:c r="G50" s="37"/>
       <x:c r="H50" s="37"/>
@@ -4982,9 +4988,9 @@
       <x:c r="K50" s="37"/>
       <x:c r="L50" s="37"/>
       <x:c r="M50" s="37"/>
-      <x:c r="N50" s="42"/>
+      <x:c r="N50" s="43"/>
       <x:c r="O50" s="37"/>
-      <x:c r="P50" s="42"/>
+      <x:c r="P50" s="43"/>
       <x:c r="Q50" s="37"/>
       <x:c r="R50" s="38"/>
       <x:c r="S50" s="38"/>
@@ -4995,7 +5001,7 @@
       <x:c r="B51" s="37"/>
       <x:c r="C51" s="37"/>
       <x:c r="D51" s="39"/>
-      <x:c r="E51" s="42"/>
+      <x:c r="E51" s="43"/>
       <x:c r="F51" s="37"/>
       <x:c r="G51" s="37"/>
       <x:c r="H51" s="37"/>
@@ -5004,9 +5010,9 @@
       <x:c r="K51" s="37"/>
       <x:c r="L51" s="37"/>
       <x:c r="M51" s="37"/>
-      <x:c r="N51" s="42"/>
+      <x:c r="N51" s="43"/>
       <x:c r="O51" s="37"/>
-      <x:c r="P51" s="42"/>
+      <x:c r="P51" s="43"/>
       <x:c r="Q51" s="37"/>
       <x:c r="R51" s="38"/>
       <x:c r="S51" s="38"/>
@@ -5017,7 +5023,7 @@
       <x:c r="B52" s="37"/>
       <x:c r="C52" s="37"/>
       <x:c r="D52" s="39"/>
-      <x:c r="E52" s="42"/>
+      <x:c r="E52" s="43"/>
       <x:c r="F52" s="37"/>
       <x:c r="G52" s="37"/>
       <x:c r="H52" s="37"/>
@@ -5026,9 +5032,9 @@
       <x:c r="K52" s="37"/>
       <x:c r="L52" s="37"/>
       <x:c r="M52" s="37"/>
-      <x:c r="N52" s="42"/>
+      <x:c r="N52" s="43"/>
       <x:c r="O52" s="37"/>
-      <x:c r="P52" s="42"/>
+      <x:c r="P52" s="43"/>
       <x:c r="Q52" s="37"/>
       <x:c r="R52" s="38"/>
       <x:c r="S52" s="38"/>
@@ -5039,7 +5045,7 @@
       <x:c r="B53" s="37"/>
       <x:c r="C53" s="37"/>
       <x:c r="D53" s="39"/>
-      <x:c r="E53" s="42"/>
+      <x:c r="E53" s="43"/>
       <x:c r="F53" s="37"/>
       <x:c r="G53" s="37"/>
       <x:c r="H53" s="37"/>
@@ -5048,9 +5054,9 @@
       <x:c r="K53" s="37"/>
       <x:c r="L53" s="37"/>
       <x:c r="M53" s="37"/>
-      <x:c r="N53" s="42"/>
+      <x:c r="N53" s="43"/>
       <x:c r="O53" s="37"/>
-      <x:c r="P53" s="42"/>
+      <x:c r="P53" s="43"/>
       <x:c r="Q53" s="37"/>
       <x:c r="R53" s="38"/>
       <x:c r="S53" s="38"/>
@@ -5061,7 +5067,7 @@
       <x:c r="B54" s="37"/>
       <x:c r="C54" s="37"/>
       <x:c r="D54" s="39"/>
-      <x:c r="E54" s="42"/>
+      <x:c r="E54" s="43"/>
       <x:c r="F54" s="37"/>
       <x:c r="G54" s="37"/>
       <x:c r="H54" s="37"/>
@@ -5070,9 +5076,9 @@
       <x:c r="K54" s="37"/>
       <x:c r="L54" s="37"/>
       <x:c r="M54" s="37"/>
-      <x:c r="N54" s="42"/>
+      <x:c r="N54" s="43"/>
       <x:c r="O54" s="37"/>
-      <x:c r="P54" s="42"/>
+      <x:c r="P54" s="43"/>
       <x:c r="Q54" s="37"/>
       <x:c r="R54" s="38"/>
       <x:c r="S54" s="38"/>
@@ -5083,7 +5089,7 @@
       <x:c r="B55" s="37"/>
       <x:c r="C55" s="37"/>
       <x:c r="D55" s="39"/>
-      <x:c r="E55" s="42"/>
+      <x:c r="E55" s="43"/>
       <x:c r="F55" s="37"/>
       <x:c r="G55" s="37"/>
       <x:c r="H55" s="37"/>
@@ -5092,9 +5098,9 @@
       <x:c r="K55" s="37"/>
       <x:c r="L55" s="37"/>
       <x:c r="M55" s="37"/>
-      <x:c r="N55" s="42"/>
+      <x:c r="N55" s="43"/>
       <x:c r="O55" s="37"/>
-      <x:c r="P55" s="42"/>
+      <x:c r="P55" s="43"/>
       <x:c r="Q55" s="37"/>
       <x:c r="R55" s="38"/>
       <x:c r="S55" s="38"/>
@@ -5105,7 +5111,7 @@
       <x:c r="B56" s="37"/>
       <x:c r="C56" s="37"/>
       <x:c r="D56" s="39"/>
-      <x:c r="E56" s="42"/>
+      <x:c r="E56" s="43"/>
       <x:c r="F56" s="37"/>
       <x:c r="G56" s="37"/>
       <x:c r="H56" s="37"/>
@@ -5114,9 +5120,9 @@
       <x:c r="K56" s="37"/>
       <x:c r="L56" s="37"/>
       <x:c r="M56" s="37"/>
-      <x:c r="N56" s="42"/>
+      <x:c r="N56" s="43"/>
       <x:c r="O56" s="37"/>
-      <x:c r="P56" s="42"/>
+      <x:c r="P56" s="43"/>
       <x:c r="Q56" s="37"/>
       <x:c r="R56" s="38"/>
       <x:c r="S56" s="38"/>
@@ -5127,7 +5133,7 @@
       <x:c r="B57" s="37"/>
       <x:c r="C57" s="37"/>
       <x:c r="D57" s="39"/>
-      <x:c r="E57" s="42"/>
+      <x:c r="E57" s="43"/>
       <x:c r="F57" s="37"/>
       <x:c r="G57" s="37"/>
       <x:c r="H57" s="37"/>
@@ -5136,9 +5142,9 @@
       <x:c r="K57" s="37"/>
       <x:c r="L57" s="37"/>
       <x:c r="M57" s="37"/>
-      <x:c r="N57" s="42"/>
+      <x:c r="N57" s="43"/>
       <x:c r="O57" s="37"/>
-      <x:c r="P57" s="42"/>
+      <x:c r="P57" s="43"/>
       <x:c r="Q57" s="37"/>
       <x:c r="R57" s="38"/>
       <x:c r="S57" s="38"/>
@@ -5149,7 +5155,7 @@
       <x:c r="B58" s="37"/>
       <x:c r="C58" s="37"/>
       <x:c r="D58" s="39"/>
-      <x:c r="E58" s="42"/>
+      <x:c r="E58" s="43"/>
       <x:c r="F58" s="37"/>
       <x:c r="G58" s="37"/>
       <x:c r="H58" s="37"/>
@@ -5158,9 +5164,9 @@
       <x:c r="K58" s="37"/>
       <x:c r="L58" s="37"/>
       <x:c r="M58" s="37"/>
-      <x:c r="N58" s="42"/>
+      <x:c r="N58" s="43"/>
       <x:c r="O58" s="37"/>
-      <x:c r="P58" s="42"/>
+      <x:c r="P58" s="43"/>
       <x:c r="Q58" s="37"/>
       <x:c r="R58" s="38"/>
       <x:c r="S58" s="38"/>
@@ -5171,7 +5177,7 @@
       <x:c r="B59" s="37"/>
       <x:c r="C59" s="37"/>
       <x:c r="D59" s="39"/>
-      <x:c r="E59" s="42"/>
+      <x:c r="E59" s="43"/>
       <x:c r="F59" s="37"/>
       <x:c r="G59" s="37"/>
       <x:c r="H59" s="37"/>
@@ -5180,9 +5186,9 @@
       <x:c r="K59" s="37"/>
       <x:c r="L59" s="37"/>
       <x:c r="M59" s="37"/>
-      <x:c r="N59" s="42"/>
+      <x:c r="N59" s="43"/>
       <x:c r="O59" s="37"/>
-      <x:c r="P59" s="42"/>
+      <x:c r="P59" s="43"/>
       <x:c r="Q59" s="37"/>
       <x:c r="R59" s="38"/>
       <x:c r="S59" s="38"/>
@@ -5193,7 +5199,7 @@
       <x:c r="B60" s="37"/>
       <x:c r="C60" s="37"/>
       <x:c r="D60" s="39"/>
-      <x:c r="E60" s="42"/>
+      <x:c r="E60" s="43"/>
       <x:c r="F60" s="37"/>
       <x:c r="G60" s="37"/>
       <x:c r="H60" s="37"/>
@@ -5202,9 +5208,9 @@
       <x:c r="K60" s="37"/>
       <x:c r="L60" s="37"/>
       <x:c r="M60" s="37"/>
-      <x:c r="N60" s="42"/>
+      <x:c r="N60" s="43"/>
       <x:c r="O60" s="37"/>
-      <x:c r="P60" s="42"/>
+      <x:c r="P60" s="43"/>
       <x:c r="Q60" s="37"/>
       <x:c r="R60" s="38"/>
       <x:c r="S60" s="38"/>
@@ -5215,7 +5221,7 @@
       <x:c r="B61" s="37"/>
       <x:c r="C61" s="37"/>
       <x:c r="D61" s="39"/>
-      <x:c r="E61" s="42"/>
+      <x:c r="E61" s="43"/>
       <x:c r="F61" s="37"/>
       <x:c r="G61" s="37"/>
       <x:c r="H61" s="37"/>
@@ -5224,9 +5230,9 @@
       <x:c r="K61" s="37"/>
       <x:c r="L61" s="37"/>
       <x:c r="M61" s="37"/>
-      <x:c r="N61" s="42"/>
+      <x:c r="N61" s="43"/>
       <x:c r="O61" s="37"/>
-      <x:c r="P61" s="42"/>
+      <x:c r="P61" s="43"/>
       <x:c r="Q61" s="37"/>
       <x:c r="R61" s="38"/>
       <x:c r="S61" s="38"/>
@@ -5237,7 +5243,7 @@
       <x:c r="B62" s="37"/>
       <x:c r="C62" s="37"/>
       <x:c r="D62" s="39"/>
-      <x:c r="E62" s="42"/>
+      <x:c r="E62" s="43"/>
       <x:c r="F62" s="37"/>
       <x:c r="G62" s="37"/>
       <x:c r="H62" s="37"/>
@@ -5246,9 +5252,9 @@
       <x:c r="K62" s="37"/>
       <x:c r="L62" s="37"/>
       <x:c r="M62" s="37"/>
-      <x:c r="N62" s="42"/>
+      <x:c r="N62" s="43"/>
       <x:c r="O62" s="37"/>
-      <x:c r="P62" s="42"/>
+      <x:c r="P62" s="43"/>
       <x:c r="Q62" s="37"/>
       <x:c r="R62" s="38"/>
       <x:c r="S62" s="38"/>
@@ -5259,7 +5265,7 @@
       <x:c r="B63" s="37"/>
       <x:c r="C63" s="37"/>
       <x:c r="D63" s="39"/>
-      <x:c r="E63" s="42"/>
+      <x:c r="E63" s="43"/>
       <x:c r="F63" s="37"/>
       <x:c r="G63" s="37"/>
       <x:c r="H63" s="37"/>
@@ -5268,9 +5274,9 @@
       <x:c r="K63" s="37"/>
       <x:c r="L63" s="37"/>
       <x:c r="M63" s="37"/>
-      <x:c r="N63" s="42"/>
+      <x:c r="N63" s="43"/>
       <x:c r="O63" s="37"/>
-      <x:c r="P63" s="42"/>
+      <x:c r="P63" s="43"/>
       <x:c r="Q63" s="37"/>
       <x:c r="R63" s="38"/>
       <x:c r="S63" s="38"/>
@@ -5281,7 +5287,7 @@
       <x:c r="B64" s="37"/>
       <x:c r="C64" s="37"/>
       <x:c r="D64" s="39"/>
-      <x:c r="E64" s="42"/>
+      <x:c r="E64" s="43"/>
       <x:c r="F64" s="37"/>
       <x:c r="G64" s="37"/>
       <x:c r="H64" s="37"/>
@@ -5290,9 +5296,9 @@
       <x:c r="K64" s="37"/>
       <x:c r="L64" s="37"/>
       <x:c r="M64" s="37"/>
-      <x:c r="N64" s="42"/>
+      <x:c r="N64" s="43"/>
       <x:c r="O64" s="37"/>
-      <x:c r="P64" s="42"/>
+      <x:c r="P64" s="43"/>
       <x:c r="Q64" s="37"/>
       <x:c r="R64" s="38"/>
       <x:c r="S64" s="38"/>
@@ -5303,7 +5309,7 @@
       <x:c r="B65" s="37"/>
       <x:c r="C65" s="37"/>
       <x:c r="D65" s="39"/>
-      <x:c r="E65" s="42"/>
+      <x:c r="E65" s="43"/>
       <x:c r="F65" s="37"/>
       <x:c r="G65" s="37"/>
       <x:c r="H65" s="37"/>
@@ -5312,9 +5318,9 @@
       <x:c r="K65" s="37"/>
       <x:c r="L65" s="37"/>
       <x:c r="M65" s="37"/>
-      <x:c r="N65" s="42"/>
+      <x:c r="N65" s="43"/>
       <x:c r="O65" s="37"/>
-      <x:c r="P65" s="42"/>
+      <x:c r="P65" s="43"/>
       <x:c r="Q65" s="37"/>
       <x:c r="R65" s="38"/>
       <x:c r="S65" s="38"/>
@@ -5325,7 +5331,7 @@
       <x:c r="B66" s="37"/>
       <x:c r="C66" s="37"/>
       <x:c r="D66" s="39"/>
-      <x:c r="E66" s="42"/>
+      <x:c r="E66" s="43"/>
       <x:c r="F66" s="37"/>
       <x:c r="G66" s="37"/>
       <x:c r="H66" s="37"/>
@@ -5334,9 +5340,9 @@
       <x:c r="K66" s="37"/>
       <x:c r="L66" s="37"/>
       <x:c r="M66" s="37"/>
-      <x:c r="N66" s="42"/>
+      <x:c r="N66" s="43"/>
       <x:c r="O66" s="37"/>
-      <x:c r="P66" s="42"/>
+      <x:c r="P66" s="43"/>
       <x:c r="Q66" s="37"/>
       <x:c r="R66" s="38"/>
       <x:c r="S66" s="38"/>
@@ -5347,7 +5353,7 @@
       <x:c r="B67" s="37"/>
       <x:c r="C67" s="37"/>
       <x:c r="D67" s="39"/>
-      <x:c r="E67" s="42"/>
+      <x:c r="E67" s="43"/>
       <x:c r="F67" s="37"/>
       <x:c r="G67" s="37"/>
       <x:c r="H67" s="37"/>
@@ -5356,9 +5362,9 @@
       <x:c r="K67" s="37"/>
       <x:c r="L67" s="37"/>
       <x:c r="M67" s="37"/>
-      <x:c r="N67" s="42"/>
+      <x:c r="N67" s="43"/>
       <x:c r="O67" s="37"/>
-      <x:c r="P67" s="42"/>
+      <x:c r="P67" s="43"/>
       <x:c r="Q67" s="37"/>
       <x:c r="R67" s="38"/>
       <x:c r="S67" s="38"/>
@@ -5369,7 +5375,7 @@
       <x:c r="B68" s="37"/>
       <x:c r="C68" s="37"/>
       <x:c r="D68" s="39"/>
-      <x:c r="E68" s="42"/>
+      <x:c r="E68" s="43"/>
       <x:c r="F68" s="37"/>
       <x:c r="G68" s="37"/>
       <x:c r="H68" s="37"/>
@@ -5378,9 +5384,9 @@
       <x:c r="K68" s="37"/>
       <x:c r="L68" s="37"/>
       <x:c r="M68" s="37"/>
-      <x:c r="N68" s="42"/>
+      <x:c r="N68" s="43"/>
       <x:c r="O68" s="37"/>
-      <x:c r="P68" s="42"/>
+      <x:c r="P68" s="43"/>
       <x:c r="Q68" s="37"/>
       <x:c r="R68" s="38"/>
       <x:c r="S68" s="38"/>
@@ -5391,7 +5397,7 @@
       <x:c r="B69" s="37"/>
       <x:c r="C69" s="37"/>
       <x:c r="D69" s="39"/>
-      <x:c r="E69" s="42"/>
+      <x:c r="E69" s="43"/>
       <x:c r="F69" s="37"/>
       <x:c r="G69" s="37"/>
       <x:c r="H69" s="37"/>
@@ -5400,9 +5406,9 @@
       <x:c r="K69" s="37"/>
       <x:c r="L69" s="37"/>
       <x:c r="M69" s="37"/>
-      <x:c r="N69" s="42"/>
+      <x:c r="N69" s="43"/>
       <x:c r="O69" s="37"/>
-      <x:c r="P69" s="42"/>
+      <x:c r="P69" s="43"/>
       <x:c r="Q69" s="37"/>
       <x:c r="R69" s="38"/>
       <x:c r="S69" s="38"/>
@@ -5413,7 +5419,7 @@
       <x:c r="B70" s="37"/>
       <x:c r="C70" s="37"/>
       <x:c r="D70" s="39"/>
-      <x:c r="E70" s="42"/>
+      <x:c r="E70" s="43"/>
       <x:c r="F70" s="37"/>
       <x:c r="G70" s="37"/>
       <x:c r="H70" s="37"/>
@@ -5422,9 +5428,9 @@
       <x:c r="K70" s="37"/>
       <x:c r="L70" s="37"/>
       <x:c r="M70" s="37"/>
-      <x:c r="N70" s="42"/>
+      <x:c r="N70" s="43"/>
       <x:c r="O70" s="37"/>
-      <x:c r="P70" s="42"/>
+      <x:c r="P70" s="43"/>
       <x:c r="Q70" s="37"/>
       <x:c r="R70" s="38"/>
       <x:c r="S70" s="38"/>
@@ -5435,7 +5441,7 @@
       <x:c r="B71" s="37"/>
       <x:c r="C71" s="37"/>
       <x:c r="D71" s="39"/>
-      <x:c r="E71" s="42"/>
+      <x:c r="E71" s="43"/>
       <x:c r="F71" s="37"/>
       <x:c r="G71" s="37"/>
       <x:c r="H71" s="37"/>
@@ -5444,9 +5450,9 @@
       <x:c r="K71" s="37"/>
       <x:c r="L71" s="37"/>
       <x:c r="M71" s="37"/>
-      <x:c r="N71" s="42"/>
+      <x:c r="N71" s="43"/>
       <x:c r="O71" s="37"/>
-      <x:c r="P71" s="42"/>
+      <x:c r="P71" s="43"/>
       <x:c r="Q71" s="37"/>
       <x:c r="R71" s="38"/>
       <x:c r="S71" s="38"/>
@@ -5457,7 +5463,7 @@
       <x:c r="B72" s="37"/>
       <x:c r="C72" s="37"/>
       <x:c r="D72" s="39"/>
-      <x:c r="E72" s="42"/>
+      <x:c r="E72" s="43"/>
       <x:c r="F72" s="37"/>
       <x:c r="G72" s="37"/>
       <x:c r="H72" s="37"/>
@@ -5466,9 +5472,9 @@
       <x:c r="K72" s="37"/>
       <x:c r="L72" s="37"/>
       <x:c r="M72" s="37"/>
-      <x:c r="N72" s="42"/>
+      <x:c r="N72" s="43"/>
       <x:c r="O72" s="37"/>
-      <x:c r="P72" s="42"/>
+      <x:c r="P72" s="43"/>
       <x:c r="Q72" s="37"/>
       <x:c r="R72" s="38"/>
       <x:c r="S72" s="38"/>
@@ -5479,7 +5485,7 @@
       <x:c r="B73" s="37"/>
       <x:c r="C73" s="37"/>
       <x:c r="D73" s="39"/>
-      <x:c r="E73" s="42"/>
+      <x:c r="E73" s="43"/>
       <x:c r="F73" s="37"/>
       <x:c r="G73" s="37"/>
       <x:c r="H73" s="37"/>
@@ -5488,9 +5494,9 @@
       <x:c r="K73" s="37"/>
       <x:c r="L73" s="37"/>
       <x:c r="M73" s="37"/>
-      <x:c r="N73" s="42"/>
+      <x:c r="N73" s="43"/>
       <x:c r="O73" s="37"/>
-      <x:c r="P73" s="42"/>
+      <x:c r="P73" s="43"/>
       <x:c r="Q73" s="37"/>
       <x:c r="R73" s="38"/>
       <x:c r="S73" s="38"/>
@@ -5501,7 +5507,7 @@
       <x:c r="B74" s="37"/>
       <x:c r="C74" s="37"/>
       <x:c r="D74" s="39"/>
-      <x:c r="E74" s="42"/>
+      <x:c r="E74" s="43"/>
       <x:c r="F74" s="37"/>
       <x:c r="G74" s="37"/>
       <x:c r="H74" s="37"/>
@@ -5510,9 +5516,9 @@
       <x:c r="K74" s="37"/>
       <x:c r="L74" s="37"/>
       <x:c r="M74" s="37"/>
-      <x:c r="N74" s="42"/>
+      <x:c r="N74" s="43"/>
       <x:c r="O74" s="37"/>
-      <x:c r="P74" s="42"/>
+      <x:c r="P74" s="43"/>
       <x:c r="Q74" s="37"/>
       <x:c r="R74" s="38"/>
       <x:c r="S74" s="38"/>
@@ -5523,7 +5529,7 @@
       <x:c r="B75" s="37"/>
       <x:c r="C75" s="37"/>
       <x:c r="D75" s="39"/>
-      <x:c r="E75" s="42"/>
+      <x:c r="E75" s="43"/>
       <x:c r="F75" s="37"/>
       <x:c r="G75" s="37"/>
       <x:c r="H75" s="37"/>
@@ -5532,9 +5538,9 @@
       <x:c r="K75" s="37"/>
       <x:c r="L75" s="37"/>
       <x:c r="M75" s="37"/>
-      <x:c r="N75" s="42"/>
+      <x:c r="N75" s="43"/>
       <x:c r="O75" s="37"/>
-      <x:c r="P75" s="42"/>
+      <x:c r="P75" s="43"/>
       <x:c r="Q75" s="37"/>
       <x:c r="R75" s="38"/>
       <x:c r="S75" s="38"/>
@@ -5545,7 +5551,7 @@
       <x:c r="B76" s="37"/>
       <x:c r="C76" s="37"/>
       <x:c r="D76" s="39"/>
-      <x:c r="E76" s="42"/>
+      <x:c r="E76" s="43"/>
       <x:c r="F76" s="37"/>
       <x:c r="G76" s="37"/>
       <x:c r="H76" s="37"/>
@@ -5554,9 +5560,9 @@
       <x:c r="K76" s="37"/>
       <x:c r="L76" s="37"/>
       <x:c r="M76" s="37"/>
-      <x:c r="N76" s="42"/>
+      <x:c r="N76" s="43"/>
       <x:c r="O76" s="37"/>
-      <x:c r="P76" s="42"/>
+      <x:c r="P76" s="43"/>
       <x:c r="Q76" s="37"/>
       <x:c r="R76" s="38"/>
       <x:c r="S76" s="38"/>
@@ -5567,7 +5573,7 @@
       <x:c r="B77" s="37"/>
       <x:c r="C77" s="37"/>
       <x:c r="D77" s="39"/>
-      <x:c r="E77" s="42"/>
+      <x:c r="E77" s="43"/>
       <x:c r="F77" s="37"/>
       <x:c r="G77" s="37"/>
       <x:c r="H77" s="37"/>
@@ -5576,9 +5582,9 @@
       <x:c r="K77" s="37"/>
       <x:c r="L77" s="37"/>
       <x:c r="M77" s="37"/>
-      <x:c r="N77" s="42"/>
+      <x:c r="N77" s="43"/>
       <x:c r="O77" s="37"/>
-      <x:c r="P77" s="42"/>
+      <x:c r="P77" s="43"/>
       <x:c r="Q77" s="37"/>
       <x:c r="R77" s="38"/>
       <x:c r="S77" s="38"/>
@@ -5589,7 +5595,7 @@
       <x:c r="B78" s="37"/>
       <x:c r="C78" s="37"/>
       <x:c r="D78" s="39"/>
-      <x:c r="E78" s="42"/>
+      <x:c r="E78" s="43"/>
       <x:c r="F78" s="37"/>
       <x:c r="G78" s="37"/>
       <x:c r="H78" s="37"/>
@@ -5598,9 +5604,9 @@
       <x:c r="K78" s="37"/>
       <x:c r="L78" s="37"/>
       <x:c r="M78" s="37"/>
-      <x:c r="N78" s="42"/>
+      <x:c r="N78" s="43"/>
       <x:c r="O78" s="37"/>
-      <x:c r="P78" s="42"/>
+      <x:c r="P78" s="43"/>
       <x:c r="Q78" s="37"/>
       <x:c r="R78" s="38"/>
       <x:c r="S78" s="38"/>
@@ -5611,7 +5617,7 @@
       <x:c r="B79" s="37"/>
       <x:c r="C79" s="37"/>
       <x:c r="D79" s="39"/>
-      <x:c r="E79" s="42"/>
+      <x:c r="E79" s="43"/>
       <x:c r="F79" s="37"/>
       <x:c r="G79" s="37"/>
       <x:c r="H79" s="37"/>
@@ -5620,9 +5626,9 @@
       <x:c r="K79" s="37"/>
       <x:c r="L79" s="37"/>
       <x:c r="M79" s="37"/>
-      <x:c r="N79" s="42"/>
+      <x:c r="N79" s="43"/>
       <x:c r="O79" s="37"/>
-      <x:c r="P79" s="42"/>
+      <x:c r="P79" s="43"/>
       <x:c r="Q79" s="37"/>
       <x:c r="R79" s="38"/>
       <x:c r="S79" s="38"/>
@@ -5633,7 +5639,7 @@
       <x:c r="B80" s="37"/>
       <x:c r="C80" s="37"/>
       <x:c r="D80" s="39"/>
-      <x:c r="E80" s="42"/>
+      <x:c r="E80" s="43"/>
       <x:c r="F80" s="37"/>
       <x:c r="G80" s="37"/>
       <x:c r="H80" s="37"/>
@@ -5642,9 +5648,9 @@
       <x:c r="K80" s="37"/>
       <x:c r="L80" s="37"/>
       <x:c r="M80" s="37"/>
-      <x:c r="N80" s="42"/>
+      <x:c r="N80" s="43"/>
       <x:c r="O80" s="37"/>
-      <x:c r="P80" s="42"/>
+      <x:c r="P80" s="43"/>
       <x:c r="Q80" s="37"/>
       <x:c r="R80" s="38"/>
       <x:c r="S80" s="38"/>
@@ -5655,7 +5661,7 @@
       <x:c r="B81" s="37"/>
       <x:c r="C81" s="37"/>
       <x:c r="D81" s="39"/>
-      <x:c r="E81" s="42"/>
+      <x:c r="E81" s="43"/>
       <x:c r="F81" s="37"/>
       <x:c r="G81" s="37"/>
       <x:c r="H81" s="37"/>
@@ -5664,9 +5670,9 @@
       <x:c r="K81" s="37"/>
       <x:c r="L81" s="37"/>
       <x:c r="M81" s="37"/>
-      <x:c r="N81" s="42"/>
+      <x:c r="N81" s="43"/>
       <x:c r="O81" s="37"/>
-      <x:c r="P81" s="42"/>
+      <x:c r="P81" s="43"/>
       <x:c r="Q81" s="37"/>
       <x:c r="R81" s="38"/>
       <x:c r="S81" s="38"/>
@@ -5677,7 +5683,7 @@
       <x:c r="B82" s="37"/>
       <x:c r="C82" s="37"/>
       <x:c r="D82" s="39"/>
-      <x:c r="E82" s="42"/>
+      <x:c r="E82" s="43"/>
       <x:c r="F82" s="37"/>
       <x:c r="G82" s="37"/>
       <x:c r="H82" s="37"/>
@@ -5686,9 +5692,9 @@
       <x:c r="K82" s="37"/>
       <x:c r="L82" s="37"/>
       <x:c r="M82" s="37"/>
-      <x:c r="N82" s="42"/>
+      <x:c r="N82" s="43"/>
       <x:c r="O82" s="37"/>
-      <x:c r="P82" s="42"/>
+      <x:c r="P82" s="43"/>
       <x:c r="Q82" s="37"/>
       <x:c r="R82" s="38"/>
       <x:c r="S82" s="38"/>
@@ -5699,7 +5705,7 @@
       <x:c r="B83" s="37"/>
       <x:c r="C83" s="37"/>
       <x:c r="D83" s="39"/>
-      <x:c r="E83" s="42"/>
+      <x:c r="E83" s="43"/>
       <x:c r="F83" s="37"/>
       <x:c r="G83" s="37"/>
       <x:c r="H83" s="37"/>
@@ -5708,9 +5714,9 @@
       <x:c r="K83" s="37"/>
       <x:c r="L83" s="37"/>
       <x:c r="M83" s="37"/>
-      <x:c r="N83" s="42"/>
+      <x:c r="N83" s="43"/>
       <x:c r="O83" s="37"/>
-      <x:c r="P83" s="42"/>
+      <x:c r="P83" s="43"/>
       <x:c r="Q83" s="37"/>
       <x:c r="R83" s="38"/>
       <x:c r="S83" s="38"/>
@@ -5721,7 +5727,7 @@
       <x:c r="B84" s="37"/>
       <x:c r="C84" s="37"/>
       <x:c r="D84" s="39"/>
-      <x:c r="E84" s="42"/>
+      <x:c r="E84" s="43"/>
       <x:c r="F84" s="37"/>
       <x:c r="G84" s="37"/>
       <x:c r="H84" s="37"/>
@@ -5730,9 +5736,9 @@
       <x:c r="K84" s="37"/>
       <x:c r="L84" s="37"/>
       <x:c r="M84" s="37"/>
-      <x:c r="N84" s="42"/>
+      <x:c r="N84" s="43"/>
       <x:c r="O84" s="37"/>
-      <x:c r="P84" s="42"/>
+      <x:c r="P84" s="43"/>
       <x:c r="Q84" s="37"/>
       <x:c r="R84" s="38"/>
       <x:c r="S84" s="38"/>
@@ -5743,7 +5749,7 @@
       <x:c r="B85" s="37"/>
       <x:c r="C85" s="37"/>
       <x:c r="D85" s="39"/>
-      <x:c r="E85" s="42"/>
+      <x:c r="E85" s="43"/>
       <x:c r="F85" s="37"/>
       <x:c r="G85" s="37"/>
       <x:c r="H85" s="37"/>
@@ -5752,9 +5758,9 @@
       <x:c r="K85" s="37"/>
       <x:c r="L85" s="37"/>
       <x:c r="M85" s="37"/>
-      <x:c r="N85" s="42"/>
+      <x:c r="N85" s="43"/>
       <x:c r="O85" s="37"/>
-      <x:c r="P85" s="42"/>
+      <x:c r="P85" s="43"/>
       <x:c r="Q85" s="37"/>
       <x:c r="R85" s="38"/>
       <x:c r="S85" s="38"/>
@@ -5765,7 +5771,7 @@
       <x:c r="B86" s="37"/>
       <x:c r="C86" s="37"/>
       <x:c r="D86" s="39"/>
-      <x:c r="E86" s="42"/>
+      <x:c r="E86" s="43"/>
       <x:c r="F86" s="37"/>
       <x:c r="G86" s="37"/>
       <x:c r="H86" s="37"/>
@@ -5774,9 +5780,9 @@
       <x:c r="K86" s="37"/>
       <x:c r="L86" s="37"/>
       <x:c r="M86" s="37"/>
-      <x:c r="N86" s="42"/>
+      <x:c r="N86" s="43"/>
       <x:c r="O86" s="37"/>
-      <x:c r="P86" s="42"/>
+      <x:c r="P86" s="43"/>
       <x:c r="Q86" s="37"/>
       <x:c r="R86" s="38"/>
       <x:c r="S86" s="38"/>
@@ -5787,7 +5793,7 @@
       <x:c r="B87" s="37"/>
       <x:c r="C87" s="37"/>
       <x:c r="D87" s="39"/>
-      <x:c r="E87" s="42"/>
+      <x:c r="E87" s="43"/>
       <x:c r="F87" s="37"/>
       <x:c r="G87" s="37"/>
       <x:c r="H87" s="37"/>
@@ -5796,9 +5802,9 @@
       <x:c r="K87" s="37"/>
       <x:c r="L87" s="37"/>
       <x:c r="M87" s="37"/>
-      <x:c r="N87" s="42"/>
+      <x:c r="N87" s="43"/>
       <x:c r="O87" s="37"/>
-      <x:c r="P87" s="42"/>
+      <x:c r="P87" s="43"/>
       <x:c r="Q87" s="37"/>
       <x:c r="R87" s="38"/>
       <x:c r="S87" s="38"/>
@@ -5809,7 +5815,7 @@
       <x:c r="B88" s="37"/>
       <x:c r="C88" s="37"/>
       <x:c r="D88" s="39"/>
-      <x:c r="E88" s="42"/>
+      <x:c r="E88" s="43"/>
       <x:c r="F88" s="37"/>
       <x:c r="G88" s="37"/>
       <x:c r="H88" s="37"/>
@@ -5818,9 +5824,9 @@
       <x:c r="K88" s="37"/>
       <x:c r="L88" s="37"/>
       <x:c r="M88" s="37"/>
-      <x:c r="N88" s="42"/>
+      <x:c r="N88" s="43"/>
       <x:c r="O88" s="37"/>
-      <x:c r="P88" s="42"/>
+      <x:c r="P88" s="43"/>
       <x:c r="Q88" s="37"/>
       <x:c r="R88" s="38"/>
       <x:c r="S88" s="38"/>
@@ -5831,7 +5837,7 @@
       <x:c r="B89" s="37"/>
       <x:c r="C89" s="37"/>
       <x:c r="D89" s="39"/>
-      <x:c r="E89" s="42"/>
+      <x:c r="E89" s="43"/>
       <x:c r="F89" s="37"/>
       <x:c r="G89" s="37"/>
       <x:c r="H89" s="37"/>
@@ -5840,9 +5846,9 @@
       <x:c r="K89" s="37"/>
       <x:c r="L89" s="37"/>
       <x:c r="M89" s="37"/>
-      <x:c r="N89" s="42"/>
+      <x:c r="N89" s="43"/>
       <x:c r="O89" s="37"/>
-      <x:c r="P89" s="42"/>
+      <x:c r="P89" s="43"/>
       <x:c r="Q89" s="37"/>
       <x:c r="R89" s="38"/>
       <x:c r="S89" s="38"/>
@@ -5853,7 +5859,7 @@
       <x:c r="B90" s="37"/>
       <x:c r="C90" s="37"/>
       <x:c r="D90" s="39"/>
-      <x:c r="E90" s="42"/>
+      <x:c r="E90" s="43"/>
       <x:c r="F90" s="37"/>
       <x:c r="G90" s="37"/>
       <x:c r="H90" s="37"/>
@@ -5862,9 +5868,9 @@
       <x:c r="K90" s="37"/>
       <x:c r="L90" s="37"/>
       <x:c r="M90" s="37"/>
-      <x:c r="N90" s="42"/>
+      <x:c r="N90" s="43"/>
       <x:c r="O90" s="37"/>
-      <x:c r="P90" s="42"/>
+      <x:c r="P90" s="43"/>
       <x:c r="Q90" s="37"/>
       <x:c r="R90" s="38"/>
       <x:c r="S90" s="38"/>
@@ -5875,7 +5881,7 @@
       <x:c r="B91" s="37"/>
       <x:c r="C91" s="37"/>
       <x:c r="D91" s="39"/>
-      <x:c r="E91" s="42"/>
+      <x:c r="E91" s="43"/>
       <x:c r="F91" s="37"/>
       <x:c r="G91" s="37"/>
       <x:c r="H91" s="37"/>
@@ -5884,9 +5890,9 @@
       <x:c r="K91" s="37"/>
       <x:c r="L91" s="37"/>
       <x:c r="M91" s="37"/>
-      <x:c r="N91" s="42"/>
+      <x:c r="N91" s="43"/>
       <x:c r="O91" s="37"/>
-      <x:c r="P91" s="42"/>
+      <x:c r="P91" s="43"/>
       <x:c r="Q91" s="37"/>
       <x:c r="R91" s="38"/>
       <x:c r="S91" s="38"/>
@@ -5897,7 +5903,7 @@
       <x:c r="B92" s="37"/>
       <x:c r="C92" s="37"/>
       <x:c r="D92" s="39"/>
-      <x:c r="E92" s="42"/>
+      <x:c r="E92" s="43"/>
       <x:c r="F92" s="37"/>
       <x:c r="G92" s="37"/>
       <x:c r="H92" s="37"/>
@@ -5906,9 +5912,9 @@
       <x:c r="K92" s="37"/>
       <x:c r="L92" s="37"/>
       <x:c r="M92" s="37"/>
-      <x:c r="N92" s="42"/>
+      <x:c r="N92" s="43"/>
       <x:c r="O92" s="37"/>
-      <x:c r="P92" s="42"/>
+      <x:c r="P92" s="43"/>
       <x:c r="Q92" s="37"/>
       <x:c r="R92" s="38"/>
       <x:c r="S92" s="38"/>
@@ -5919,7 +5925,7 @@
       <x:c r="B93" s="37"/>
       <x:c r="C93" s="37"/>
       <x:c r="D93" s="39"/>
-      <x:c r="E93" s="42"/>
+      <x:c r="E93" s="43"/>
       <x:c r="F93" s="37"/>
       <x:c r="G93" s="37"/>
       <x:c r="H93" s="37"/>
@@ -5928,9 +5934,9 @@
       <x:c r="K93" s="37"/>
       <x:c r="L93" s="37"/>
       <x:c r="M93" s="37"/>
-      <x:c r="N93" s="42"/>
+      <x:c r="N93" s="43"/>
       <x:c r="O93" s="37"/>
-      <x:c r="P93" s="42"/>
+      <x:c r="P93" s="43"/>
       <x:c r="Q93" s="37"/>
       <x:c r="R93" s="38"/>
       <x:c r="S93" s="38"/>
@@ -5941,7 +5947,7 @@
       <x:c r="B94" s="37"/>
       <x:c r="C94" s="37"/>
       <x:c r="D94" s="39"/>
-      <x:c r="E94" s="42"/>
+      <x:c r="E94" s="43"/>
       <x:c r="F94" s="37"/>
       <x:c r="G94" s="37"/>
       <x:c r="H94" s="37"/>
@@ -5950,9 +5956,9 @@
       <x:c r="K94" s="37"/>
       <x:c r="L94" s="37"/>
       <x:c r="M94" s="37"/>
-      <x:c r="N94" s="42"/>
+      <x:c r="N94" s="43"/>
       <x:c r="O94" s="37"/>
-      <x:c r="P94" s="42"/>
+      <x:c r="P94" s="43"/>
       <x:c r="Q94" s="37"/>
       <x:c r="R94" s="38"/>
       <x:c r="S94" s="38"/>
@@ -5963,7 +5969,7 @@
       <x:c r="B95" s="37"/>
       <x:c r="C95" s="37"/>
       <x:c r="D95" s="39"/>
-      <x:c r="E95" s="42"/>
+      <x:c r="E95" s="43"/>
       <x:c r="F95" s="37"/>
       <x:c r="G95" s="37"/>
       <x:c r="H95" s="37"/>
@@ -5972,9 +5978,9 @@
       <x:c r="K95" s="37"/>
       <x:c r="L95" s="37"/>
       <x:c r="M95" s="37"/>
-      <x:c r="N95" s="42"/>
+      <x:c r="N95" s="43"/>
       <x:c r="O95" s="37"/>
-      <x:c r="P95" s="42"/>
+      <x:c r="P95" s="43"/>
       <x:c r="Q95" s="37"/>
       <x:c r="R95" s="38"/>
       <x:c r="S95" s="38"/>
@@ -5985,7 +5991,7 @@
       <x:c r="B96" s="37"/>
       <x:c r="C96" s="37"/>
       <x:c r="D96" s="39"/>
-      <x:c r="E96" s="42"/>
+      <x:c r="E96" s="43"/>
       <x:c r="F96" s="37"/>
       <x:c r="G96" s="37"/>
       <x:c r="H96" s="37"/>
@@ -5994,9 +6000,9 @@
       <x:c r="K96" s="37"/>
       <x:c r="L96" s="37"/>
       <x:c r="M96" s="37"/>
-      <x:c r="N96" s="42"/>
+      <x:c r="N96" s="43"/>
       <x:c r="O96" s="37"/>
-      <x:c r="P96" s="42"/>
+      <x:c r="P96" s="43"/>
       <x:c r="Q96" s="37"/>
       <x:c r="R96" s="38"/>
       <x:c r="S96" s="38"/>
@@ -6007,7 +6013,7 @@
       <x:c r="B97" s="37"/>
       <x:c r="C97" s="37"/>
       <x:c r="D97" s="39"/>
-      <x:c r="E97" s="42"/>
+      <x:c r="E97" s="43"/>
       <x:c r="F97" s="37"/>
       <x:c r="G97" s="37"/>
       <x:c r="H97" s="37"/>
@@ -6016,9 +6022,9 @@
       <x:c r="K97" s="37"/>
       <x:c r="L97" s="37"/>
       <x:c r="M97" s="37"/>
-      <x:c r="N97" s="42"/>
+      <x:c r="N97" s="43"/>
       <x:c r="O97" s="37"/>
-      <x:c r="P97" s="42"/>
+      <x:c r="P97" s="43"/>
       <x:c r="Q97" s="37"/>
       <x:c r="R97" s="38"/>
       <x:c r="S97" s="38"/>
@@ -6029,7 +6035,7 @@
       <x:c r="B98" s="37"/>
       <x:c r="C98" s="37"/>
       <x:c r="D98" s="39"/>
-      <x:c r="E98" s="42"/>
+      <x:c r="E98" s="43"/>
       <x:c r="F98" s="37"/>
       <x:c r="G98" s="37"/>
       <x:c r="H98" s="37"/>
@@ -6038,9 +6044,9 @@
       <x:c r="K98" s="37"/>
       <x:c r="L98" s="37"/>
       <x:c r="M98" s="37"/>
-      <x:c r="N98" s="42"/>
+      <x:c r="N98" s="43"/>
       <x:c r="O98" s="37"/>
-      <x:c r="P98" s="42"/>
+      <x:c r="P98" s="43"/>
       <x:c r="Q98" s="37"/>
       <x:c r="R98" s="38"/>
       <x:c r="S98" s="38"/>
@@ -6051,7 +6057,7 @@
       <x:c r="B99" s="37"/>
       <x:c r="C99" s="37"/>
       <x:c r="D99" s="39"/>
-      <x:c r="E99" s="42"/>
+      <x:c r="E99" s="43"/>
       <x:c r="F99" s="37"/>
       <x:c r="G99" s="37"/>
       <x:c r="H99" s="37"/>
@@ -6060,9 +6066,9 @@
       <x:c r="K99" s="37"/>
       <x:c r="L99" s="37"/>
       <x:c r="M99" s="37"/>
-      <x:c r="N99" s="42"/>
+      <x:c r="N99" s="43"/>
       <x:c r="O99" s="37"/>
-      <x:c r="P99" s="42"/>
+      <x:c r="P99" s="43"/>
       <x:c r="Q99" s="37"/>
       <x:c r="R99" s="38"/>
       <x:c r="S99" s="38"/>
@@ -6073,7 +6079,7 @@
       <x:c r="B100" s="37"/>
       <x:c r="C100" s="37"/>
       <x:c r="D100" s="39"/>
-      <x:c r="E100" s="42"/>
+      <x:c r="E100" s="43"/>
       <x:c r="F100" s="37"/>
       <x:c r="G100" s="37"/>
       <x:c r="H100" s="37"/>
@@ -6082,9 +6088,9 @@
       <x:c r="K100" s="37"/>
       <x:c r="L100" s="37"/>
       <x:c r="M100" s="37"/>
-      <x:c r="N100" s="42"/>
+      <x:c r="N100" s="43"/>
       <x:c r="O100" s="37"/>
-      <x:c r="P100" s="42"/>
+      <x:c r="P100" s="43"/>
       <x:c r="Q100" s="37"/>
       <x:c r="R100" s="38"/>
       <x:c r="S100" s="38"/>
@@ -6095,7 +6101,7 @@
       <x:c r="B101" s="37"/>
       <x:c r="C101" s="37"/>
       <x:c r="D101" s="39"/>
-      <x:c r="E101" s="42"/>
+      <x:c r="E101" s="43"/>
       <x:c r="F101" s="37"/>
       <x:c r="G101" s="37"/>
       <x:c r="H101" s="37"/>
@@ -6104,9 +6110,9 @@
       <x:c r="K101" s="37"/>
       <x:c r="L101" s="37"/>
       <x:c r="M101" s="37"/>
-      <x:c r="N101" s="42"/>
+      <x:c r="N101" s="43"/>
       <x:c r="O101" s="37"/>
-      <x:c r="P101" s="42"/>
+      <x:c r="P101" s="43"/>
       <x:c r="Q101" s="37"/>
       <x:c r="R101" s="38"/>
       <x:c r="S101" s="38"/>
@@ -6117,7 +6123,7 @@
       <x:c r="B102" s="37"/>
       <x:c r="C102" s="37"/>
       <x:c r="D102" s="39"/>
-      <x:c r="E102" s="42"/>
+      <x:c r="E102" s="43"/>
       <x:c r="F102" s="37"/>
       <x:c r="G102" s="37"/>
       <x:c r="H102" s="37"/>
@@ -6126,9 +6132,9 @@
       <x:c r="K102" s="37"/>
       <x:c r="L102" s="37"/>
       <x:c r="M102" s="37"/>
-      <x:c r="N102" s="42"/>
+      <x:c r="N102" s="43"/>
       <x:c r="O102" s="37"/>
-      <x:c r="P102" s="42"/>
+      <x:c r="P102" s="43"/>
       <x:c r="Q102" s="37"/>
       <x:c r="R102" s="38"/>
       <x:c r="S102" s="38"/>
@@ -6139,7 +6145,7 @@
       <x:c r="B103" s="37"/>
       <x:c r="C103" s="37"/>
       <x:c r="D103" s="39"/>
-      <x:c r="E103" s="42"/>
+      <x:c r="E103" s="43"/>
       <x:c r="F103" s="37"/>
       <x:c r="G103" s="37"/>
       <x:c r="H103" s="37"/>
@@ -6148,9 +6154,9 @@
       <x:c r="K103" s="37"/>
       <x:c r="L103" s="37"/>
       <x:c r="M103" s="37"/>
-      <x:c r="N103" s="42"/>
+      <x:c r="N103" s="43"/>
       <x:c r="O103" s="37"/>
-      <x:c r="P103" s="42"/>
+      <x:c r="P103" s="43"/>
       <x:c r="Q103" s="37"/>
       <x:c r="R103" s="38"/>
       <x:c r="S103" s="38"/>
@@ -6161,7 +6167,7 @@
       <x:c r="B104" s="37"/>
       <x:c r="C104" s="37"/>
       <x:c r="D104" s="39"/>
-      <x:c r="E104" s="42"/>
+      <x:c r="E104" s="43"/>
       <x:c r="F104" s="37"/>
       <x:c r="G104" s="37"/>
       <x:c r="H104" s="37"/>
@@ -6170,9 +6176,9 @@
       <x:c r="K104" s="37"/>
       <x:c r="L104" s="37"/>
       <x:c r="M104" s="37"/>
-      <x:c r="N104" s="42"/>
+      <x:c r="N104" s="43"/>
       <x:c r="O104" s="37"/>
-      <x:c r="P104" s="42"/>
+      <x:c r="P104" s="43"/>
       <x:c r="Q104" s="37"/>
       <x:c r="R104" s="38"/>
       <x:c r="S104" s="38"/>
@@ -6200,7 +6206,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re84895ab756b40bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3777480f84542d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7292,7 +7298,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16bca566bd94405b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3eb80480e8c412e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9890,7 +9896,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a553304eb644744"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64a62e0cedb54fa5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11950,7 +11956,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42af88a6d4c74354"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7b143d395bf406d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13487,7 +13493,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f00ca48fae8433e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15bd3f05cf5b4f5d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14579,7 +14585,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R212ee6c6ffbb4d6e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a8c13ce999c4e4a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16324,7 +16330,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92857e2caa4341b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88884bd895c44b80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17962,7 +17968,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33654fb807ed4e2c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc748eba30e24291"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17979,22 +17985,24 @@
     <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="25" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="26" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="24" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="26" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="18" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="32" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="18" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="18" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="32" hidden="0" customWidth="1"/>
     <x:col min="21" max="21" width="18" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="18" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -18021,10 +18029,12 @@
       <x:c r="S1" s="20"/>
       <x:c r="T1" s="20"/>
       <x:c r="U1" s="20"/>
+      <x:c r="V1" s="20"/>
+      <x:c r="W1" s="20"/>
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="24" t="str">
-        <x:v>Enter everything being paid for and who it relates to. Category Name must already exist. Account Ref is optional.</x:v>
+        <x:v>Enter every cost. Use per_traveler for an individual's expense, fixed for a one-time trip cost, or percentage_of_individual for HS Leadership/Admin fees.</x:v>
       </x:c>
       <x:c r="B2" s="24"/>
       <x:c r="C2" s="24"/>
@@ -18046,6 +18056,8 @@
       <x:c r="S2" s="24"/>
       <x:c r="T2" s="24"/>
       <x:c r="U2" s="24"/>
+      <x:c r="V2" s="24"/>
+      <x:c r="W2" s="24"/>
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="28" t="str">
@@ -18071,6 +18083,8 @@
       <x:c r="S3" s="28"/>
       <x:c r="T3" s="28"/>
       <x:c r="U3" s="28"/>
+      <x:c r="V3" s="28"/>
+      <x:c r="W3" s="28"/>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
       <x:c r="A4" s="33" t="str">
@@ -18089,51 +18103,57 @@
         <x:v>Account Ref</x:v>
       </x:c>
       <x:c r="F4" s="33" t="str">
+        <x:v>Calculation Method</x:v>
+      </x:c>
+      <x:c r="G4" s="33" t="str">
+        <x:v>Percentage Rate</x:v>
+      </x:c>
+      <x:c r="H4" s="33" t="str">
         <x:v>Quantity</x:v>
       </x:c>
-      <x:c r="G4" s="33" t="str">
+      <x:c r="I4" s="33" t="str">
         <x:v>Estimated Unit Cost</x:v>
       </x:c>
-      <x:c r="H4" s="33" t="str">
+      <x:c r="J4" s="33" t="str">
         <x:v>Estimated Total</x:v>
       </x:c>
-      <x:c r="I4" s="33" t="str">
+      <x:c r="K4" s="33" t="str">
         <x:v>Actual Total</x:v>
       </x:c>
-      <x:c r="J4" s="33" t="str">
+      <x:c r="L4" s="33" t="str">
         <x:v>Vendor Name</x:v>
       </x:c>
-      <x:c r="K4" s="33" t="str">
+      <x:c r="M4" s="33" t="str">
         <x:v>Vendor Organization Name</x:v>
       </x:c>
-      <x:c r="L4" s="33" t="str">
+      <x:c r="N4" s="33" t="str">
         <x:v>Settlement Route</x:v>
       </x:c>
-      <x:c r="M4" s="33" t="str">
+      <x:c r="O4" s="33" t="str">
         <x:v>Payment Status</x:v>
       </x:c>
-      <x:c r="N4" s="33" t="str">
+      <x:c r="P4" s="33" t="str">
         <x:v>Payment Method</x:v>
       </x:c>
-      <x:c r="O4" s="33" t="str">
+      <x:c r="Q4" s="33" t="str">
         <x:v>External Reference</x:v>
       </x:c>
-      <x:c r="P4" s="33" t="str">
+      <x:c r="R4" s="33" t="str">
         <x:v>Due Date</x:v>
       </x:c>
-      <x:c r="Q4" s="33" t="str">
+      <x:c r="S4" s="33" t="str">
         <x:v>Paid Date</x:v>
       </x:c>
-      <x:c r="R4" s="33" t="str">
+      <x:c r="T4" s="33" t="str">
         <x:v>Notes</x:v>
       </x:c>
-      <x:c r="S4" s="33" t="str">
+      <x:c r="U4" s="33" t="str">
         <x:v>Record ID</x:v>
       </x:c>
-      <x:c r="T4" s="33" t="str">
+      <x:c r="V4" s="33" t="str">
         <x:v>Original Updated At</x:v>
       </x:c>
-      <x:c r="U4" s="33" t="str">
+      <x:c r="W4" s="33" t="str">
         <x:v>Original Fingerprint</x:v>
       </x:c>
     </x:row>
@@ -18143,22 +18163,24 @@
       <x:c r="C5" s="37"/>
       <x:c r="D5" s="37"/>
       <x:c r="E5" s="37"/>
-      <x:c r="F5" s="41"/>
-      <x:c r="G5" s="42"/>
+      <x:c r="F5" s="37"/>
+      <x:c r="G5" s="41"/>
       <x:c r="H5" s="42"/>
-      <x:c r="I5" s="42"/>
-      <x:c r="J5" s="37"/>
-      <x:c r="K5" s="37"/>
+      <x:c r="I5" s="43"/>
+      <x:c r="J5" s="43"/>
+      <x:c r="K5" s="43"/>
       <x:c r="L5" s="37"/>
       <x:c r="M5" s="37"/>
       <x:c r="N5" s="37"/>
       <x:c r="O5" s="37"/>
-      <x:c r="P5" s="39"/>
-      <x:c r="Q5" s="39"/>
-      <x:c r="R5" s="37"/>
-      <x:c r="S5" s="38"/>
-      <x:c r="T5" s="38"/>
+      <x:c r="P5" s="37"/>
+      <x:c r="Q5" s="37"/>
+      <x:c r="R5" s="39"/>
+      <x:c r="S5" s="39"/>
+      <x:c r="T5" s="37"/>
       <x:c r="U5" s="38"/>
+      <x:c r="V5" s="38"/>
+      <x:c r="W5" s="38"/>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="37"/>
@@ -18166,22 +18188,24 @@
       <x:c r="C6" s="37"/>
       <x:c r="D6" s="37"/>
       <x:c r="E6" s="37"/>
-      <x:c r="F6" s="41"/>
-      <x:c r="G6" s="42"/>
+      <x:c r="F6" s="37"/>
+      <x:c r="G6" s="41"/>
       <x:c r="H6" s="42"/>
-      <x:c r="I6" s="42"/>
-      <x:c r="J6" s="37"/>
-      <x:c r="K6" s="37"/>
+      <x:c r="I6" s="43"/>
+      <x:c r="J6" s="43"/>
+      <x:c r="K6" s="43"/>
       <x:c r="L6" s="37"/>
       <x:c r="M6" s="37"/>
       <x:c r="N6" s="37"/>
       <x:c r="O6" s="37"/>
-      <x:c r="P6" s="39"/>
-      <x:c r="Q6" s="39"/>
-      <x:c r="R6" s="37"/>
-      <x:c r="S6" s="38"/>
-      <x:c r="T6" s="38"/>
+      <x:c r="P6" s="37"/>
+      <x:c r="Q6" s="37"/>
+      <x:c r="R6" s="39"/>
+      <x:c r="S6" s="39"/>
+      <x:c r="T6" s="37"/>
       <x:c r="U6" s="38"/>
+      <x:c r="V6" s="38"/>
+      <x:c r="W6" s="38"/>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
       <x:c r="A7" s="37"/>
@@ -18189,22 +18213,24 @@
       <x:c r="C7" s="37"/>
       <x:c r="D7" s="37"/>
       <x:c r="E7" s="37"/>
-      <x:c r="F7" s="41"/>
-      <x:c r="G7" s="42"/>
+      <x:c r="F7" s="37"/>
+      <x:c r="G7" s="41"/>
       <x:c r="H7" s="42"/>
-      <x:c r="I7" s="42"/>
-      <x:c r="J7" s="37"/>
-      <x:c r="K7" s="37"/>
+      <x:c r="I7" s="43"/>
+      <x:c r="J7" s="43"/>
+      <x:c r="K7" s="43"/>
       <x:c r="L7" s="37"/>
       <x:c r="M7" s="37"/>
       <x:c r="N7" s="37"/>
       <x:c r="O7" s="37"/>
-      <x:c r="P7" s="39"/>
-      <x:c r="Q7" s="39"/>
-      <x:c r="R7" s="37"/>
-      <x:c r="S7" s="38"/>
-      <x:c r="T7" s="38"/>
+      <x:c r="P7" s="37"/>
+      <x:c r="Q7" s="37"/>
+      <x:c r="R7" s="39"/>
+      <x:c r="S7" s="39"/>
+      <x:c r="T7" s="37"/>
       <x:c r="U7" s="38"/>
+      <x:c r="V7" s="38"/>
+      <x:c r="W7" s="38"/>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="37"/>
@@ -18212,22 +18238,24 @@
       <x:c r="C8" s="37"/>
       <x:c r="D8" s="37"/>
       <x:c r="E8" s="37"/>
-      <x:c r="F8" s="41"/>
-      <x:c r="G8" s="42"/>
+      <x:c r="F8" s="37"/>
+      <x:c r="G8" s="41"/>
       <x:c r="H8" s="42"/>
-      <x:c r="I8" s="42"/>
-      <x:c r="J8" s="37"/>
-      <x:c r="K8" s="37"/>
+      <x:c r="I8" s="43"/>
+      <x:c r="J8" s="43"/>
+      <x:c r="K8" s="43"/>
       <x:c r="L8" s="37"/>
       <x:c r="M8" s="37"/>
       <x:c r="N8" s="37"/>
       <x:c r="O8" s="37"/>
-      <x:c r="P8" s="39"/>
-      <x:c r="Q8" s="39"/>
-      <x:c r="R8" s="37"/>
-      <x:c r="S8" s="38"/>
-      <x:c r="T8" s="38"/>
+      <x:c r="P8" s="37"/>
+      <x:c r="Q8" s="37"/>
+      <x:c r="R8" s="39"/>
+      <x:c r="S8" s="39"/>
+      <x:c r="T8" s="37"/>
       <x:c r="U8" s="38"/>
+      <x:c r="V8" s="38"/>
+      <x:c r="W8" s="38"/>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="37"/>
@@ -18235,22 +18263,24 @@
       <x:c r="C9" s="37"/>
       <x:c r="D9" s="37"/>
       <x:c r="E9" s="37"/>
-      <x:c r="F9" s="41"/>
-      <x:c r="G9" s="42"/>
+      <x:c r="F9" s="37"/>
+      <x:c r="G9" s="41"/>
       <x:c r="H9" s="42"/>
-      <x:c r="I9" s="42"/>
-      <x:c r="J9" s="37"/>
-      <x:c r="K9" s="37"/>
+      <x:c r="I9" s="43"/>
+      <x:c r="J9" s="43"/>
+      <x:c r="K9" s="43"/>
       <x:c r="L9" s="37"/>
       <x:c r="M9" s="37"/>
       <x:c r="N9" s="37"/>
       <x:c r="O9" s="37"/>
-      <x:c r="P9" s="39"/>
-      <x:c r="Q9" s="39"/>
-      <x:c r="R9" s="37"/>
-      <x:c r="S9" s="38"/>
-      <x:c r="T9" s="38"/>
+      <x:c r="P9" s="37"/>
+      <x:c r="Q9" s="37"/>
+      <x:c r="R9" s="39"/>
+      <x:c r="S9" s="39"/>
+      <x:c r="T9" s="37"/>
       <x:c r="U9" s="38"/>
+      <x:c r="V9" s="38"/>
+      <x:c r="W9" s="38"/>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="37"/>
@@ -18258,22 +18288,24 @@
       <x:c r="C10" s="37"/>
       <x:c r="D10" s="37"/>
       <x:c r="E10" s="37"/>
-      <x:c r="F10" s="41"/>
-      <x:c r="G10" s="42"/>
+      <x:c r="F10" s="37"/>
+      <x:c r="G10" s="41"/>
       <x:c r="H10" s="42"/>
-      <x:c r="I10" s="42"/>
-      <x:c r="J10" s="37"/>
-      <x:c r="K10" s="37"/>
+      <x:c r="I10" s="43"/>
+      <x:c r="J10" s="43"/>
+      <x:c r="K10" s="43"/>
       <x:c r="L10" s="37"/>
       <x:c r="M10" s="37"/>
       <x:c r="N10" s="37"/>
       <x:c r="O10" s="37"/>
-      <x:c r="P10" s="39"/>
-      <x:c r="Q10" s="39"/>
-      <x:c r="R10" s="37"/>
-      <x:c r="S10" s="38"/>
-      <x:c r="T10" s="38"/>
+      <x:c r="P10" s="37"/>
+      <x:c r="Q10" s="37"/>
+      <x:c r="R10" s="39"/>
+      <x:c r="S10" s="39"/>
+      <x:c r="T10" s="37"/>
       <x:c r="U10" s="38"/>
+      <x:c r="V10" s="38"/>
+      <x:c r="W10" s="38"/>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="37"/>
@@ -18281,22 +18313,24 @@
       <x:c r="C11" s="37"/>
       <x:c r="D11" s="37"/>
       <x:c r="E11" s="37"/>
-      <x:c r="F11" s="41"/>
-      <x:c r="G11" s="42"/>
+      <x:c r="F11" s="37"/>
+      <x:c r="G11" s="41"/>
       <x:c r="H11" s="42"/>
-      <x:c r="I11" s="42"/>
-      <x:c r="J11" s="37"/>
-      <x:c r="K11" s="37"/>
+      <x:c r="I11" s="43"/>
+      <x:c r="J11" s="43"/>
+      <x:c r="K11" s="43"/>
       <x:c r="L11" s="37"/>
       <x:c r="M11" s="37"/>
       <x:c r="N11" s="37"/>
       <x:c r="O11" s="37"/>
-      <x:c r="P11" s="39"/>
-      <x:c r="Q11" s="39"/>
-      <x:c r="R11" s="37"/>
-      <x:c r="S11" s="38"/>
-      <x:c r="T11" s="38"/>
+      <x:c r="P11" s="37"/>
+      <x:c r="Q11" s="37"/>
+      <x:c r="R11" s="39"/>
+      <x:c r="S11" s="39"/>
+      <x:c r="T11" s="37"/>
       <x:c r="U11" s="38"/>
+      <x:c r="V11" s="38"/>
+      <x:c r="W11" s="38"/>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="37"/>
@@ -18304,22 +18338,24 @@
       <x:c r="C12" s="37"/>
       <x:c r="D12" s="37"/>
       <x:c r="E12" s="37"/>
-      <x:c r="F12" s="41"/>
-      <x:c r="G12" s="42"/>
+      <x:c r="F12" s="37"/>
+      <x:c r="G12" s="41"/>
       <x:c r="H12" s="42"/>
-      <x:c r="I12" s="42"/>
-      <x:c r="J12" s="37"/>
-      <x:c r="K12" s="37"/>
+      <x:c r="I12" s="43"/>
+      <x:c r="J12" s="43"/>
+      <x:c r="K12" s="43"/>
       <x:c r="L12" s="37"/>
       <x:c r="M12" s="37"/>
       <x:c r="N12" s="37"/>
       <x:c r="O12" s="37"/>
-      <x:c r="P12" s="39"/>
-      <x:c r="Q12" s="39"/>
-      <x:c r="R12" s="37"/>
-      <x:c r="S12" s="38"/>
-      <x:c r="T12" s="38"/>
+      <x:c r="P12" s="37"/>
+      <x:c r="Q12" s="37"/>
+      <x:c r="R12" s="39"/>
+      <x:c r="S12" s="39"/>
+      <x:c r="T12" s="37"/>
       <x:c r="U12" s="38"/>
+      <x:c r="V12" s="38"/>
+      <x:c r="W12" s="38"/>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="37"/>
@@ -18327,22 +18363,24 @@
       <x:c r="C13" s="37"/>
       <x:c r="D13" s="37"/>
       <x:c r="E13" s="37"/>
-      <x:c r="F13" s="41"/>
-      <x:c r="G13" s="42"/>
+      <x:c r="F13" s="37"/>
+      <x:c r="G13" s="41"/>
       <x:c r="H13" s="42"/>
-      <x:c r="I13" s="42"/>
-      <x:c r="J13" s="37"/>
-      <x:c r="K13" s="37"/>
+      <x:c r="I13" s="43"/>
+      <x:c r="J13" s="43"/>
+      <x:c r="K13" s="43"/>
       <x:c r="L13" s="37"/>
       <x:c r="M13" s="37"/>
       <x:c r="N13" s="37"/>
       <x:c r="O13" s="37"/>
-      <x:c r="P13" s="39"/>
-      <x:c r="Q13" s="39"/>
-      <x:c r="R13" s="37"/>
-      <x:c r="S13" s="38"/>
-      <x:c r="T13" s="38"/>
+      <x:c r="P13" s="37"/>
+      <x:c r="Q13" s="37"/>
+      <x:c r="R13" s="39"/>
+      <x:c r="S13" s="39"/>
+      <x:c r="T13" s="37"/>
       <x:c r="U13" s="38"/>
+      <x:c r="V13" s="38"/>
+      <x:c r="W13" s="38"/>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" s="37"/>
@@ -18350,22 +18388,24 @@
       <x:c r="C14" s="37"/>
       <x:c r="D14" s="37"/>
       <x:c r="E14" s="37"/>
-      <x:c r="F14" s="41"/>
-      <x:c r="G14" s="42"/>
+      <x:c r="F14" s="37"/>
+      <x:c r="G14" s="41"/>
       <x:c r="H14" s="42"/>
-      <x:c r="I14" s="42"/>
-      <x:c r="J14" s="37"/>
-      <x:c r="K14" s="37"/>
+      <x:c r="I14" s="43"/>
+      <x:c r="J14" s="43"/>
+      <x:c r="K14" s="43"/>
       <x:c r="L14" s="37"/>
       <x:c r="M14" s="37"/>
       <x:c r="N14" s="37"/>
       <x:c r="O14" s="37"/>
-      <x:c r="P14" s="39"/>
-      <x:c r="Q14" s="39"/>
-      <x:c r="R14" s="37"/>
-      <x:c r="S14" s="38"/>
-      <x:c r="T14" s="38"/>
+      <x:c r="P14" s="37"/>
+      <x:c r="Q14" s="37"/>
+      <x:c r="R14" s="39"/>
+      <x:c r="S14" s="39"/>
+      <x:c r="T14" s="37"/>
       <x:c r="U14" s="38"/>
+      <x:c r="V14" s="38"/>
+      <x:c r="W14" s="38"/>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="37"/>
@@ -18373,22 +18413,24 @@
       <x:c r="C15" s="37"/>
       <x:c r="D15" s="37"/>
       <x:c r="E15" s="37"/>
-      <x:c r="F15" s="41"/>
-      <x:c r="G15" s="42"/>
+      <x:c r="F15" s="37"/>
+      <x:c r="G15" s="41"/>
       <x:c r="H15" s="42"/>
-      <x:c r="I15" s="42"/>
-      <x:c r="J15" s="37"/>
-      <x:c r="K15" s="37"/>
+      <x:c r="I15" s="43"/>
+      <x:c r="J15" s="43"/>
+      <x:c r="K15" s="43"/>
       <x:c r="L15" s="37"/>
       <x:c r="M15" s="37"/>
       <x:c r="N15" s="37"/>
       <x:c r="O15" s="37"/>
-      <x:c r="P15" s="39"/>
-      <x:c r="Q15" s="39"/>
-      <x:c r="R15" s="37"/>
-      <x:c r="S15" s="38"/>
-      <x:c r="T15" s="38"/>
+      <x:c r="P15" s="37"/>
+      <x:c r="Q15" s="37"/>
+      <x:c r="R15" s="39"/>
+      <x:c r="S15" s="39"/>
+      <x:c r="T15" s="37"/>
       <x:c r="U15" s="38"/>
+      <x:c r="V15" s="38"/>
+      <x:c r="W15" s="38"/>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="37"/>
@@ -18396,22 +18438,24 @@
       <x:c r="C16" s="37"/>
       <x:c r="D16" s="37"/>
       <x:c r="E16" s="37"/>
-      <x:c r="F16" s="41"/>
-      <x:c r="G16" s="42"/>
+      <x:c r="F16" s="37"/>
+      <x:c r="G16" s="41"/>
       <x:c r="H16" s="42"/>
-      <x:c r="I16" s="42"/>
-      <x:c r="J16" s="37"/>
-      <x:c r="K16" s="37"/>
+      <x:c r="I16" s="43"/>
+      <x:c r="J16" s="43"/>
+      <x:c r="K16" s="43"/>
       <x:c r="L16" s="37"/>
       <x:c r="M16" s="37"/>
       <x:c r="N16" s="37"/>
       <x:c r="O16" s="37"/>
-      <x:c r="P16" s="39"/>
-      <x:c r="Q16" s="39"/>
-      <x:c r="R16" s="37"/>
-      <x:c r="S16" s="38"/>
-      <x:c r="T16" s="38"/>
+      <x:c r="P16" s="37"/>
+      <x:c r="Q16" s="37"/>
+      <x:c r="R16" s="39"/>
+      <x:c r="S16" s="39"/>
+      <x:c r="T16" s="37"/>
       <x:c r="U16" s="38"/>
+      <x:c r="V16" s="38"/>
+      <x:c r="W16" s="38"/>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
       <x:c r="A17" s="37"/>
@@ -18419,22 +18463,24 @@
       <x:c r="C17" s="37"/>
       <x:c r="D17" s="37"/>
       <x:c r="E17" s="37"/>
-      <x:c r="F17" s="41"/>
-      <x:c r="G17" s="42"/>
+      <x:c r="F17" s="37"/>
+      <x:c r="G17" s="41"/>
       <x:c r="H17" s="42"/>
-      <x:c r="I17" s="42"/>
-      <x:c r="J17" s="37"/>
-      <x:c r="K17" s="37"/>
+      <x:c r="I17" s="43"/>
+      <x:c r="J17" s="43"/>
+      <x:c r="K17" s="43"/>
       <x:c r="L17" s="37"/>
       <x:c r="M17" s="37"/>
       <x:c r="N17" s="37"/>
       <x:c r="O17" s="37"/>
-      <x:c r="P17" s="39"/>
-      <x:c r="Q17" s="39"/>
-      <x:c r="R17" s="37"/>
-      <x:c r="S17" s="38"/>
-      <x:c r="T17" s="38"/>
+      <x:c r="P17" s="37"/>
+      <x:c r="Q17" s="37"/>
+      <x:c r="R17" s="39"/>
+      <x:c r="S17" s="39"/>
+      <x:c r="T17" s="37"/>
       <x:c r="U17" s="38"/>
+      <x:c r="V17" s="38"/>
+      <x:c r="W17" s="38"/>
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
       <x:c r="A18" s="37"/>
@@ -18442,22 +18488,24 @@
       <x:c r="C18" s="37"/>
       <x:c r="D18" s="37"/>
       <x:c r="E18" s="37"/>
-      <x:c r="F18" s="41"/>
-      <x:c r="G18" s="42"/>
+      <x:c r="F18" s="37"/>
+      <x:c r="G18" s="41"/>
       <x:c r="H18" s="42"/>
-      <x:c r="I18" s="42"/>
-      <x:c r="J18" s="37"/>
-      <x:c r="K18" s="37"/>
+      <x:c r="I18" s="43"/>
+      <x:c r="J18" s="43"/>
+      <x:c r="K18" s="43"/>
       <x:c r="L18" s="37"/>
       <x:c r="M18" s="37"/>
       <x:c r="N18" s="37"/>
       <x:c r="O18" s="37"/>
-      <x:c r="P18" s="39"/>
-      <x:c r="Q18" s="39"/>
-      <x:c r="R18" s="37"/>
-      <x:c r="S18" s="38"/>
-      <x:c r="T18" s="38"/>
+      <x:c r="P18" s="37"/>
+      <x:c r="Q18" s="37"/>
+      <x:c r="R18" s="39"/>
+      <x:c r="S18" s="39"/>
+      <x:c r="T18" s="37"/>
       <x:c r="U18" s="38"/>
+      <x:c r="V18" s="38"/>
+      <x:c r="W18" s="38"/>
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
       <x:c r="A19" s="37"/>
@@ -18465,22 +18513,24 @@
       <x:c r="C19" s="37"/>
       <x:c r="D19" s="37"/>
       <x:c r="E19" s="37"/>
-      <x:c r="F19" s="41"/>
-      <x:c r="G19" s="42"/>
+      <x:c r="F19" s="37"/>
+      <x:c r="G19" s="41"/>
       <x:c r="H19" s="42"/>
-      <x:c r="I19" s="42"/>
-      <x:c r="J19" s="37"/>
-      <x:c r="K19" s="37"/>
+      <x:c r="I19" s="43"/>
+      <x:c r="J19" s="43"/>
+      <x:c r="K19" s="43"/>
       <x:c r="L19" s="37"/>
       <x:c r="M19" s="37"/>
       <x:c r="N19" s="37"/>
       <x:c r="O19" s="37"/>
-      <x:c r="P19" s="39"/>
-      <x:c r="Q19" s="39"/>
-      <x:c r="R19" s="37"/>
-      <x:c r="S19" s="38"/>
-      <x:c r="T19" s="38"/>
+      <x:c r="P19" s="37"/>
+      <x:c r="Q19" s="37"/>
+      <x:c r="R19" s="39"/>
+      <x:c r="S19" s="39"/>
+      <x:c r="T19" s="37"/>
       <x:c r="U19" s="38"/>
+      <x:c r="V19" s="38"/>
+      <x:c r="W19" s="38"/>
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="37"/>
@@ -18488,22 +18538,24 @@
       <x:c r="C20" s="37"/>
       <x:c r="D20" s="37"/>
       <x:c r="E20" s="37"/>
-      <x:c r="F20" s="41"/>
-      <x:c r="G20" s="42"/>
+      <x:c r="F20" s="37"/>
+      <x:c r="G20" s="41"/>
       <x:c r="H20" s="42"/>
-      <x:c r="I20" s="42"/>
-      <x:c r="J20" s="37"/>
-      <x:c r="K20" s="37"/>
+      <x:c r="I20" s="43"/>
+      <x:c r="J20" s="43"/>
+      <x:c r="K20" s="43"/>
       <x:c r="L20" s="37"/>
       <x:c r="M20" s="37"/>
       <x:c r="N20" s="37"/>
       <x:c r="O20" s="37"/>
-      <x:c r="P20" s="39"/>
-      <x:c r="Q20" s="39"/>
-      <x:c r="R20" s="37"/>
-      <x:c r="S20" s="38"/>
-      <x:c r="T20" s="38"/>
+      <x:c r="P20" s="37"/>
+      <x:c r="Q20" s="37"/>
+      <x:c r="R20" s="39"/>
+      <x:c r="S20" s="39"/>
+      <x:c r="T20" s="37"/>
       <x:c r="U20" s="38"/>
+      <x:c r="V20" s="38"/>
+      <x:c r="W20" s="38"/>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
       <x:c r="A21" s="37"/>
@@ -18511,22 +18563,24 @@
       <x:c r="C21" s="37"/>
       <x:c r="D21" s="37"/>
       <x:c r="E21" s="37"/>
-      <x:c r="F21" s="41"/>
-      <x:c r="G21" s="42"/>
+      <x:c r="F21" s="37"/>
+      <x:c r="G21" s="41"/>
       <x:c r="H21" s="42"/>
-      <x:c r="I21" s="42"/>
-      <x:c r="J21" s="37"/>
-      <x:c r="K21" s="37"/>
+      <x:c r="I21" s="43"/>
+      <x:c r="J21" s="43"/>
+      <x:c r="K21" s="43"/>
       <x:c r="L21" s="37"/>
       <x:c r="M21" s="37"/>
       <x:c r="N21" s="37"/>
       <x:c r="O21" s="37"/>
-      <x:c r="P21" s="39"/>
-      <x:c r="Q21" s="39"/>
-      <x:c r="R21" s="37"/>
-      <x:c r="S21" s="38"/>
-      <x:c r="T21" s="38"/>
+      <x:c r="P21" s="37"/>
+      <x:c r="Q21" s="37"/>
+      <x:c r="R21" s="39"/>
+      <x:c r="S21" s="39"/>
+      <x:c r="T21" s="37"/>
       <x:c r="U21" s="38"/>
+      <x:c r="V21" s="38"/>
+      <x:c r="W21" s="38"/>
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
       <x:c r="A22" s="37"/>
@@ -18534,22 +18588,24 @@
       <x:c r="C22" s="37"/>
       <x:c r="D22" s="37"/>
       <x:c r="E22" s="37"/>
-      <x:c r="F22" s="41"/>
-      <x:c r="G22" s="42"/>
+      <x:c r="F22" s="37"/>
+      <x:c r="G22" s="41"/>
       <x:c r="H22" s="42"/>
-      <x:c r="I22" s="42"/>
-      <x:c r="J22" s="37"/>
-      <x:c r="K22" s="37"/>
+      <x:c r="I22" s="43"/>
+      <x:c r="J22" s="43"/>
+      <x:c r="K22" s="43"/>
       <x:c r="L22" s="37"/>
       <x:c r="M22" s="37"/>
       <x:c r="N22" s="37"/>
       <x:c r="O22" s="37"/>
-      <x:c r="P22" s="39"/>
-      <x:c r="Q22" s="39"/>
-      <x:c r="R22" s="37"/>
-      <x:c r="S22" s="38"/>
-      <x:c r="T22" s="38"/>
+      <x:c r="P22" s="37"/>
+      <x:c r="Q22" s="37"/>
+      <x:c r="R22" s="39"/>
+      <x:c r="S22" s="39"/>
+      <x:c r="T22" s="37"/>
       <x:c r="U22" s="38"/>
+      <x:c r="V22" s="38"/>
+      <x:c r="W22" s="38"/>
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
       <x:c r="A23" s="37"/>
@@ -18557,22 +18613,24 @@
       <x:c r="C23" s="37"/>
       <x:c r="D23" s="37"/>
       <x:c r="E23" s="37"/>
-      <x:c r="F23" s="41"/>
-      <x:c r="G23" s="42"/>
+      <x:c r="F23" s="37"/>
+      <x:c r="G23" s="41"/>
       <x:c r="H23" s="42"/>
-      <x:c r="I23" s="42"/>
-      <x:c r="J23" s="37"/>
-      <x:c r="K23" s="37"/>
+      <x:c r="I23" s="43"/>
+      <x:c r="J23" s="43"/>
+      <x:c r="K23" s="43"/>
       <x:c r="L23" s="37"/>
       <x:c r="M23" s="37"/>
       <x:c r="N23" s="37"/>
       <x:c r="O23" s="37"/>
-      <x:c r="P23" s="39"/>
-      <x:c r="Q23" s="39"/>
-      <x:c r="R23" s="37"/>
-      <x:c r="S23" s="38"/>
-      <x:c r="T23" s="38"/>
+      <x:c r="P23" s="37"/>
+      <x:c r="Q23" s="37"/>
+      <x:c r="R23" s="39"/>
+      <x:c r="S23" s="39"/>
+      <x:c r="T23" s="37"/>
       <x:c r="U23" s="38"/>
+      <x:c r="V23" s="38"/>
+      <x:c r="W23" s="38"/>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
       <x:c r="A24" s="37"/>
@@ -18580,22 +18638,24 @@
       <x:c r="C24" s="37"/>
       <x:c r="D24" s="37"/>
       <x:c r="E24" s="37"/>
-      <x:c r="F24" s="41"/>
-      <x:c r="G24" s="42"/>
+      <x:c r="F24" s="37"/>
+      <x:c r="G24" s="41"/>
       <x:c r="H24" s="42"/>
-      <x:c r="I24" s="42"/>
-      <x:c r="J24" s="37"/>
-      <x:c r="K24" s="37"/>
+      <x:c r="I24" s="43"/>
+      <x:c r="J24" s="43"/>
+      <x:c r="K24" s="43"/>
       <x:c r="L24" s="37"/>
       <x:c r="M24" s="37"/>
       <x:c r="N24" s="37"/>
       <x:c r="O24" s="37"/>
-      <x:c r="P24" s="39"/>
-      <x:c r="Q24" s="39"/>
-      <x:c r="R24" s="37"/>
-      <x:c r="S24" s="38"/>
-      <x:c r="T24" s="38"/>
+      <x:c r="P24" s="37"/>
+      <x:c r="Q24" s="37"/>
+      <x:c r="R24" s="39"/>
+      <x:c r="S24" s="39"/>
+      <x:c r="T24" s="37"/>
       <x:c r="U24" s="38"/>
+      <x:c r="V24" s="38"/>
+      <x:c r="W24" s="38"/>
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
       <x:c r="A25" s="37"/>
@@ -18603,22 +18663,24 @@
       <x:c r="C25" s="37"/>
       <x:c r="D25" s="37"/>
       <x:c r="E25" s="37"/>
-      <x:c r="F25" s="41"/>
-      <x:c r="G25" s="42"/>
+      <x:c r="F25" s="37"/>
+      <x:c r="G25" s="41"/>
       <x:c r="H25" s="42"/>
-      <x:c r="I25" s="42"/>
-      <x:c r="J25" s="37"/>
-      <x:c r="K25" s="37"/>
+      <x:c r="I25" s="43"/>
+      <x:c r="J25" s="43"/>
+      <x:c r="K25" s="43"/>
       <x:c r="L25" s="37"/>
       <x:c r="M25" s="37"/>
       <x:c r="N25" s="37"/>
       <x:c r="O25" s="37"/>
-      <x:c r="P25" s="39"/>
-      <x:c r="Q25" s="39"/>
-      <x:c r="R25" s="37"/>
-      <x:c r="S25" s="38"/>
-      <x:c r="T25" s="38"/>
+      <x:c r="P25" s="37"/>
+      <x:c r="Q25" s="37"/>
+      <x:c r="R25" s="39"/>
+      <x:c r="S25" s="39"/>
+      <x:c r="T25" s="37"/>
       <x:c r="U25" s="38"/>
+      <x:c r="V25" s="38"/>
+      <x:c r="W25" s="38"/>
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
       <x:c r="A26" s="37"/>
@@ -18626,22 +18688,24 @@
       <x:c r="C26" s="37"/>
       <x:c r="D26" s="37"/>
       <x:c r="E26" s="37"/>
-      <x:c r="F26" s="41"/>
-      <x:c r="G26" s="42"/>
+      <x:c r="F26" s="37"/>
+      <x:c r="G26" s="41"/>
       <x:c r="H26" s="42"/>
-      <x:c r="I26" s="42"/>
-      <x:c r="J26" s="37"/>
-      <x:c r="K26" s="37"/>
+      <x:c r="I26" s="43"/>
+      <x:c r="J26" s="43"/>
+      <x:c r="K26" s="43"/>
       <x:c r="L26" s="37"/>
       <x:c r="M26" s="37"/>
       <x:c r="N26" s="37"/>
       <x:c r="O26" s="37"/>
-      <x:c r="P26" s="39"/>
-      <x:c r="Q26" s="39"/>
-      <x:c r="R26" s="37"/>
-      <x:c r="S26" s="38"/>
-      <x:c r="T26" s="38"/>
+      <x:c r="P26" s="37"/>
+      <x:c r="Q26" s="37"/>
+      <x:c r="R26" s="39"/>
+      <x:c r="S26" s="39"/>
+      <x:c r="T26" s="37"/>
       <x:c r="U26" s="38"/>
+      <x:c r="V26" s="38"/>
+      <x:c r="W26" s="38"/>
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
       <x:c r="A27" s="37"/>
@@ -18649,22 +18713,24 @@
       <x:c r="C27" s="37"/>
       <x:c r="D27" s="37"/>
       <x:c r="E27" s="37"/>
-      <x:c r="F27" s="41"/>
-      <x:c r="G27" s="42"/>
+      <x:c r="F27" s="37"/>
+      <x:c r="G27" s="41"/>
       <x:c r="H27" s="42"/>
-      <x:c r="I27" s="42"/>
-      <x:c r="J27" s="37"/>
-      <x:c r="K27" s="37"/>
+      <x:c r="I27" s="43"/>
+      <x:c r="J27" s="43"/>
+      <x:c r="K27" s="43"/>
       <x:c r="L27" s="37"/>
       <x:c r="M27" s="37"/>
       <x:c r="N27" s="37"/>
       <x:c r="O27" s="37"/>
-      <x:c r="P27" s="39"/>
-      <x:c r="Q27" s="39"/>
-      <x:c r="R27" s="37"/>
-      <x:c r="S27" s="38"/>
-      <x:c r="T27" s="38"/>
+      <x:c r="P27" s="37"/>
+      <x:c r="Q27" s="37"/>
+      <x:c r="R27" s="39"/>
+      <x:c r="S27" s="39"/>
+      <x:c r="T27" s="37"/>
       <x:c r="U27" s="38"/>
+      <x:c r="V27" s="38"/>
+      <x:c r="W27" s="38"/>
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
       <x:c r="A28" s="37"/>
@@ -18672,22 +18738,24 @@
       <x:c r="C28" s="37"/>
       <x:c r="D28" s="37"/>
       <x:c r="E28" s="37"/>
-      <x:c r="F28" s="41"/>
-      <x:c r="G28" s="42"/>
+      <x:c r="F28" s="37"/>
+      <x:c r="G28" s="41"/>
       <x:c r="H28" s="42"/>
-      <x:c r="I28" s="42"/>
-      <x:c r="J28" s="37"/>
-      <x:c r="K28" s="37"/>
+      <x:c r="I28" s="43"/>
+      <x:c r="J28" s="43"/>
+      <x:c r="K28" s="43"/>
       <x:c r="L28" s="37"/>
       <x:c r="M28" s="37"/>
       <x:c r="N28" s="37"/>
       <x:c r="O28" s="37"/>
-      <x:c r="P28" s="39"/>
-      <x:c r="Q28" s="39"/>
-      <x:c r="R28" s="37"/>
-      <x:c r="S28" s="38"/>
-      <x:c r="T28" s="38"/>
+      <x:c r="P28" s="37"/>
+      <x:c r="Q28" s="37"/>
+      <x:c r="R28" s="39"/>
+      <x:c r="S28" s="39"/>
+      <x:c r="T28" s="37"/>
       <x:c r="U28" s="38"/>
+      <x:c r="V28" s="38"/>
+      <x:c r="W28" s="38"/>
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
       <x:c r="A29" s="37"/>
@@ -18695,22 +18763,24 @@
       <x:c r="C29" s="37"/>
       <x:c r="D29" s="37"/>
       <x:c r="E29" s="37"/>
-      <x:c r="F29" s="41"/>
-      <x:c r="G29" s="42"/>
+      <x:c r="F29" s="37"/>
+      <x:c r="G29" s="41"/>
       <x:c r="H29" s="42"/>
-      <x:c r="I29" s="42"/>
-      <x:c r="J29" s="37"/>
-      <x:c r="K29" s="37"/>
+      <x:c r="I29" s="43"/>
+      <x:c r="J29" s="43"/>
+      <x:c r="K29" s="43"/>
       <x:c r="L29" s="37"/>
       <x:c r="M29" s="37"/>
       <x:c r="N29" s="37"/>
       <x:c r="O29" s="37"/>
-      <x:c r="P29" s="39"/>
-      <x:c r="Q29" s="39"/>
-      <x:c r="R29" s="37"/>
-      <x:c r="S29" s="38"/>
-      <x:c r="T29" s="38"/>
+      <x:c r="P29" s="37"/>
+      <x:c r="Q29" s="37"/>
+      <x:c r="R29" s="39"/>
+      <x:c r="S29" s="39"/>
+      <x:c r="T29" s="37"/>
       <x:c r="U29" s="38"/>
+      <x:c r="V29" s="38"/>
+      <x:c r="W29" s="38"/>
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
       <x:c r="A30" s="37"/>
@@ -18718,22 +18788,24 @@
       <x:c r="C30" s="37"/>
       <x:c r="D30" s="37"/>
       <x:c r="E30" s="37"/>
-      <x:c r="F30" s="41"/>
-      <x:c r="G30" s="42"/>
+      <x:c r="F30" s="37"/>
+      <x:c r="G30" s="41"/>
       <x:c r="H30" s="42"/>
-      <x:c r="I30" s="42"/>
-      <x:c r="J30" s="37"/>
-      <x:c r="K30" s="37"/>
+      <x:c r="I30" s="43"/>
+      <x:c r="J30" s="43"/>
+      <x:c r="K30" s="43"/>
       <x:c r="L30" s="37"/>
       <x:c r="M30" s="37"/>
       <x:c r="N30" s="37"/>
       <x:c r="O30" s="37"/>
-      <x:c r="P30" s="39"/>
-      <x:c r="Q30" s="39"/>
-      <x:c r="R30" s="37"/>
-      <x:c r="S30" s="38"/>
-      <x:c r="T30" s="38"/>
+      <x:c r="P30" s="37"/>
+      <x:c r="Q30" s="37"/>
+      <x:c r="R30" s="39"/>
+      <x:c r="S30" s="39"/>
+      <x:c r="T30" s="37"/>
       <x:c r="U30" s="38"/>
+      <x:c r="V30" s="38"/>
+      <x:c r="W30" s="38"/>
     </x:row>
     <x:row r="31" ht="24" customHeight="1">
       <x:c r="A31" s="37"/>
@@ -18741,22 +18813,24 @@
       <x:c r="C31" s="37"/>
       <x:c r="D31" s="37"/>
       <x:c r="E31" s="37"/>
-      <x:c r="F31" s="41"/>
-      <x:c r="G31" s="42"/>
+      <x:c r="F31" s="37"/>
+      <x:c r="G31" s="41"/>
       <x:c r="H31" s="42"/>
-      <x:c r="I31" s="42"/>
-      <x:c r="J31" s="37"/>
-      <x:c r="K31" s="37"/>
+      <x:c r="I31" s="43"/>
+      <x:c r="J31" s="43"/>
+      <x:c r="K31" s="43"/>
       <x:c r="L31" s="37"/>
       <x:c r="M31" s="37"/>
       <x:c r="N31" s="37"/>
       <x:c r="O31" s="37"/>
-      <x:c r="P31" s="39"/>
-      <x:c r="Q31" s="39"/>
-      <x:c r="R31" s="37"/>
-      <x:c r="S31" s="38"/>
-      <x:c r="T31" s="38"/>
+      <x:c r="P31" s="37"/>
+      <x:c r="Q31" s="37"/>
+      <x:c r="R31" s="39"/>
+      <x:c r="S31" s="39"/>
+      <x:c r="T31" s="37"/>
       <x:c r="U31" s="38"/>
+      <x:c r="V31" s="38"/>
+      <x:c r="W31" s="38"/>
     </x:row>
     <x:row r="32" ht="24" customHeight="1">
       <x:c r="A32" s="37"/>
@@ -18764,22 +18838,24 @@
       <x:c r="C32" s="37"/>
       <x:c r="D32" s="37"/>
       <x:c r="E32" s="37"/>
-      <x:c r="F32" s="41"/>
-      <x:c r="G32" s="42"/>
+      <x:c r="F32" s="37"/>
+      <x:c r="G32" s="41"/>
       <x:c r="H32" s="42"/>
-      <x:c r="I32" s="42"/>
-      <x:c r="J32" s="37"/>
-      <x:c r="K32" s="37"/>
+      <x:c r="I32" s="43"/>
+      <x:c r="J32" s="43"/>
+      <x:c r="K32" s="43"/>
       <x:c r="L32" s="37"/>
       <x:c r="M32" s="37"/>
       <x:c r="N32" s="37"/>
       <x:c r="O32" s="37"/>
-      <x:c r="P32" s="39"/>
-      <x:c r="Q32" s="39"/>
-      <x:c r="R32" s="37"/>
-      <x:c r="S32" s="38"/>
-      <x:c r="T32" s="38"/>
+      <x:c r="P32" s="37"/>
+      <x:c r="Q32" s="37"/>
+      <x:c r="R32" s="39"/>
+      <x:c r="S32" s="39"/>
+      <x:c r="T32" s="37"/>
       <x:c r="U32" s="38"/>
+      <x:c r="V32" s="38"/>
+      <x:c r="W32" s="38"/>
     </x:row>
     <x:row r="33" ht="24" customHeight="1">
       <x:c r="A33" s="37"/>
@@ -18787,22 +18863,24 @@
       <x:c r="C33" s="37"/>
       <x:c r="D33" s="37"/>
       <x:c r="E33" s="37"/>
-      <x:c r="F33" s="41"/>
-      <x:c r="G33" s="42"/>
+      <x:c r="F33" s="37"/>
+      <x:c r="G33" s="41"/>
       <x:c r="H33" s="42"/>
-      <x:c r="I33" s="42"/>
-      <x:c r="J33" s="37"/>
-      <x:c r="K33" s="37"/>
+      <x:c r="I33" s="43"/>
+      <x:c r="J33" s="43"/>
+      <x:c r="K33" s="43"/>
       <x:c r="L33" s="37"/>
       <x:c r="M33" s="37"/>
       <x:c r="N33" s="37"/>
       <x:c r="O33" s="37"/>
-      <x:c r="P33" s="39"/>
-      <x:c r="Q33" s="39"/>
-      <x:c r="R33" s="37"/>
-      <x:c r="S33" s="38"/>
-      <x:c r="T33" s="38"/>
+      <x:c r="P33" s="37"/>
+      <x:c r="Q33" s="37"/>
+      <x:c r="R33" s="39"/>
+      <x:c r="S33" s="39"/>
+      <x:c r="T33" s="37"/>
       <x:c r="U33" s="38"/>
+      <x:c r="V33" s="38"/>
+      <x:c r="W33" s="38"/>
     </x:row>
     <x:row r="34" ht="24" customHeight="1">
       <x:c r="A34" s="37"/>
@@ -18810,22 +18888,24 @@
       <x:c r="C34" s="37"/>
       <x:c r="D34" s="37"/>
       <x:c r="E34" s="37"/>
-      <x:c r="F34" s="41"/>
-      <x:c r="G34" s="42"/>
+      <x:c r="F34" s="37"/>
+      <x:c r="G34" s="41"/>
       <x:c r="H34" s="42"/>
-      <x:c r="I34" s="42"/>
-      <x:c r="J34" s="37"/>
-      <x:c r="K34" s="37"/>
+      <x:c r="I34" s="43"/>
+      <x:c r="J34" s="43"/>
+      <x:c r="K34" s="43"/>
       <x:c r="L34" s="37"/>
       <x:c r="M34" s="37"/>
       <x:c r="N34" s="37"/>
       <x:c r="O34" s="37"/>
-      <x:c r="P34" s="39"/>
-      <x:c r="Q34" s="39"/>
-      <x:c r="R34" s="37"/>
-      <x:c r="S34" s="38"/>
-      <x:c r="T34" s="38"/>
+      <x:c r="P34" s="37"/>
+      <x:c r="Q34" s="37"/>
+      <x:c r="R34" s="39"/>
+      <x:c r="S34" s="39"/>
+      <x:c r="T34" s="37"/>
       <x:c r="U34" s="38"/>
+      <x:c r="V34" s="38"/>
+      <x:c r="W34" s="38"/>
     </x:row>
     <x:row r="35" ht="24" customHeight="1">
       <x:c r="A35" s="37"/>
@@ -18833,22 +18913,24 @@
       <x:c r="C35" s="37"/>
       <x:c r="D35" s="37"/>
       <x:c r="E35" s="37"/>
-      <x:c r="F35" s="41"/>
-      <x:c r="G35" s="42"/>
+      <x:c r="F35" s="37"/>
+      <x:c r="G35" s="41"/>
       <x:c r="H35" s="42"/>
-      <x:c r="I35" s="42"/>
-      <x:c r="J35" s="37"/>
-      <x:c r="K35" s="37"/>
+      <x:c r="I35" s="43"/>
+      <x:c r="J35" s="43"/>
+      <x:c r="K35" s="43"/>
       <x:c r="L35" s="37"/>
       <x:c r="M35" s="37"/>
       <x:c r="N35" s="37"/>
       <x:c r="O35" s="37"/>
-      <x:c r="P35" s="39"/>
-      <x:c r="Q35" s="39"/>
-      <x:c r="R35" s="37"/>
-      <x:c r="S35" s="38"/>
-      <x:c r="T35" s="38"/>
+      <x:c r="P35" s="37"/>
+      <x:c r="Q35" s="37"/>
+      <x:c r="R35" s="39"/>
+      <x:c r="S35" s="39"/>
+      <x:c r="T35" s="37"/>
       <x:c r="U35" s="38"/>
+      <x:c r="V35" s="38"/>
+      <x:c r="W35" s="38"/>
     </x:row>
     <x:row r="36" ht="24" customHeight="1">
       <x:c r="A36" s="37"/>
@@ -18856,22 +18938,24 @@
       <x:c r="C36" s="37"/>
       <x:c r="D36" s="37"/>
       <x:c r="E36" s="37"/>
-      <x:c r="F36" s="41"/>
-      <x:c r="G36" s="42"/>
+      <x:c r="F36" s="37"/>
+      <x:c r="G36" s="41"/>
       <x:c r="H36" s="42"/>
-      <x:c r="I36" s="42"/>
-      <x:c r="J36" s="37"/>
-      <x:c r="K36" s="37"/>
+      <x:c r="I36" s="43"/>
+      <x:c r="J36" s="43"/>
+      <x:c r="K36" s="43"/>
       <x:c r="L36" s="37"/>
       <x:c r="M36" s="37"/>
       <x:c r="N36" s="37"/>
       <x:c r="O36" s="37"/>
-      <x:c r="P36" s="39"/>
-      <x:c r="Q36" s="39"/>
-      <x:c r="R36" s="37"/>
-      <x:c r="S36" s="38"/>
-      <x:c r="T36" s="38"/>
+      <x:c r="P36" s="37"/>
+      <x:c r="Q36" s="37"/>
+      <x:c r="R36" s="39"/>
+      <x:c r="S36" s="39"/>
+      <x:c r="T36" s="37"/>
       <x:c r="U36" s="38"/>
+      <x:c r="V36" s="38"/>
+      <x:c r="W36" s="38"/>
     </x:row>
     <x:row r="37" ht="24" customHeight="1">
       <x:c r="A37" s="37"/>
@@ -18879,22 +18963,24 @@
       <x:c r="C37" s="37"/>
       <x:c r="D37" s="37"/>
       <x:c r="E37" s="37"/>
-      <x:c r="F37" s="41"/>
-      <x:c r="G37" s="42"/>
+      <x:c r="F37" s="37"/>
+      <x:c r="G37" s="41"/>
       <x:c r="H37" s="42"/>
-      <x:c r="I37" s="42"/>
-      <x:c r="J37" s="37"/>
-      <x:c r="K37" s="37"/>
+      <x:c r="I37" s="43"/>
+      <x:c r="J37" s="43"/>
+      <x:c r="K37" s="43"/>
       <x:c r="L37" s="37"/>
       <x:c r="M37" s="37"/>
       <x:c r="N37" s="37"/>
       <x:c r="O37" s="37"/>
-      <x:c r="P37" s="39"/>
-      <x:c r="Q37" s="39"/>
-      <x:c r="R37" s="37"/>
-      <x:c r="S37" s="38"/>
-      <x:c r="T37" s="38"/>
+      <x:c r="P37" s="37"/>
+      <x:c r="Q37" s="37"/>
+      <x:c r="R37" s="39"/>
+      <x:c r="S37" s="39"/>
+      <x:c r="T37" s="37"/>
       <x:c r="U37" s="38"/>
+      <x:c r="V37" s="38"/>
+      <x:c r="W37" s="38"/>
     </x:row>
     <x:row r="38" ht="24" customHeight="1">
       <x:c r="A38" s="37"/>
@@ -18902,22 +18988,24 @@
       <x:c r="C38" s="37"/>
       <x:c r="D38" s="37"/>
       <x:c r="E38" s="37"/>
-      <x:c r="F38" s="41"/>
-      <x:c r="G38" s="42"/>
+      <x:c r="F38" s="37"/>
+      <x:c r="G38" s="41"/>
       <x:c r="H38" s="42"/>
-      <x:c r="I38" s="42"/>
-      <x:c r="J38" s="37"/>
-      <x:c r="K38" s="37"/>
+      <x:c r="I38" s="43"/>
+      <x:c r="J38" s="43"/>
+      <x:c r="K38" s="43"/>
       <x:c r="L38" s="37"/>
       <x:c r="M38" s="37"/>
       <x:c r="N38" s="37"/>
       <x:c r="O38" s="37"/>
-      <x:c r="P38" s="39"/>
-      <x:c r="Q38" s="39"/>
-      <x:c r="R38" s="37"/>
-      <x:c r="S38" s="38"/>
-      <x:c r="T38" s="38"/>
+      <x:c r="P38" s="37"/>
+      <x:c r="Q38" s="37"/>
+      <x:c r="R38" s="39"/>
+      <x:c r="S38" s="39"/>
+      <x:c r="T38" s="37"/>
       <x:c r="U38" s="38"/>
+      <x:c r="V38" s="38"/>
+      <x:c r="W38" s="38"/>
     </x:row>
     <x:row r="39" ht="24" customHeight="1">
       <x:c r="A39" s="37"/>
@@ -18925,22 +19013,24 @@
       <x:c r="C39" s="37"/>
       <x:c r="D39" s="37"/>
       <x:c r="E39" s="37"/>
-      <x:c r="F39" s="41"/>
-      <x:c r="G39" s="42"/>
+      <x:c r="F39" s="37"/>
+      <x:c r="G39" s="41"/>
       <x:c r="H39" s="42"/>
-      <x:c r="I39" s="42"/>
-      <x:c r="J39" s="37"/>
-      <x:c r="K39" s="37"/>
+      <x:c r="I39" s="43"/>
+      <x:c r="J39" s="43"/>
+      <x:c r="K39" s="43"/>
       <x:c r="L39" s="37"/>
       <x:c r="M39" s="37"/>
       <x:c r="N39" s="37"/>
       <x:c r="O39" s="37"/>
-      <x:c r="P39" s="39"/>
-      <x:c r="Q39" s="39"/>
-      <x:c r="R39" s="37"/>
-      <x:c r="S39" s="38"/>
-      <x:c r="T39" s="38"/>
+      <x:c r="P39" s="37"/>
+      <x:c r="Q39" s="37"/>
+      <x:c r="R39" s="39"/>
+      <x:c r="S39" s="39"/>
+      <x:c r="T39" s="37"/>
       <x:c r="U39" s="38"/>
+      <x:c r="V39" s="38"/>
+      <x:c r="W39" s="38"/>
     </x:row>
     <x:row r="40" ht="24" customHeight="1">
       <x:c r="A40" s="37"/>
@@ -18948,22 +19038,24 @@
       <x:c r="C40" s="37"/>
       <x:c r="D40" s="37"/>
       <x:c r="E40" s="37"/>
-      <x:c r="F40" s="41"/>
-      <x:c r="G40" s="42"/>
+      <x:c r="F40" s="37"/>
+      <x:c r="G40" s="41"/>
       <x:c r="H40" s="42"/>
-      <x:c r="I40" s="42"/>
-      <x:c r="J40" s="37"/>
-      <x:c r="K40" s="37"/>
+      <x:c r="I40" s="43"/>
+      <x:c r="J40" s="43"/>
+      <x:c r="K40" s="43"/>
       <x:c r="L40" s="37"/>
       <x:c r="M40" s="37"/>
       <x:c r="N40" s="37"/>
       <x:c r="O40" s="37"/>
-      <x:c r="P40" s="39"/>
-      <x:c r="Q40" s="39"/>
-      <x:c r="R40" s="37"/>
-      <x:c r="S40" s="38"/>
-      <x:c r="T40" s="38"/>
+      <x:c r="P40" s="37"/>
+      <x:c r="Q40" s="37"/>
+      <x:c r="R40" s="39"/>
+      <x:c r="S40" s="39"/>
+      <x:c r="T40" s="37"/>
       <x:c r="U40" s="38"/>
+      <x:c r="V40" s="38"/>
+      <x:c r="W40" s="38"/>
     </x:row>
     <x:row r="41" ht="24" customHeight="1">
       <x:c r="A41" s="37"/>
@@ -18971,22 +19063,24 @@
       <x:c r="C41" s="37"/>
       <x:c r="D41" s="37"/>
       <x:c r="E41" s="37"/>
-      <x:c r="F41" s="41"/>
-      <x:c r="G41" s="42"/>
+      <x:c r="F41" s="37"/>
+      <x:c r="G41" s="41"/>
       <x:c r="H41" s="42"/>
-      <x:c r="I41" s="42"/>
-      <x:c r="J41" s="37"/>
-      <x:c r="K41" s="37"/>
+      <x:c r="I41" s="43"/>
+      <x:c r="J41" s="43"/>
+      <x:c r="K41" s="43"/>
       <x:c r="L41" s="37"/>
       <x:c r="M41" s="37"/>
       <x:c r="N41" s="37"/>
       <x:c r="O41" s="37"/>
-      <x:c r="P41" s="39"/>
-      <x:c r="Q41" s="39"/>
-      <x:c r="R41" s="37"/>
-      <x:c r="S41" s="38"/>
-      <x:c r="T41" s="38"/>
+      <x:c r="P41" s="37"/>
+      <x:c r="Q41" s="37"/>
+      <x:c r="R41" s="39"/>
+      <x:c r="S41" s="39"/>
+      <x:c r="T41" s="37"/>
       <x:c r="U41" s="38"/>
+      <x:c r="V41" s="38"/>
+      <x:c r="W41" s="38"/>
     </x:row>
     <x:row r="42" ht="24" customHeight="1">
       <x:c r="A42" s="37"/>
@@ -18994,22 +19088,24 @@
       <x:c r="C42" s="37"/>
       <x:c r="D42" s="37"/>
       <x:c r="E42" s="37"/>
-      <x:c r="F42" s="41"/>
-      <x:c r="G42" s="42"/>
+      <x:c r="F42" s="37"/>
+      <x:c r="G42" s="41"/>
       <x:c r="H42" s="42"/>
-      <x:c r="I42" s="42"/>
-      <x:c r="J42" s="37"/>
-      <x:c r="K42" s="37"/>
+      <x:c r="I42" s="43"/>
+      <x:c r="J42" s="43"/>
+      <x:c r="K42" s="43"/>
       <x:c r="L42" s="37"/>
       <x:c r="M42" s="37"/>
       <x:c r="N42" s="37"/>
       <x:c r="O42" s="37"/>
-      <x:c r="P42" s="39"/>
-      <x:c r="Q42" s="39"/>
-      <x:c r="R42" s="37"/>
-      <x:c r="S42" s="38"/>
-      <x:c r="T42" s="38"/>
+      <x:c r="P42" s="37"/>
+      <x:c r="Q42" s="37"/>
+      <x:c r="R42" s="39"/>
+      <x:c r="S42" s="39"/>
+      <x:c r="T42" s="37"/>
       <x:c r="U42" s="38"/>
+      <x:c r="V42" s="38"/>
+      <x:c r="W42" s="38"/>
     </x:row>
     <x:row r="43" ht="24" customHeight="1">
       <x:c r="A43" s="37"/>
@@ -19017,22 +19113,24 @@
       <x:c r="C43" s="37"/>
       <x:c r="D43" s="37"/>
       <x:c r="E43" s="37"/>
-      <x:c r="F43" s="41"/>
-      <x:c r="G43" s="42"/>
+      <x:c r="F43" s="37"/>
+      <x:c r="G43" s="41"/>
       <x:c r="H43" s="42"/>
-      <x:c r="I43" s="42"/>
-      <x:c r="J43" s="37"/>
-      <x:c r="K43" s="37"/>
+      <x:c r="I43" s="43"/>
+      <x:c r="J43" s="43"/>
+      <x:c r="K43" s="43"/>
       <x:c r="L43" s="37"/>
       <x:c r="M43" s="37"/>
       <x:c r="N43" s="37"/>
       <x:c r="O43" s="37"/>
-      <x:c r="P43" s="39"/>
-      <x:c r="Q43" s="39"/>
-      <x:c r="R43" s="37"/>
-      <x:c r="S43" s="38"/>
-      <x:c r="T43" s="38"/>
+      <x:c r="P43" s="37"/>
+      <x:c r="Q43" s="37"/>
+      <x:c r="R43" s="39"/>
+      <x:c r="S43" s="39"/>
+      <x:c r="T43" s="37"/>
       <x:c r="U43" s="38"/>
+      <x:c r="V43" s="38"/>
+      <x:c r="W43" s="38"/>
     </x:row>
     <x:row r="44" ht="24" customHeight="1">
       <x:c r="A44" s="37"/>
@@ -19040,22 +19138,24 @@
       <x:c r="C44" s="37"/>
       <x:c r="D44" s="37"/>
       <x:c r="E44" s="37"/>
-      <x:c r="F44" s="41"/>
-      <x:c r="G44" s="42"/>
+      <x:c r="F44" s="37"/>
+      <x:c r="G44" s="41"/>
       <x:c r="H44" s="42"/>
-      <x:c r="I44" s="42"/>
-      <x:c r="J44" s="37"/>
-      <x:c r="K44" s="37"/>
+      <x:c r="I44" s="43"/>
+      <x:c r="J44" s="43"/>
+      <x:c r="K44" s="43"/>
       <x:c r="L44" s="37"/>
       <x:c r="M44" s="37"/>
       <x:c r="N44" s="37"/>
       <x:c r="O44" s="37"/>
-      <x:c r="P44" s="39"/>
-      <x:c r="Q44" s="39"/>
-      <x:c r="R44" s="37"/>
-      <x:c r="S44" s="38"/>
-      <x:c r="T44" s="38"/>
+      <x:c r="P44" s="37"/>
+      <x:c r="Q44" s="37"/>
+      <x:c r="R44" s="39"/>
+      <x:c r="S44" s="39"/>
+      <x:c r="T44" s="37"/>
       <x:c r="U44" s="38"/>
+      <x:c r="V44" s="38"/>
+      <x:c r="W44" s="38"/>
     </x:row>
     <x:row r="45" ht="24" customHeight="1">
       <x:c r="A45" s="37"/>
@@ -19063,22 +19163,24 @@
       <x:c r="C45" s="37"/>
       <x:c r="D45" s="37"/>
       <x:c r="E45" s="37"/>
-      <x:c r="F45" s="41"/>
-      <x:c r="G45" s="42"/>
+      <x:c r="F45" s="37"/>
+      <x:c r="G45" s="41"/>
       <x:c r="H45" s="42"/>
-      <x:c r="I45" s="42"/>
-      <x:c r="J45" s="37"/>
-      <x:c r="K45" s="37"/>
+      <x:c r="I45" s="43"/>
+      <x:c r="J45" s="43"/>
+      <x:c r="K45" s="43"/>
       <x:c r="L45" s="37"/>
       <x:c r="M45" s="37"/>
       <x:c r="N45" s="37"/>
       <x:c r="O45" s="37"/>
-      <x:c r="P45" s="39"/>
-      <x:c r="Q45" s="39"/>
-      <x:c r="R45" s="37"/>
-      <x:c r="S45" s="38"/>
-      <x:c r="T45" s="38"/>
+      <x:c r="P45" s="37"/>
+      <x:c r="Q45" s="37"/>
+      <x:c r="R45" s="39"/>
+      <x:c r="S45" s="39"/>
+      <x:c r="T45" s="37"/>
       <x:c r="U45" s="38"/>
+      <x:c r="V45" s="38"/>
+      <x:c r="W45" s="38"/>
     </x:row>
     <x:row r="46" ht="24" customHeight="1">
       <x:c r="A46" s="37"/>
@@ -19086,22 +19188,24 @@
       <x:c r="C46" s="37"/>
       <x:c r="D46" s="37"/>
       <x:c r="E46" s="37"/>
-      <x:c r="F46" s="41"/>
-      <x:c r="G46" s="42"/>
+      <x:c r="F46" s="37"/>
+      <x:c r="G46" s="41"/>
       <x:c r="H46" s="42"/>
-      <x:c r="I46" s="42"/>
-      <x:c r="J46" s="37"/>
-      <x:c r="K46" s="37"/>
+      <x:c r="I46" s="43"/>
+      <x:c r="J46" s="43"/>
+      <x:c r="K46" s="43"/>
       <x:c r="L46" s="37"/>
       <x:c r="M46" s="37"/>
       <x:c r="N46" s="37"/>
       <x:c r="O46" s="37"/>
-      <x:c r="P46" s="39"/>
-      <x:c r="Q46" s="39"/>
-      <x:c r="R46" s="37"/>
-      <x:c r="S46" s="38"/>
-      <x:c r="T46" s="38"/>
+      <x:c r="P46" s="37"/>
+      <x:c r="Q46" s="37"/>
+      <x:c r="R46" s="39"/>
+      <x:c r="S46" s="39"/>
+      <x:c r="T46" s="37"/>
       <x:c r="U46" s="38"/>
+      <x:c r="V46" s="38"/>
+      <x:c r="W46" s="38"/>
     </x:row>
     <x:row r="47" ht="24" customHeight="1">
       <x:c r="A47" s="37"/>
@@ -19109,22 +19213,24 @@
       <x:c r="C47" s="37"/>
       <x:c r="D47" s="37"/>
       <x:c r="E47" s="37"/>
-      <x:c r="F47" s="41"/>
-      <x:c r="G47" s="42"/>
+      <x:c r="F47" s="37"/>
+      <x:c r="G47" s="41"/>
       <x:c r="H47" s="42"/>
-      <x:c r="I47" s="42"/>
-      <x:c r="J47" s="37"/>
-      <x:c r="K47" s="37"/>
+      <x:c r="I47" s="43"/>
+      <x:c r="J47" s="43"/>
+      <x:c r="K47" s="43"/>
       <x:c r="L47" s="37"/>
       <x:c r="M47" s="37"/>
       <x:c r="N47" s="37"/>
       <x:c r="O47" s="37"/>
-      <x:c r="P47" s="39"/>
-      <x:c r="Q47" s="39"/>
-      <x:c r="R47" s="37"/>
-      <x:c r="S47" s="38"/>
-      <x:c r="T47" s="38"/>
+      <x:c r="P47" s="37"/>
+      <x:c r="Q47" s="37"/>
+      <x:c r="R47" s="39"/>
+      <x:c r="S47" s="39"/>
+      <x:c r="T47" s="37"/>
       <x:c r="U47" s="38"/>
+      <x:c r="V47" s="38"/>
+      <x:c r="W47" s="38"/>
     </x:row>
     <x:row r="48" ht="24" customHeight="1">
       <x:c r="A48" s="37"/>
@@ -19132,22 +19238,24 @@
       <x:c r="C48" s="37"/>
       <x:c r="D48" s="37"/>
       <x:c r="E48" s="37"/>
-      <x:c r="F48" s="41"/>
-      <x:c r="G48" s="42"/>
+      <x:c r="F48" s="37"/>
+      <x:c r="G48" s="41"/>
       <x:c r="H48" s="42"/>
-      <x:c r="I48" s="42"/>
-      <x:c r="J48" s="37"/>
-      <x:c r="K48" s="37"/>
+      <x:c r="I48" s="43"/>
+      <x:c r="J48" s="43"/>
+      <x:c r="K48" s="43"/>
       <x:c r="L48" s="37"/>
       <x:c r="M48" s="37"/>
       <x:c r="N48" s="37"/>
       <x:c r="O48" s="37"/>
-      <x:c r="P48" s="39"/>
-      <x:c r="Q48" s="39"/>
-      <x:c r="R48" s="37"/>
-      <x:c r="S48" s="38"/>
-      <x:c r="T48" s="38"/>
+      <x:c r="P48" s="37"/>
+      <x:c r="Q48" s="37"/>
+      <x:c r="R48" s="39"/>
+      <x:c r="S48" s="39"/>
+      <x:c r="T48" s="37"/>
       <x:c r="U48" s="38"/>
+      <x:c r="V48" s="38"/>
+      <x:c r="W48" s="38"/>
     </x:row>
     <x:row r="49" ht="24" customHeight="1">
       <x:c r="A49" s="37"/>
@@ -19155,22 +19263,24 @@
       <x:c r="C49" s="37"/>
       <x:c r="D49" s="37"/>
       <x:c r="E49" s="37"/>
-      <x:c r="F49" s="41"/>
-      <x:c r="G49" s="42"/>
+      <x:c r="F49" s="37"/>
+      <x:c r="G49" s="41"/>
       <x:c r="H49" s="42"/>
-      <x:c r="I49" s="42"/>
-      <x:c r="J49" s="37"/>
-      <x:c r="K49" s="37"/>
+      <x:c r="I49" s="43"/>
+      <x:c r="J49" s="43"/>
+      <x:c r="K49" s="43"/>
       <x:c r="L49" s="37"/>
       <x:c r="M49" s="37"/>
       <x:c r="N49" s="37"/>
       <x:c r="O49" s="37"/>
-      <x:c r="P49" s="39"/>
-      <x:c r="Q49" s="39"/>
-      <x:c r="R49" s="37"/>
-      <x:c r="S49" s="38"/>
-      <x:c r="T49" s="38"/>
+      <x:c r="P49" s="37"/>
+      <x:c r="Q49" s="37"/>
+      <x:c r="R49" s="39"/>
+      <x:c r="S49" s="39"/>
+      <x:c r="T49" s="37"/>
       <x:c r="U49" s="38"/>
+      <x:c r="V49" s="38"/>
+      <x:c r="W49" s="38"/>
     </x:row>
     <x:row r="50" ht="24" customHeight="1">
       <x:c r="A50" s="37"/>
@@ -19178,22 +19288,24 @@
       <x:c r="C50" s="37"/>
       <x:c r="D50" s="37"/>
       <x:c r="E50" s="37"/>
-      <x:c r="F50" s="41"/>
-      <x:c r="G50" s="42"/>
+      <x:c r="F50" s="37"/>
+      <x:c r="G50" s="41"/>
       <x:c r="H50" s="42"/>
-      <x:c r="I50" s="42"/>
-      <x:c r="J50" s="37"/>
-      <x:c r="K50" s="37"/>
+      <x:c r="I50" s="43"/>
+      <x:c r="J50" s="43"/>
+      <x:c r="K50" s="43"/>
       <x:c r="L50" s="37"/>
       <x:c r="M50" s="37"/>
       <x:c r="N50" s="37"/>
       <x:c r="O50" s="37"/>
-      <x:c r="P50" s="39"/>
-      <x:c r="Q50" s="39"/>
-      <x:c r="R50" s="37"/>
-      <x:c r="S50" s="38"/>
-      <x:c r="T50" s="38"/>
+      <x:c r="P50" s="37"/>
+      <x:c r="Q50" s="37"/>
+      <x:c r="R50" s="39"/>
+      <x:c r="S50" s="39"/>
+      <x:c r="T50" s="37"/>
       <x:c r="U50" s="38"/>
+      <x:c r="V50" s="38"/>
+      <x:c r="W50" s="38"/>
     </x:row>
     <x:row r="51" ht="24" customHeight="1">
       <x:c r="A51" s="37"/>
@@ -19201,22 +19313,24 @@
       <x:c r="C51" s="37"/>
       <x:c r="D51" s="37"/>
       <x:c r="E51" s="37"/>
-      <x:c r="F51" s="41"/>
-      <x:c r="G51" s="42"/>
+      <x:c r="F51" s="37"/>
+      <x:c r="G51" s="41"/>
       <x:c r="H51" s="42"/>
-      <x:c r="I51" s="42"/>
-      <x:c r="J51" s="37"/>
-      <x:c r="K51" s="37"/>
+      <x:c r="I51" s="43"/>
+      <x:c r="J51" s="43"/>
+      <x:c r="K51" s="43"/>
       <x:c r="L51" s="37"/>
       <x:c r="M51" s="37"/>
       <x:c r="N51" s="37"/>
       <x:c r="O51" s="37"/>
-      <x:c r="P51" s="39"/>
-      <x:c r="Q51" s="39"/>
-      <x:c r="R51" s="37"/>
-      <x:c r="S51" s="38"/>
-      <x:c r="T51" s="38"/>
+      <x:c r="P51" s="37"/>
+      <x:c r="Q51" s="37"/>
+      <x:c r="R51" s="39"/>
+      <x:c r="S51" s="39"/>
+      <x:c r="T51" s="37"/>
       <x:c r="U51" s="38"/>
+      <x:c r="V51" s="38"/>
+      <x:c r="W51" s="38"/>
     </x:row>
     <x:row r="52" ht="24" customHeight="1">
       <x:c r="A52" s="37"/>
@@ -19224,22 +19338,24 @@
       <x:c r="C52" s="37"/>
       <x:c r="D52" s="37"/>
       <x:c r="E52" s="37"/>
-      <x:c r="F52" s="41"/>
-      <x:c r="G52" s="42"/>
+      <x:c r="F52" s="37"/>
+      <x:c r="G52" s="41"/>
       <x:c r="H52" s="42"/>
-      <x:c r="I52" s="42"/>
-      <x:c r="J52" s="37"/>
-      <x:c r="K52" s="37"/>
+      <x:c r="I52" s="43"/>
+      <x:c r="J52" s="43"/>
+      <x:c r="K52" s="43"/>
       <x:c r="L52" s="37"/>
       <x:c r="M52" s="37"/>
       <x:c r="N52" s="37"/>
       <x:c r="O52" s="37"/>
-      <x:c r="P52" s="39"/>
-      <x:c r="Q52" s="39"/>
-      <x:c r="R52" s="37"/>
-      <x:c r="S52" s="38"/>
-      <x:c r="T52" s="38"/>
+      <x:c r="P52" s="37"/>
+      <x:c r="Q52" s="37"/>
+      <x:c r="R52" s="39"/>
+      <x:c r="S52" s="39"/>
+      <x:c r="T52" s="37"/>
       <x:c r="U52" s="38"/>
+      <x:c r="V52" s="38"/>
+      <x:c r="W52" s="38"/>
     </x:row>
     <x:row r="53" ht="24" customHeight="1">
       <x:c r="A53" s="37"/>
@@ -19247,22 +19363,24 @@
       <x:c r="C53" s="37"/>
       <x:c r="D53" s="37"/>
       <x:c r="E53" s="37"/>
-      <x:c r="F53" s="41"/>
-      <x:c r="G53" s="42"/>
+      <x:c r="F53" s="37"/>
+      <x:c r="G53" s="41"/>
       <x:c r="H53" s="42"/>
-      <x:c r="I53" s="42"/>
-      <x:c r="J53" s="37"/>
-      <x:c r="K53" s="37"/>
+      <x:c r="I53" s="43"/>
+      <x:c r="J53" s="43"/>
+      <x:c r="K53" s="43"/>
       <x:c r="L53" s="37"/>
       <x:c r="M53" s="37"/>
       <x:c r="N53" s="37"/>
       <x:c r="O53" s="37"/>
-      <x:c r="P53" s="39"/>
-      <x:c r="Q53" s="39"/>
-      <x:c r="R53" s="37"/>
-      <x:c r="S53" s="38"/>
-      <x:c r="T53" s="38"/>
+      <x:c r="P53" s="37"/>
+      <x:c r="Q53" s="37"/>
+      <x:c r="R53" s="39"/>
+      <x:c r="S53" s="39"/>
+      <x:c r="T53" s="37"/>
       <x:c r="U53" s="38"/>
+      <x:c r="V53" s="38"/>
+      <x:c r="W53" s="38"/>
     </x:row>
     <x:row r="54" ht="24" customHeight="1">
       <x:c r="A54" s="37"/>
@@ -19270,22 +19388,24 @@
       <x:c r="C54" s="37"/>
       <x:c r="D54" s="37"/>
       <x:c r="E54" s="37"/>
-      <x:c r="F54" s="41"/>
-      <x:c r="G54" s="42"/>
+      <x:c r="F54" s="37"/>
+      <x:c r="G54" s="41"/>
       <x:c r="H54" s="42"/>
-      <x:c r="I54" s="42"/>
-      <x:c r="J54" s="37"/>
-      <x:c r="K54" s="37"/>
+      <x:c r="I54" s="43"/>
+      <x:c r="J54" s="43"/>
+      <x:c r="K54" s="43"/>
       <x:c r="L54" s="37"/>
       <x:c r="M54" s="37"/>
       <x:c r="N54" s="37"/>
       <x:c r="O54" s="37"/>
-      <x:c r="P54" s="39"/>
-      <x:c r="Q54" s="39"/>
-      <x:c r="R54" s="37"/>
-      <x:c r="S54" s="38"/>
-      <x:c r="T54" s="38"/>
+      <x:c r="P54" s="37"/>
+      <x:c r="Q54" s="37"/>
+      <x:c r="R54" s="39"/>
+      <x:c r="S54" s="39"/>
+      <x:c r="T54" s="37"/>
       <x:c r="U54" s="38"/>
+      <x:c r="V54" s="38"/>
+      <x:c r="W54" s="38"/>
     </x:row>
     <x:row r="55" ht="24" customHeight="1">
       <x:c r="A55" s="37"/>
@@ -19293,22 +19413,24 @@
       <x:c r="C55" s="37"/>
       <x:c r="D55" s="37"/>
       <x:c r="E55" s="37"/>
-      <x:c r="F55" s="41"/>
-      <x:c r="G55" s="42"/>
+      <x:c r="F55" s="37"/>
+      <x:c r="G55" s="41"/>
       <x:c r="H55" s="42"/>
-      <x:c r="I55" s="42"/>
-      <x:c r="J55" s="37"/>
-      <x:c r="K55" s="37"/>
+      <x:c r="I55" s="43"/>
+      <x:c r="J55" s="43"/>
+      <x:c r="K55" s="43"/>
       <x:c r="L55" s="37"/>
       <x:c r="M55" s="37"/>
       <x:c r="N55" s="37"/>
       <x:c r="O55" s="37"/>
-      <x:c r="P55" s="39"/>
-      <x:c r="Q55" s="39"/>
-      <x:c r="R55" s="37"/>
-      <x:c r="S55" s="38"/>
-      <x:c r="T55" s="38"/>
+      <x:c r="P55" s="37"/>
+      <x:c r="Q55" s="37"/>
+      <x:c r="R55" s="39"/>
+      <x:c r="S55" s="39"/>
+      <x:c r="T55" s="37"/>
       <x:c r="U55" s="38"/>
+      <x:c r="V55" s="38"/>
+      <x:c r="W55" s="38"/>
     </x:row>
     <x:row r="56" ht="24" customHeight="1">
       <x:c r="A56" s="37"/>
@@ -19316,22 +19438,24 @@
       <x:c r="C56" s="37"/>
       <x:c r="D56" s="37"/>
       <x:c r="E56" s="37"/>
-      <x:c r="F56" s="41"/>
-      <x:c r="G56" s="42"/>
+      <x:c r="F56" s="37"/>
+      <x:c r="G56" s="41"/>
       <x:c r="H56" s="42"/>
-      <x:c r="I56" s="42"/>
-      <x:c r="J56" s="37"/>
-      <x:c r="K56" s="37"/>
+      <x:c r="I56" s="43"/>
+      <x:c r="J56" s="43"/>
+      <x:c r="K56" s="43"/>
       <x:c r="L56" s="37"/>
       <x:c r="M56" s="37"/>
       <x:c r="N56" s="37"/>
       <x:c r="O56" s="37"/>
-      <x:c r="P56" s="39"/>
-      <x:c r="Q56" s="39"/>
-      <x:c r="R56" s="37"/>
-      <x:c r="S56" s="38"/>
-      <x:c r="T56" s="38"/>
+      <x:c r="P56" s="37"/>
+      <x:c r="Q56" s="37"/>
+      <x:c r="R56" s="39"/>
+      <x:c r="S56" s="39"/>
+      <x:c r="T56" s="37"/>
       <x:c r="U56" s="38"/>
+      <x:c r="V56" s="38"/>
+      <x:c r="W56" s="38"/>
     </x:row>
     <x:row r="57" ht="24" customHeight="1">
       <x:c r="A57" s="37"/>
@@ -19339,22 +19463,24 @@
       <x:c r="C57" s="37"/>
       <x:c r="D57" s="37"/>
       <x:c r="E57" s="37"/>
-      <x:c r="F57" s="41"/>
-      <x:c r="G57" s="42"/>
+      <x:c r="F57" s="37"/>
+      <x:c r="G57" s="41"/>
       <x:c r="H57" s="42"/>
-      <x:c r="I57" s="42"/>
-      <x:c r="J57" s="37"/>
-      <x:c r="K57" s="37"/>
+      <x:c r="I57" s="43"/>
+      <x:c r="J57" s="43"/>
+      <x:c r="K57" s="43"/>
       <x:c r="L57" s="37"/>
       <x:c r="M57" s="37"/>
       <x:c r="N57" s="37"/>
       <x:c r="O57" s="37"/>
-      <x:c r="P57" s="39"/>
-      <x:c r="Q57" s="39"/>
-      <x:c r="R57" s="37"/>
-      <x:c r="S57" s="38"/>
-      <x:c r="T57" s="38"/>
+      <x:c r="P57" s="37"/>
+      <x:c r="Q57" s="37"/>
+      <x:c r="R57" s="39"/>
+      <x:c r="S57" s="39"/>
+      <x:c r="T57" s="37"/>
       <x:c r="U57" s="38"/>
+      <x:c r="V57" s="38"/>
+      <x:c r="W57" s="38"/>
     </x:row>
     <x:row r="58" ht="24" customHeight="1">
       <x:c r="A58" s="37"/>
@@ -19362,22 +19488,24 @@
       <x:c r="C58" s="37"/>
       <x:c r="D58" s="37"/>
       <x:c r="E58" s="37"/>
-      <x:c r="F58" s="41"/>
-      <x:c r="G58" s="42"/>
+      <x:c r="F58" s="37"/>
+      <x:c r="G58" s="41"/>
       <x:c r="H58" s="42"/>
-      <x:c r="I58" s="42"/>
-      <x:c r="J58" s="37"/>
-      <x:c r="K58" s="37"/>
+      <x:c r="I58" s="43"/>
+      <x:c r="J58" s="43"/>
+      <x:c r="K58" s="43"/>
       <x:c r="L58" s="37"/>
       <x:c r="M58" s="37"/>
       <x:c r="N58" s="37"/>
       <x:c r="O58" s="37"/>
-      <x:c r="P58" s="39"/>
-      <x:c r="Q58" s="39"/>
-      <x:c r="R58" s="37"/>
-      <x:c r="S58" s="38"/>
-      <x:c r="T58" s="38"/>
+      <x:c r="P58" s="37"/>
+      <x:c r="Q58" s="37"/>
+      <x:c r="R58" s="39"/>
+      <x:c r="S58" s="39"/>
+      <x:c r="T58" s="37"/>
       <x:c r="U58" s="38"/>
+      <x:c r="V58" s="38"/>
+      <x:c r="W58" s="38"/>
     </x:row>
     <x:row r="59" ht="24" customHeight="1">
       <x:c r="A59" s="37"/>
@@ -19385,22 +19513,24 @@
       <x:c r="C59" s="37"/>
       <x:c r="D59" s="37"/>
       <x:c r="E59" s="37"/>
-      <x:c r="F59" s="41"/>
-      <x:c r="G59" s="42"/>
+      <x:c r="F59" s="37"/>
+      <x:c r="G59" s="41"/>
       <x:c r="H59" s="42"/>
-      <x:c r="I59" s="42"/>
-      <x:c r="J59" s="37"/>
-      <x:c r="K59" s="37"/>
+      <x:c r="I59" s="43"/>
+      <x:c r="J59" s="43"/>
+      <x:c r="K59" s="43"/>
       <x:c r="L59" s="37"/>
       <x:c r="M59" s="37"/>
       <x:c r="N59" s="37"/>
       <x:c r="O59" s="37"/>
-      <x:c r="P59" s="39"/>
-      <x:c r="Q59" s="39"/>
-      <x:c r="R59" s="37"/>
-      <x:c r="S59" s="38"/>
-      <x:c r="T59" s="38"/>
+      <x:c r="P59" s="37"/>
+      <x:c r="Q59" s="37"/>
+      <x:c r="R59" s="39"/>
+      <x:c r="S59" s="39"/>
+      <x:c r="T59" s="37"/>
       <x:c r="U59" s="38"/>
+      <x:c r="V59" s="38"/>
+      <x:c r="W59" s="38"/>
     </x:row>
     <x:row r="60" ht="24" customHeight="1">
       <x:c r="A60" s="37"/>
@@ -19408,22 +19538,24 @@
       <x:c r="C60" s="37"/>
       <x:c r="D60" s="37"/>
       <x:c r="E60" s="37"/>
-      <x:c r="F60" s="41"/>
-      <x:c r="G60" s="42"/>
+      <x:c r="F60" s="37"/>
+      <x:c r="G60" s="41"/>
       <x:c r="H60" s="42"/>
-      <x:c r="I60" s="42"/>
-      <x:c r="J60" s="37"/>
-      <x:c r="K60" s="37"/>
+      <x:c r="I60" s="43"/>
+      <x:c r="J60" s="43"/>
+      <x:c r="K60" s="43"/>
       <x:c r="L60" s="37"/>
       <x:c r="M60" s="37"/>
       <x:c r="N60" s="37"/>
       <x:c r="O60" s="37"/>
-      <x:c r="P60" s="39"/>
-      <x:c r="Q60" s="39"/>
-      <x:c r="R60" s="37"/>
-      <x:c r="S60" s="38"/>
-      <x:c r="T60" s="38"/>
+      <x:c r="P60" s="37"/>
+      <x:c r="Q60" s="37"/>
+      <x:c r="R60" s="39"/>
+      <x:c r="S60" s="39"/>
+      <x:c r="T60" s="37"/>
       <x:c r="U60" s="38"/>
+      <x:c r="V60" s="38"/>
+      <x:c r="W60" s="38"/>
     </x:row>
     <x:row r="61" ht="24" customHeight="1">
       <x:c r="A61" s="37"/>
@@ -19431,22 +19563,24 @@
       <x:c r="C61" s="37"/>
       <x:c r="D61" s="37"/>
       <x:c r="E61" s="37"/>
-      <x:c r="F61" s="41"/>
-      <x:c r="G61" s="42"/>
+      <x:c r="F61" s="37"/>
+      <x:c r="G61" s="41"/>
       <x:c r="H61" s="42"/>
-      <x:c r="I61" s="42"/>
-      <x:c r="J61" s="37"/>
-      <x:c r="K61" s="37"/>
+      <x:c r="I61" s="43"/>
+      <x:c r="J61" s="43"/>
+      <x:c r="K61" s="43"/>
       <x:c r="L61" s="37"/>
       <x:c r="M61" s="37"/>
       <x:c r="N61" s="37"/>
       <x:c r="O61" s="37"/>
-      <x:c r="P61" s="39"/>
-      <x:c r="Q61" s="39"/>
-      <x:c r="R61" s="37"/>
-      <x:c r="S61" s="38"/>
-      <x:c r="T61" s="38"/>
+      <x:c r="P61" s="37"/>
+      <x:c r="Q61" s="37"/>
+      <x:c r="R61" s="39"/>
+      <x:c r="S61" s="39"/>
+      <x:c r="T61" s="37"/>
       <x:c r="U61" s="38"/>
+      <x:c r="V61" s="38"/>
+      <x:c r="W61" s="38"/>
     </x:row>
     <x:row r="62" ht="24" customHeight="1">
       <x:c r="A62" s="37"/>
@@ -19454,22 +19588,24 @@
       <x:c r="C62" s="37"/>
       <x:c r="D62" s="37"/>
       <x:c r="E62" s="37"/>
-      <x:c r="F62" s="41"/>
-      <x:c r="G62" s="42"/>
+      <x:c r="F62" s="37"/>
+      <x:c r="G62" s="41"/>
       <x:c r="H62" s="42"/>
-      <x:c r="I62" s="42"/>
-      <x:c r="J62" s="37"/>
-      <x:c r="K62" s="37"/>
+      <x:c r="I62" s="43"/>
+      <x:c r="J62" s="43"/>
+      <x:c r="K62" s="43"/>
       <x:c r="L62" s="37"/>
       <x:c r="M62" s="37"/>
       <x:c r="N62" s="37"/>
       <x:c r="O62" s="37"/>
-      <x:c r="P62" s="39"/>
-      <x:c r="Q62" s="39"/>
-      <x:c r="R62" s="37"/>
-      <x:c r="S62" s="38"/>
-      <x:c r="T62" s="38"/>
+      <x:c r="P62" s="37"/>
+      <x:c r="Q62" s="37"/>
+      <x:c r="R62" s="39"/>
+      <x:c r="S62" s="39"/>
+      <x:c r="T62" s="37"/>
       <x:c r="U62" s="38"/>
+      <x:c r="V62" s="38"/>
+      <x:c r="W62" s="38"/>
     </x:row>
     <x:row r="63" ht="24" customHeight="1">
       <x:c r="A63" s="37"/>
@@ -19477,22 +19613,24 @@
       <x:c r="C63" s="37"/>
       <x:c r="D63" s="37"/>
       <x:c r="E63" s="37"/>
-      <x:c r="F63" s="41"/>
-      <x:c r="G63" s="42"/>
+      <x:c r="F63" s="37"/>
+      <x:c r="G63" s="41"/>
       <x:c r="H63" s="42"/>
-      <x:c r="I63" s="42"/>
-      <x:c r="J63" s="37"/>
-      <x:c r="K63" s="37"/>
+      <x:c r="I63" s="43"/>
+      <x:c r="J63" s="43"/>
+      <x:c r="K63" s="43"/>
       <x:c r="L63" s="37"/>
       <x:c r="M63" s="37"/>
       <x:c r="N63" s="37"/>
       <x:c r="O63" s="37"/>
-      <x:c r="P63" s="39"/>
-      <x:c r="Q63" s="39"/>
-      <x:c r="R63" s="37"/>
-      <x:c r="S63" s="38"/>
-      <x:c r="T63" s="38"/>
+      <x:c r="P63" s="37"/>
+      <x:c r="Q63" s="37"/>
+      <x:c r="R63" s="39"/>
+      <x:c r="S63" s="39"/>
+      <x:c r="T63" s="37"/>
       <x:c r="U63" s="38"/>
+      <x:c r="V63" s="38"/>
+      <x:c r="W63" s="38"/>
     </x:row>
     <x:row r="64" ht="24" customHeight="1">
       <x:c r="A64" s="37"/>
@@ -19500,22 +19638,24 @@
       <x:c r="C64" s="37"/>
       <x:c r="D64" s="37"/>
       <x:c r="E64" s="37"/>
-      <x:c r="F64" s="41"/>
-      <x:c r="G64" s="42"/>
+      <x:c r="F64" s="37"/>
+      <x:c r="G64" s="41"/>
       <x:c r="H64" s="42"/>
-      <x:c r="I64" s="42"/>
-      <x:c r="J64" s="37"/>
-      <x:c r="K64" s="37"/>
+      <x:c r="I64" s="43"/>
+      <x:c r="J64" s="43"/>
+      <x:c r="K64" s="43"/>
       <x:c r="L64" s="37"/>
       <x:c r="M64" s="37"/>
       <x:c r="N64" s="37"/>
       <x:c r="O64" s="37"/>
-      <x:c r="P64" s="39"/>
-      <x:c r="Q64" s="39"/>
-      <x:c r="R64" s="37"/>
-      <x:c r="S64" s="38"/>
-      <x:c r="T64" s="38"/>
+      <x:c r="P64" s="37"/>
+      <x:c r="Q64" s="37"/>
+      <x:c r="R64" s="39"/>
+      <x:c r="S64" s="39"/>
+      <x:c r="T64" s="37"/>
       <x:c r="U64" s="38"/>
+      <x:c r="V64" s="38"/>
+      <x:c r="W64" s="38"/>
     </x:row>
     <x:row r="65" ht="24" customHeight="1">
       <x:c r="A65" s="37"/>
@@ -19523,22 +19663,24 @@
       <x:c r="C65" s="37"/>
       <x:c r="D65" s="37"/>
       <x:c r="E65" s="37"/>
-      <x:c r="F65" s="41"/>
-      <x:c r="G65" s="42"/>
+      <x:c r="F65" s="37"/>
+      <x:c r="G65" s="41"/>
       <x:c r="H65" s="42"/>
-      <x:c r="I65" s="42"/>
-      <x:c r="J65" s="37"/>
-      <x:c r="K65" s="37"/>
+      <x:c r="I65" s="43"/>
+      <x:c r="J65" s="43"/>
+      <x:c r="K65" s="43"/>
       <x:c r="L65" s="37"/>
       <x:c r="M65" s="37"/>
       <x:c r="N65" s="37"/>
       <x:c r="O65" s="37"/>
-      <x:c r="P65" s="39"/>
-      <x:c r="Q65" s="39"/>
-      <x:c r="R65" s="37"/>
-      <x:c r="S65" s="38"/>
-      <x:c r="T65" s="38"/>
+      <x:c r="P65" s="37"/>
+      <x:c r="Q65" s="37"/>
+      <x:c r="R65" s="39"/>
+      <x:c r="S65" s="39"/>
+      <x:c r="T65" s="37"/>
       <x:c r="U65" s="38"/>
+      <x:c r="V65" s="38"/>
+      <x:c r="W65" s="38"/>
     </x:row>
     <x:row r="66" ht="24" customHeight="1">
       <x:c r="A66" s="37"/>
@@ -19546,22 +19688,24 @@
       <x:c r="C66" s="37"/>
       <x:c r="D66" s="37"/>
       <x:c r="E66" s="37"/>
-      <x:c r="F66" s="41"/>
-      <x:c r="G66" s="42"/>
+      <x:c r="F66" s="37"/>
+      <x:c r="G66" s="41"/>
       <x:c r="H66" s="42"/>
-      <x:c r="I66" s="42"/>
-      <x:c r="J66" s="37"/>
-      <x:c r="K66" s="37"/>
+      <x:c r="I66" s="43"/>
+      <x:c r="J66" s="43"/>
+      <x:c r="K66" s="43"/>
       <x:c r="L66" s="37"/>
       <x:c r="M66" s="37"/>
       <x:c r="N66" s="37"/>
       <x:c r="O66" s="37"/>
-      <x:c r="P66" s="39"/>
-      <x:c r="Q66" s="39"/>
-      <x:c r="R66" s="37"/>
-      <x:c r="S66" s="38"/>
-      <x:c r="T66" s="38"/>
+      <x:c r="P66" s="37"/>
+      <x:c r="Q66" s="37"/>
+      <x:c r="R66" s="39"/>
+      <x:c r="S66" s="39"/>
+      <x:c r="T66" s="37"/>
       <x:c r="U66" s="38"/>
+      <x:c r="V66" s="38"/>
+      <x:c r="W66" s="38"/>
     </x:row>
     <x:row r="67" ht="24" customHeight="1">
       <x:c r="A67" s="37"/>
@@ -19569,22 +19713,24 @@
       <x:c r="C67" s="37"/>
       <x:c r="D67" s="37"/>
       <x:c r="E67" s="37"/>
-      <x:c r="F67" s="41"/>
-      <x:c r="G67" s="42"/>
+      <x:c r="F67" s="37"/>
+      <x:c r="G67" s="41"/>
       <x:c r="H67" s="42"/>
-      <x:c r="I67" s="42"/>
-      <x:c r="J67" s="37"/>
-      <x:c r="K67" s="37"/>
+      <x:c r="I67" s="43"/>
+      <x:c r="J67" s="43"/>
+      <x:c r="K67" s="43"/>
       <x:c r="L67" s="37"/>
       <x:c r="M67" s="37"/>
       <x:c r="N67" s="37"/>
       <x:c r="O67" s="37"/>
-      <x:c r="P67" s="39"/>
-      <x:c r="Q67" s="39"/>
-      <x:c r="R67" s="37"/>
-      <x:c r="S67" s="38"/>
-      <x:c r="T67" s="38"/>
+      <x:c r="P67" s="37"/>
+      <x:c r="Q67" s="37"/>
+      <x:c r="R67" s="39"/>
+      <x:c r="S67" s="39"/>
+      <x:c r="T67" s="37"/>
       <x:c r="U67" s="38"/>
+      <x:c r="V67" s="38"/>
+      <x:c r="W67" s="38"/>
     </x:row>
     <x:row r="68" ht="24" customHeight="1">
       <x:c r="A68" s="37"/>
@@ -19592,22 +19738,24 @@
       <x:c r="C68" s="37"/>
       <x:c r="D68" s="37"/>
       <x:c r="E68" s="37"/>
-      <x:c r="F68" s="41"/>
-      <x:c r="G68" s="42"/>
+      <x:c r="F68" s="37"/>
+      <x:c r="G68" s="41"/>
       <x:c r="H68" s="42"/>
-      <x:c r="I68" s="42"/>
-      <x:c r="J68" s="37"/>
-      <x:c r="K68" s="37"/>
+      <x:c r="I68" s="43"/>
+      <x:c r="J68" s="43"/>
+      <x:c r="K68" s="43"/>
       <x:c r="L68" s="37"/>
       <x:c r="M68" s="37"/>
       <x:c r="N68" s="37"/>
       <x:c r="O68" s="37"/>
-      <x:c r="P68" s="39"/>
-      <x:c r="Q68" s="39"/>
-      <x:c r="R68" s="37"/>
-      <x:c r="S68" s="38"/>
-      <x:c r="T68" s="38"/>
+      <x:c r="P68" s="37"/>
+      <x:c r="Q68" s="37"/>
+      <x:c r="R68" s="39"/>
+      <x:c r="S68" s="39"/>
+      <x:c r="T68" s="37"/>
       <x:c r="U68" s="38"/>
+      <x:c r="V68" s="38"/>
+      <x:c r="W68" s="38"/>
     </x:row>
     <x:row r="69" ht="24" customHeight="1">
       <x:c r="A69" s="37"/>
@@ -19615,22 +19763,24 @@
       <x:c r="C69" s="37"/>
       <x:c r="D69" s="37"/>
       <x:c r="E69" s="37"/>
-      <x:c r="F69" s="41"/>
-      <x:c r="G69" s="42"/>
+      <x:c r="F69" s="37"/>
+      <x:c r="G69" s="41"/>
       <x:c r="H69" s="42"/>
-      <x:c r="I69" s="42"/>
-      <x:c r="J69" s="37"/>
-      <x:c r="K69" s="37"/>
+      <x:c r="I69" s="43"/>
+      <x:c r="J69" s="43"/>
+      <x:c r="K69" s="43"/>
       <x:c r="L69" s="37"/>
       <x:c r="M69" s="37"/>
       <x:c r="N69" s="37"/>
       <x:c r="O69" s="37"/>
-      <x:c r="P69" s="39"/>
-      <x:c r="Q69" s="39"/>
-      <x:c r="R69" s="37"/>
-      <x:c r="S69" s="38"/>
-      <x:c r="T69" s="38"/>
+      <x:c r="P69" s="37"/>
+      <x:c r="Q69" s="37"/>
+      <x:c r="R69" s="39"/>
+      <x:c r="S69" s="39"/>
+      <x:c r="T69" s="37"/>
       <x:c r="U69" s="38"/>
+      <x:c r="V69" s="38"/>
+      <x:c r="W69" s="38"/>
     </x:row>
     <x:row r="70" ht="24" customHeight="1">
       <x:c r="A70" s="37"/>
@@ -19638,22 +19788,24 @@
       <x:c r="C70" s="37"/>
       <x:c r="D70" s="37"/>
       <x:c r="E70" s="37"/>
-      <x:c r="F70" s="41"/>
-      <x:c r="G70" s="42"/>
+      <x:c r="F70" s="37"/>
+      <x:c r="G70" s="41"/>
       <x:c r="H70" s="42"/>
-      <x:c r="I70" s="42"/>
-      <x:c r="J70" s="37"/>
-      <x:c r="K70" s="37"/>
+      <x:c r="I70" s="43"/>
+      <x:c r="J70" s="43"/>
+      <x:c r="K70" s="43"/>
       <x:c r="L70" s="37"/>
       <x:c r="M70" s="37"/>
       <x:c r="N70" s="37"/>
       <x:c r="O70" s="37"/>
-      <x:c r="P70" s="39"/>
-      <x:c r="Q70" s="39"/>
-      <x:c r="R70" s="37"/>
-      <x:c r="S70" s="38"/>
-      <x:c r="T70" s="38"/>
+      <x:c r="P70" s="37"/>
+      <x:c r="Q70" s="37"/>
+      <x:c r="R70" s="39"/>
+      <x:c r="S70" s="39"/>
+      <x:c r="T70" s="37"/>
       <x:c r="U70" s="38"/>
+      <x:c r="V70" s="38"/>
+      <x:c r="W70" s="38"/>
     </x:row>
     <x:row r="71" ht="24" customHeight="1">
       <x:c r="A71" s="37"/>
@@ -19661,22 +19813,24 @@
       <x:c r="C71" s="37"/>
       <x:c r="D71" s="37"/>
       <x:c r="E71" s="37"/>
-      <x:c r="F71" s="41"/>
-      <x:c r="G71" s="42"/>
+      <x:c r="F71" s="37"/>
+      <x:c r="G71" s="41"/>
       <x:c r="H71" s="42"/>
-      <x:c r="I71" s="42"/>
-      <x:c r="J71" s="37"/>
-      <x:c r="K71" s="37"/>
+      <x:c r="I71" s="43"/>
+      <x:c r="J71" s="43"/>
+      <x:c r="K71" s="43"/>
       <x:c r="L71" s="37"/>
       <x:c r="M71" s="37"/>
       <x:c r="N71" s="37"/>
       <x:c r="O71" s="37"/>
-      <x:c r="P71" s="39"/>
-      <x:c r="Q71" s="39"/>
-      <x:c r="R71" s="37"/>
-      <x:c r="S71" s="38"/>
-      <x:c r="T71" s="38"/>
+      <x:c r="P71" s="37"/>
+      <x:c r="Q71" s="37"/>
+      <x:c r="R71" s="39"/>
+      <x:c r="S71" s="39"/>
+      <x:c r="T71" s="37"/>
       <x:c r="U71" s="38"/>
+      <x:c r="V71" s="38"/>
+      <x:c r="W71" s="38"/>
     </x:row>
     <x:row r="72" ht="24" customHeight="1">
       <x:c r="A72" s="37"/>
@@ -19684,22 +19838,24 @@
       <x:c r="C72" s="37"/>
       <x:c r="D72" s="37"/>
       <x:c r="E72" s="37"/>
-      <x:c r="F72" s="41"/>
-      <x:c r="G72" s="42"/>
+      <x:c r="F72" s="37"/>
+      <x:c r="G72" s="41"/>
       <x:c r="H72" s="42"/>
-      <x:c r="I72" s="42"/>
-      <x:c r="J72" s="37"/>
-      <x:c r="K72" s="37"/>
+      <x:c r="I72" s="43"/>
+      <x:c r="J72" s="43"/>
+      <x:c r="K72" s="43"/>
       <x:c r="L72" s="37"/>
       <x:c r="M72" s="37"/>
       <x:c r="N72" s="37"/>
       <x:c r="O72" s="37"/>
-      <x:c r="P72" s="39"/>
-      <x:c r="Q72" s="39"/>
-      <x:c r="R72" s="37"/>
-      <x:c r="S72" s="38"/>
-      <x:c r="T72" s="38"/>
+      <x:c r="P72" s="37"/>
+      <x:c r="Q72" s="37"/>
+      <x:c r="R72" s="39"/>
+      <x:c r="S72" s="39"/>
+      <x:c r="T72" s="37"/>
       <x:c r="U72" s="38"/>
+      <x:c r="V72" s="38"/>
+      <x:c r="W72" s="38"/>
     </x:row>
     <x:row r="73" ht="24" customHeight="1">
       <x:c r="A73" s="37"/>
@@ -19707,22 +19863,24 @@
       <x:c r="C73" s="37"/>
       <x:c r="D73" s="37"/>
       <x:c r="E73" s="37"/>
-      <x:c r="F73" s="41"/>
-      <x:c r="G73" s="42"/>
+      <x:c r="F73" s="37"/>
+      <x:c r="G73" s="41"/>
       <x:c r="H73" s="42"/>
-      <x:c r="I73" s="42"/>
-      <x:c r="J73" s="37"/>
-      <x:c r="K73" s="37"/>
+      <x:c r="I73" s="43"/>
+      <x:c r="J73" s="43"/>
+      <x:c r="K73" s="43"/>
       <x:c r="L73" s="37"/>
       <x:c r="M73" s="37"/>
       <x:c r="N73" s="37"/>
       <x:c r="O73" s="37"/>
-      <x:c r="P73" s="39"/>
-      <x:c r="Q73" s="39"/>
-      <x:c r="R73" s="37"/>
-      <x:c r="S73" s="38"/>
-      <x:c r="T73" s="38"/>
+      <x:c r="P73" s="37"/>
+      <x:c r="Q73" s="37"/>
+      <x:c r="R73" s="39"/>
+      <x:c r="S73" s="39"/>
+      <x:c r="T73" s="37"/>
       <x:c r="U73" s="38"/>
+      <x:c r="V73" s="38"/>
+      <x:c r="W73" s="38"/>
     </x:row>
     <x:row r="74" ht="24" customHeight="1">
       <x:c r="A74" s="37"/>
@@ -19730,22 +19888,24 @@
       <x:c r="C74" s="37"/>
       <x:c r="D74" s="37"/>
       <x:c r="E74" s="37"/>
-      <x:c r="F74" s="41"/>
-      <x:c r="G74" s="42"/>
+      <x:c r="F74" s="37"/>
+      <x:c r="G74" s="41"/>
       <x:c r="H74" s="42"/>
-      <x:c r="I74" s="42"/>
-      <x:c r="J74" s="37"/>
-      <x:c r="K74" s="37"/>
+      <x:c r="I74" s="43"/>
+      <x:c r="J74" s="43"/>
+      <x:c r="K74" s="43"/>
       <x:c r="L74" s="37"/>
       <x:c r="M74" s="37"/>
       <x:c r="N74" s="37"/>
       <x:c r="O74" s="37"/>
-      <x:c r="P74" s="39"/>
-      <x:c r="Q74" s="39"/>
-      <x:c r="R74" s="37"/>
-      <x:c r="S74" s="38"/>
-      <x:c r="T74" s="38"/>
+      <x:c r="P74" s="37"/>
+      <x:c r="Q74" s="37"/>
+      <x:c r="R74" s="39"/>
+      <x:c r="S74" s="39"/>
+      <x:c r="T74" s="37"/>
       <x:c r="U74" s="38"/>
+      <x:c r="V74" s="38"/>
+      <x:c r="W74" s="38"/>
     </x:row>
     <x:row r="75" ht="24" customHeight="1">
       <x:c r="A75" s="37"/>
@@ -19753,22 +19913,24 @@
       <x:c r="C75" s="37"/>
       <x:c r="D75" s="37"/>
       <x:c r="E75" s="37"/>
-      <x:c r="F75" s="41"/>
-      <x:c r="G75" s="42"/>
+      <x:c r="F75" s="37"/>
+      <x:c r="G75" s="41"/>
       <x:c r="H75" s="42"/>
-      <x:c r="I75" s="42"/>
-      <x:c r="J75" s="37"/>
-      <x:c r="K75" s="37"/>
+      <x:c r="I75" s="43"/>
+      <x:c r="J75" s="43"/>
+      <x:c r="K75" s="43"/>
       <x:c r="L75" s="37"/>
       <x:c r="M75" s="37"/>
       <x:c r="N75" s="37"/>
       <x:c r="O75" s="37"/>
-      <x:c r="P75" s="39"/>
-      <x:c r="Q75" s="39"/>
-      <x:c r="R75" s="37"/>
-      <x:c r="S75" s="38"/>
-      <x:c r="T75" s="38"/>
+      <x:c r="P75" s="37"/>
+      <x:c r="Q75" s="37"/>
+      <x:c r="R75" s="39"/>
+      <x:c r="S75" s="39"/>
+      <x:c r="T75" s="37"/>
       <x:c r="U75" s="38"/>
+      <x:c r="V75" s="38"/>
+      <x:c r="W75" s="38"/>
     </x:row>
     <x:row r="76" ht="24" customHeight="1">
       <x:c r="A76" s="37"/>
@@ -19776,22 +19938,24 @@
       <x:c r="C76" s="37"/>
       <x:c r="D76" s="37"/>
       <x:c r="E76" s="37"/>
-      <x:c r="F76" s="41"/>
-      <x:c r="G76" s="42"/>
+      <x:c r="F76" s="37"/>
+      <x:c r="G76" s="41"/>
       <x:c r="H76" s="42"/>
-      <x:c r="I76" s="42"/>
-      <x:c r="J76" s="37"/>
-      <x:c r="K76" s="37"/>
+      <x:c r="I76" s="43"/>
+      <x:c r="J76" s="43"/>
+      <x:c r="K76" s="43"/>
       <x:c r="L76" s="37"/>
       <x:c r="M76" s="37"/>
       <x:c r="N76" s="37"/>
       <x:c r="O76" s="37"/>
-      <x:c r="P76" s="39"/>
-      <x:c r="Q76" s="39"/>
-      <x:c r="R76" s="37"/>
-      <x:c r="S76" s="38"/>
-      <x:c r="T76" s="38"/>
+      <x:c r="P76" s="37"/>
+      <x:c r="Q76" s="37"/>
+      <x:c r="R76" s="39"/>
+      <x:c r="S76" s="39"/>
+      <x:c r="T76" s="37"/>
       <x:c r="U76" s="38"/>
+      <x:c r="V76" s="38"/>
+      <x:c r="W76" s="38"/>
     </x:row>
     <x:row r="77" ht="24" customHeight="1">
       <x:c r="A77" s="37"/>
@@ -19799,22 +19963,24 @@
       <x:c r="C77" s="37"/>
       <x:c r="D77" s="37"/>
       <x:c r="E77" s="37"/>
-      <x:c r="F77" s="41"/>
-      <x:c r="G77" s="42"/>
+      <x:c r="F77" s="37"/>
+      <x:c r="G77" s="41"/>
       <x:c r="H77" s="42"/>
-      <x:c r="I77" s="42"/>
-      <x:c r="J77" s="37"/>
-      <x:c r="K77" s="37"/>
+      <x:c r="I77" s="43"/>
+      <x:c r="J77" s="43"/>
+      <x:c r="K77" s="43"/>
       <x:c r="L77" s="37"/>
       <x:c r="M77" s="37"/>
       <x:c r="N77" s="37"/>
       <x:c r="O77" s="37"/>
-      <x:c r="P77" s="39"/>
-      <x:c r="Q77" s="39"/>
-      <x:c r="R77" s="37"/>
-      <x:c r="S77" s="38"/>
-      <x:c r="T77" s="38"/>
+      <x:c r="P77" s="37"/>
+      <x:c r="Q77" s="37"/>
+      <x:c r="R77" s="39"/>
+      <x:c r="S77" s="39"/>
+      <x:c r="T77" s="37"/>
       <x:c r="U77" s="38"/>
+      <x:c r="V77" s="38"/>
+      <x:c r="W77" s="38"/>
     </x:row>
     <x:row r="78" ht="24" customHeight="1">
       <x:c r="A78" s="37"/>
@@ -19822,22 +19988,24 @@
       <x:c r="C78" s="37"/>
       <x:c r="D78" s="37"/>
       <x:c r="E78" s="37"/>
-      <x:c r="F78" s="41"/>
-      <x:c r="G78" s="42"/>
+      <x:c r="F78" s="37"/>
+      <x:c r="G78" s="41"/>
       <x:c r="H78" s="42"/>
-      <x:c r="I78" s="42"/>
-      <x:c r="J78" s="37"/>
-      <x:c r="K78" s="37"/>
+      <x:c r="I78" s="43"/>
+      <x:c r="J78" s="43"/>
+      <x:c r="K78" s="43"/>
       <x:c r="L78" s="37"/>
       <x:c r="M78" s="37"/>
       <x:c r="N78" s="37"/>
       <x:c r="O78" s="37"/>
-      <x:c r="P78" s="39"/>
-      <x:c r="Q78" s="39"/>
-      <x:c r="R78" s="37"/>
-      <x:c r="S78" s="38"/>
-      <x:c r="T78" s="38"/>
+      <x:c r="P78" s="37"/>
+      <x:c r="Q78" s="37"/>
+      <x:c r="R78" s="39"/>
+      <x:c r="S78" s="39"/>
+      <x:c r="T78" s="37"/>
       <x:c r="U78" s="38"/>
+      <x:c r="V78" s="38"/>
+      <x:c r="W78" s="38"/>
     </x:row>
     <x:row r="79" ht="24" customHeight="1">
       <x:c r="A79" s="37"/>
@@ -19845,22 +20013,24 @@
       <x:c r="C79" s="37"/>
       <x:c r="D79" s="37"/>
       <x:c r="E79" s="37"/>
-      <x:c r="F79" s="41"/>
-      <x:c r="G79" s="42"/>
+      <x:c r="F79" s="37"/>
+      <x:c r="G79" s="41"/>
       <x:c r="H79" s="42"/>
-      <x:c r="I79" s="42"/>
-      <x:c r="J79" s="37"/>
-      <x:c r="K79" s="37"/>
+      <x:c r="I79" s="43"/>
+      <x:c r="J79" s="43"/>
+      <x:c r="K79" s="43"/>
       <x:c r="L79" s="37"/>
       <x:c r="M79" s="37"/>
       <x:c r="N79" s="37"/>
       <x:c r="O79" s="37"/>
-      <x:c r="P79" s="39"/>
-      <x:c r="Q79" s="39"/>
-      <x:c r="R79" s="37"/>
-      <x:c r="S79" s="38"/>
-      <x:c r="T79" s="38"/>
+      <x:c r="P79" s="37"/>
+      <x:c r="Q79" s="37"/>
+      <x:c r="R79" s="39"/>
+      <x:c r="S79" s="39"/>
+      <x:c r="T79" s="37"/>
       <x:c r="U79" s="38"/>
+      <x:c r="V79" s="38"/>
+      <x:c r="W79" s="38"/>
     </x:row>
     <x:row r="80" ht="24" customHeight="1">
       <x:c r="A80" s="37"/>
@@ -19868,22 +20038,24 @@
       <x:c r="C80" s="37"/>
       <x:c r="D80" s="37"/>
       <x:c r="E80" s="37"/>
-      <x:c r="F80" s="41"/>
-      <x:c r="G80" s="42"/>
+      <x:c r="F80" s="37"/>
+      <x:c r="G80" s="41"/>
       <x:c r="H80" s="42"/>
-      <x:c r="I80" s="42"/>
-      <x:c r="J80" s="37"/>
-      <x:c r="K80" s="37"/>
+      <x:c r="I80" s="43"/>
+      <x:c r="J80" s="43"/>
+      <x:c r="K80" s="43"/>
       <x:c r="L80" s="37"/>
       <x:c r="M80" s="37"/>
       <x:c r="N80" s="37"/>
       <x:c r="O80" s="37"/>
-      <x:c r="P80" s="39"/>
-      <x:c r="Q80" s="39"/>
-      <x:c r="R80" s="37"/>
-      <x:c r="S80" s="38"/>
-      <x:c r="T80" s="38"/>
+      <x:c r="P80" s="37"/>
+      <x:c r="Q80" s="37"/>
+      <x:c r="R80" s="39"/>
+      <x:c r="S80" s="39"/>
+      <x:c r="T80" s="37"/>
       <x:c r="U80" s="38"/>
+      <x:c r="V80" s="38"/>
+      <x:c r="W80" s="38"/>
     </x:row>
     <x:row r="81" ht="24" customHeight="1">
       <x:c r="A81" s="37"/>
@@ -19891,22 +20063,24 @@
       <x:c r="C81" s="37"/>
       <x:c r="D81" s="37"/>
       <x:c r="E81" s="37"/>
-      <x:c r="F81" s="41"/>
-      <x:c r="G81" s="42"/>
+      <x:c r="F81" s="37"/>
+      <x:c r="G81" s="41"/>
       <x:c r="H81" s="42"/>
-      <x:c r="I81" s="42"/>
-      <x:c r="J81" s="37"/>
-      <x:c r="K81" s="37"/>
+      <x:c r="I81" s="43"/>
+      <x:c r="J81" s="43"/>
+      <x:c r="K81" s="43"/>
       <x:c r="L81" s="37"/>
       <x:c r="M81" s="37"/>
       <x:c r="N81" s="37"/>
       <x:c r="O81" s="37"/>
-      <x:c r="P81" s="39"/>
-      <x:c r="Q81" s="39"/>
-      <x:c r="R81" s="37"/>
-      <x:c r="S81" s="38"/>
-      <x:c r="T81" s="38"/>
+      <x:c r="P81" s="37"/>
+      <x:c r="Q81" s="37"/>
+      <x:c r="R81" s="39"/>
+      <x:c r="S81" s="39"/>
+      <x:c r="T81" s="37"/>
       <x:c r="U81" s="38"/>
+      <x:c r="V81" s="38"/>
+      <x:c r="W81" s="38"/>
     </x:row>
     <x:row r="82" ht="24" customHeight="1">
       <x:c r="A82" s="37"/>
@@ -19914,22 +20088,24 @@
       <x:c r="C82" s="37"/>
       <x:c r="D82" s="37"/>
       <x:c r="E82" s="37"/>
-      <x:c r="F82" s="41"/>
-      <x:c r="G82" s="42"/>
+      <x:c r="F82" s="37"/>
+      <x:c r="G82" s="41"/>
       <x:c r="H82" s="42"/>
-      <x:c r="I82" s="42"/>
-      <x:c r="J82" s="37"/>
-      <x:c r="K82" s="37"/>
+      <x:c r="I82" s="43"/>
+      <x:c r="J82" s="43"/>
+      <x:c r="K82" s="43"/>
       <x:c r="L82" s="37"/>
       <x:c r="M82" s="37"/>
       <x:c r="N82" s="37"/>
       <x:c r="O82" s="37"/>
-      <x:c r="P82" s="39"/>
-      <x:c r="Q82" s="39"/>
-      <x:c r="R82" s="37"/>
-      <x:c r="S82" s="38"/>
-      <x:c r="T82" s="38"/>
+      <x:c r="P82" s="37"/>
+      <x:c r="Q82" s="37"/>
+      <x:c r="R82" s="39"/>
+      <x:c r="S82" s="39"/>
+      <x:c r="T82" s="37"/>
       <x:c r="U82" s="38"/>
+      <x:c r="V82" s="38"/>
+      <x:c r="W82" s="38"/>
     </x:row>
     <x:row r="83" ht="24" customHeight="1">
       <x:c r="A83" s="37"/>
@@ -19937,22 +20113,24 @@
       <x:c r="C83" s="37"/>
       <x:c r="D83" s="37"/>
       <x:c r="E83" s="37"/>
-      <x:c r="F83" s="41"/>
-      <x:c r="G83" s="42"/>
+      <x:c r="F83" s="37"/>
+      <x:c r="G83" s="41"/>
       <x:c r="H83" s="42"/>
-      <x:c r="I83" s="42"/>
-      <x:c r="J83" s="37"/>
-      <x:c r="K83" s="37"/>
+      <x:c r="I83" s="43"/>
+      <x:c r="J83" s="43"/>
+      <x:c r="K83" s="43"/>
       <x:c r="L83" s="37"/>
       <x:c r="M83" s="37"/>
       <x:c r="N83" s="37"/>
       <x:c r="O83" s="37"/>
-      <x:c r="P83" s="39"/>
-      <x:c r="Q83" s="39"/>
-      <x:c r="R83" s="37"/>
-      <x:c r="S83" s="38"/>
-      <x:c r="T83" s="38"/>
+      <x:c r="P83" s="37"/>
+      <x:c r="Q83" s="37"/>
+      <x:c r="R83" s="39"/>
+      <x:c r="S83" s="39"/>
+      <x:c r="T83" s="37"/>
       <x:c r="U83" s="38"/>
+      <x:c r="V83" s="38"/>
+      <x:c r="W83" s="38"/>
     </x:row>
     <x:row r="84" ht="24" customHeight="1">
       <x:c r="A84" s="37"/>
@@ -19960,22 +20138,24 @@
       <x:c r="C84" s="37"/>
       <x:c r="D84" s="37"/>
       <x:c r="E84" s="37"/>
-      <x:c r="F84" s="41"/>
-      <x:c r="G84" s="42"/>
+      <x:c r="F84" s="37"/>
+      <x:c r="G84" s="41"/>
       <x:c r="H84" s="42"/>
-      <x:c r="I84" s="42"/>
-      <x:c r="J84" s="37"/>
-      <x:c r="K84" s="37"/>
+      <x:c r="I84" s="43"/>
+      <x:c r="J84" s="43"/>
+      <x:c r="K84" s="43"/>
       <x:c r="L84" s="37"/>
       <x:c r="M84" s="37"/>
       <x:c r="N84" s="37"/>
       <x:c r="O84" s="37"/>
-      <x:c r="P84" s="39"/>
-      <x:c r="Q84" s="39"/>
-      <x:c r="R84" s="37"/>
-      <x:c r="S84" s="38"/>
-      <x:c r="T84" s="38"/>
+      <x:c r="P84" s="37"/>
+      <x:c r="Q84" s="37"/>
+      <x:c r="R84" s="39"/>
+      <x:c r="S84" s="39"/>
+      <x:c r="T84" s="37"/>
       <x:c r="U84" s="38"/>
+      <x:c r="V84" s="38"/>
+      <x:c r="W84" s="38"/>
     </x:row>
     <x:row r="85" ht="24" customHeight="1">
       <x:c r="A85" s="37"/>
@@ -19983,22 +20163,24 @@
       <x:c r="C85" s="37"/>
       <x:c r="D85" s="37"/>
       <x:c r="E85" s="37"/>
-      <x:c r="F85" s="41"/>
-      <x:c r="G85" s="42"/>
+      <x:c r="F85" s="37"/>
+      <x:c r="G85" s="41"/>
       <x:c r="H85" s="42"/>
-      <x:c r="I85" s="42"/>
-      <x:c r="J85" s="37"/>
-      <x:c r="K85" s="37"/>
+      <x:c r="I85" s="43"/>
+      <x:c r="J85" s="43"/>
+      <x:c r="K85" s="43"/>
       <x:c r="L85" s="37"/>
       <x:c r="M85" s="37"/>
       <x:c r="N85" s="37"/>
       <x:c r="O85" s="37"/>
-      <x:c r="P85" s="39"/>
-      <x:c r="Q85" s="39"/>
-      <x:c r="R85" s="37"/>
-      <x:c r="S85" s="38"/>
-      <x:c r="T85" s="38"/>
+      <x:c r="P85" s="37"/>
+      <x:c r="Q85" s="37"/>
+      <x:c r="R85" s="39"/>
+      <x:c r="S85" s="39"/>
+      <x:c r="T85" s="37"/>
       <x:c r="U85" s="38"/>
+      <x:c r="V85" s="38"/>
+      <x:c r="W85" s="38"/>
     </x:row>
     <x:row r="86" ht="24" customHeight="1">
       <x:c r="A86" s="37"/>
@@ -20006,22 +20188,24 @@
       <x:c r="C86" s="37"/>
       <x:c r="D86" s="37"/>
       <x:c r="E86" s="37"/>
-      <x:c r="F86" s="41"/>
-      <x:c r="G86" s="42"/>
+      <x:c r="F86" s="37"/>
+      <x:c r="G86" s="41"/>
       <x:c r="H86" s="42"/>
-      <x:c r="I86" s="42"/>
-      <x:c r="J86" s="37"/>
-      <x:c r="K86" s="37"/>
+      <x:c r="I86" s="43"/>
+      <x:c r="J86" s="43"/>
+      <x:c r="K86" s="43"/>
       <x:c r="L86" s="37"/>
       <x:c r="M86" s="37"/>
       <x:c r="N86" s="37"/>
       <x:c r="O86" s="37"/>
-      <x:c r="P86" s="39"/>
-      <x:c r="Q86" s="39"/>
-      <x:c r="R86" s="37"/>
-      <x:c r="S86" s="38"/>
-      <x:c r="T86" s="38"/>
+      <x:c r="P86" s="37"/>
+      <x:c r="Q86" s="37"/>
+      <x:c r="R86" s="39"/>
+      <x:c r="S86" s="39"/>
+      <x:c r="T86" s="37"/>
       <x:c r="U86" s="38"/>
+      <x:c r="V86" s="38"/>
+      <x:c r="W86" s="38"/>
     </x:row>
     <x:row r="87" ht="24" customHeight="1">
       <x:c r="A87" s="37"/>
@@ -20029,22 +20213,24 @@
       <x:c r="C87" s="37"/>
       <x:c r="D87" s="37"/>
       <x:c r="E87" s="37"/>
-      <x:c r="F87" s="41"/>
-      <x:c r="G87" s="42"/>
+      <x:c r="F87" s="37"/>
+      <x:c r="G87" s="41"/>
       <x:c r="H87" s="42"/>
-      <x:c r="I87" s="42"/>
-      <x:c r="J87" s="37"/>
-      <x:c r="K87" s="37"/>
+      <x:c r="I87" s="43"/>
+      <x:c r="J87" s="43"/>
+      <x:c r="K87" s="43"/>
       <x:c r="L87" s="37"/>
       <x:c r="M87" s="37"/>
       <x:c r="N87" s="37"/>
       <x:c r="O87" s="37"/>
-      <x:c r="P87" s="39"/>
-      <x:c r="Q87" s="39"/>
-      <x:c r="R87" s="37"/>
-      <x:c r="S87" s="38"/>
-      <x:c r="T87" s="38"/>
+      <x:c r="P87" s="37"/>
+      <x:c r="Q87" s="37"/>
+      <x:c r="R87" s="39"/>
+      <x:c r="S87" s="39"/>
+      <x:c r="T87" s="37"/>
       <x:c r="U87" s="38"/>
+      <x:c r="V87" s="38"/>
+      <x:c r="W87" s="38"/>
     </x:row>
     <x:row r="88" ht="24" customHeight="1">
       <x:c r="A88" s="37"/>
@@ -20052,22 +20238,24 @@
       <x:c r="C88" s="37"/>
       <x:c r="D88" s="37"/>
       <x:c r="E88" s="37"/>
-      <x:c r="F88" s="41"/>
-      <x:c r="G88" s="42"/>
+      <x:c r="F88" s="37"/>
+      <x:c r="G88" s="41"/>
       <x:c r="H88" s="42"/>
-      <x:c r="I88" s="42"/>
-      <x:c r="J88" s="37"/>
-      <x:c r="K88" s="37"/>
+      <x:c r="I88" s="43"/>
+      <x:c r="J88" s="43"/>
+      <x:c r="K88" s="43"/>
       <x:c r="L88" s="37"/>
       <x:c r="M88" s="37"/>
       <x:c r="N88" s="37"/>
       <x:c r="O88" s="37"/>
-      <x:c r="P88" s="39"/>
-      <x:c r="Q88" s="39"/>
-      <x:c r="R88" s="37"/>
-      <x:c r="S88" s="38"/>
-      <x:c r="T88" s="38"/>
+      <x:c r="P88" s="37"/>
+      <x:c r="Q88" s="37"/>
+      <x:c r="R88" s="39"/>
+      <x:c r="S88" s="39"/>
+      <x:c r="T88" s="37"/>
       <x:c r="U88" s="38"/>
+      <x:c r="V88" s="38"/>
+      <x:c r="W88" s="38"/>
     </x:row>
     <x:row r="89" ht="24" customHeight="1">
       <x:c r="A89" s="37"/>
@@ -20075,22 +20263,24 @@
       <x:c r="C89" s="37"/>
       <x:c r="D89" s="37"/>
       <x:c r="E89" s="37"/>
-      <x:c r="F89" s="41"/>
-      <x:c r="G89" s="42"/>
+      <x:c r="F89" s="37"/>
+      <x:c r="G89" s="41"/>
       <x:c r="H89" s="42"/>
-      <x:c r="I89" s="42"/>
-      <x:c r="J89" s="37"/>
-      <x:c r="K89" s="37"/>
+      <x:c r="I89" s="43"/>
+      <x:c r="J89" s="43"/>
+      <x:c r="K89" s="43"/>
       <x:c r="L89" s="37"/>
       <x:c r="M89" s="37"/>
       <x:c r="N89" s="37"/>
       <x:c r="O89" s="37"/>
-      <x:c r="P89" s="39"/>
-      <x:c r="Q89" s="39"/>
-      <x:c r="R89" s="37"/>
-      <x:c r="S89" s="38"/>
-      <x:c r="T89" s="38"/>
+      <x:c r="P89" s="37"/>
+      <x:c r="Q89" s="37"/>
+      <x:c r="R89" s="39"/>
+      <x:c r="S89" s="39"/>
+      <x:c r="T89" s="37"/>
       <x:c r="U89" s="38"/>
+      <x:c r="V89" s="38"/>
+      <x:c r="W89" s="38"/>
     </x:row>
     <x:row r="90" ht="24" customHeight="1">
       <x:c r="A90" s="37"/>
@@ -20098,22 +20288,24 @@
       <x:c r="C90" s="37"/>
       <x:c r="D90" s="37"/>
       <x:c r="E90" s="37"/>
-      <x:c r="F90" s="41"/>
-      <x:c r="G90" s="42"/>
+      <x:c r="F90" s="37"/>
+      <x:c r="G90" s="41"/>
       <x:c r="H90" s="42"/>
-      <x:c r="I90" s="42"/>
-      <x:c r="J90" s="37"/>
-      <x:c r="K90" s="37"/>
+      <x:c r="I90" s="43"/>
+      <x:c r="J90" s="43"/>
+      <x:c r="K90" s="43"/>
       <x:c r="L90" s="37"/>
       <x:c r="M90" s="37"/>
       <x:c r="N90" s="37"/>
       <x:c r="O90" s="37"/>
-      <x:c r="P90" s="39"/>
-      <x:c r="Q90" s="39"/>
-      <x:c r="R90" s="37"/>
-      <x:c r="S90" s="38"/>
-      <x:c r="T90" s="38"/>
+      <x:c r="P90" s="37"/>
+      <x:c r="Q90" s="37"/>
+      <x:c r="R90" s="39"/>
+      <x:c r="S90" s="39"/>
+      <x:c r="T90" s="37"/>
       <x:c r="U90" s="38"/>
+      <x:c r="V90" s="38"/>
+      <x:c r="W90" s="38"/>
     </x:row>
     <x:row r="91" ht="24" customHeight="1">
       <x:c r="A91" s="37"/>
@@ -20121,22 +20313,24 @@
       <x:c r="C91" s="37"/>
       <x:c r="D91" s="37"/>
       <x:c r="E91" s="37"/>
-      <x:c r="F91" s="41"/>
-      <x:c r="G91" s="42"/>
+      <x:c r="F91" s="37"/>
+      <x:c r="G91" s="41"/>
       <x:c r="H91" s="42"/>
-      <x:c r="I91" s="42"/>
-      <x:c r="J91" s="37"/>
-      <x:c r="K91" s="37"/>
+      <x:c r="I91" s="43"/>
+      <x:c r="J91" s="43"/>
+      <x:c r="K91" s="43"/>
       <x:c r="L91" s="37"/>
       <x:c r="M91" s="37"/>
       <x:c r="N91" s="37"/>
       <x:c r="O91" s="37"/>
-      <x:c r="P91" s="39"/>
-      <x:c r="Q91" s="39"/>
-      <x:c r="R91" s="37"/>
-      <x:c r="S91" s="38"/>
-      <x:c r="T91" s="38"/>
+      <x:c r="P91" s="37"/>
+      <x:c r="Q91" s="37"/>
+      <x:c r="R91" s="39"/>
+      <x:c r="S91" s="39"/>
+      <x:c r="T91" s="37"/>
       <x:c r="U91" s="38"/>
+      <x:c r="V91" s="38"/>
+      <x:c r="W91" s="38"/>
     </x:row>
     <x:row r="92" ht="24" customHeight="1">
       <x:c r="A92" s="37"/>
@@ -20144,22 +20338,24 @@
       <x:c r="C92" s="37"/>
       <x:c r="D92" s="37"/>
       <x:c r="E92" s="37"/>
-      <x:c r="F92" s="41"/>
-      <x:c r="G92" s="42"/>
+      <x:c r="F92" s="37"/>
+      <x:c r="G92" s="41"/>
       <x:c r="H92" s="42"/>
-      <x:c r="I92" s="42"/>
-      <x:c r="J92" s="37"/>
-      <x:c r="K92" s="37"/>
+      <x:c r="I92" s="43"/>
+      <x:c r="J92" s="43"/>
+      <x:c r="K92" s="43"/>
       <x:c r="L92" s="37"/>
       <x:c r="M92" s="37"/>
       <x:c r="N92" s="37"/>
       <x:c r="O92" s="37"/>
-      <x:c r="P92" s="39"/>
-      <x:c r="Q92" s="39"/>
-      <x:c r="R92" s="37"/>
-      <x:c r="S92" s="38"/>
-      <x:c r="T92" s="38"/>
+      <x:c r="P92" s="37"/>
+      <x:c r="Q92" s="37"/>
+      <x:c r="R92" s="39"/>
+      <x:c r="S92" s="39"/>
+      <x:c r="T92" s="37"/>
       <x:c r="U92" s="38"/>
+      <x:c r="V92" s="38"/>
+      <x:c r="W92" s="38"/>
     </x:row>
     <x:row r="93" ht="24" customHeight="1">
       <x:c r="A93" s="37"/>
@@ -20167,22 +20363,24 @@
       <x:c r="C93" s="37"/>
       <x:c r="D93" s="37"/>
       <x:c r="E93" s="37"/>
-      <x:c r="F93" s="41"/>
-      <x:c r="G93" s="42"/>
+      <x:c r="F93" s="37"/>
+      <x:c r="G93" s="41"/>
       <x:c r="H93" s="42"/>
-      <x:c r="I93" s="42"/>
-      <x:c r="J93" s="37"/>
-      <x:c r="K93" s="37"/>
+      <x:c r="I93" s="43"/>
+      <x:c r="J93" s="43"/>
+      <x:c r="K93" s="43"/>
       <x:c r="L93" s="37"/>
       <x:c r="M93" s="37"/>
       <x:c r="N93" s="37"/>
       <x:c r="O93" s="37"/>
-      <x:c r="P93" s="39"/>
-      <x:c r="Q93" s="39"/>
-      <x:c r="R93" s="37"/>
-      <x:c r="S93" s="38"/>
-      <x:c r="T93" s="38"/>
+      <x:c r="P93" s="37"/>
+      <x:c r="Q93" s="37"/>
+      <x:c r="R93" s="39"/>
+      <x:c r="S93" s="39"/>
+      <x:c r="T93" s="37"/>
       <x:c r="U93" s="38"/>
+      <x:c r="V93" s="38"/>
+      <x:c r="W93" s="38"/>
     </x:row>
     <x:row r="94" ht="24" customHeight="1">
       <x:c r="A94" s="37"/>
@@ -20190,22 +20388,24 @@
       <x:c r="C94" s="37"/>
       <x:c r="D94" s="37"/>
       <x:c r="E94" s="37"/>
-      <x:c r="F94" s="41"/>
-      <x:c r="G94" s="42"/>
+      <x:c r="F94" s="37"/>
+      <x:c r="G94" s="41"/>
       <x:c r="H94" s="42"/>
-      <x:c r="I94" s="42"/>
-      <x:c r="J94" s="37"/>
-      <x:c r="K94" s="37"/>
+      <x:c r="I94" s="43"/>
+      <x:c r="J94" s="43"/>
+      <x:c r="K94" s="43"/>
       <x:c r="L94" s="37"/>
       <x:c r="M94" s="37"/>
       <x:c r="N94" s="37"/>
       <x:c r="O94" s="37"/>
-      <x:c r="P94" s="39"/>
-      <x:c r="Q94" s="39"/>
-      <x:c r="R94" s="37"/>
-      <x:c r="S94" s="38"/>
-      <x:c r="T94" s="38"/>
+      <x:c r="P94" s="37"/>
+      <x:c r="Q94" s="37"/>
+      <x:c r="R94" s="39"/>
+      <x:c r="S94" s="39"/>
+      <x:c r="T94" s="37"/>
       <x:c r="U94" s="38"/>
+      <x:c r="V94" s="38"/>
+      <x:c r="W94" s="38"/>
     </x:row>
     <x:row r="95" ht="24" customHeight="1">
       <x:c r="A95" s="37"/>
@@ -20213,22 +20413,24 @@
       <x:c r="C95" s="37"/>
       <x:c r="D95" s="37"/>
       <x:c r="E95" s="37"/>
-      <x:c r="F95" s="41"/>
-      <x:c r="G95" s="42"/>
+      <x:c r="F95" s="37"/>
+      <x:c r="G95" s="41"/>
       <x:c r="H95" s="42"/>
-      <x:c r="I95" s="42"/>
-      <x:c r="J95" s="37"/>
-      <x:c r="K95" s="37"/>
+      <x:c r="I95" s="43"/>
+      <x:c r="J95" s="43"/>
+      <x:c r="K95" s="43"/>
       <x:c r="L95" s="37"/>
       <x:c r="M95" s="37"/>
       <x:c r="N95" s="37"/>
       <x:c r="O95" s="37"/>
-      <x:c r="P95" s="39"/>
-      <x:c r="Q95" s="39"/>
-      <x:c r="R95" s="37"/>
-      <x:c r="S95" s="38"/>
-      <x:c r="T95" s="38"/>
+      <x:c r="P95" s="37"/>
+      <x:c r="Q95" s="37"/>
+      <x:c r="R95" s="39"/>
+      <x:c r="S95" s="39"/>
+      <x:c r="T95" s="37"/>
       <x:c r="U95" s="38"/>
+      <x:c r="V95" s="38"/>
+      <x:c r="W95" s="38"/>
     </x:row>
     <x:row r="96" ht="24" customHeight="1">
       <x:c r="A96" s="37"/>
@@ -20236,22 +20438,24 @@
       <x:c r="C96" s="37"/>
       <x:c r="D96" s="37"/>
       <x:c r="E96" s="37"/>
-      <x:c r="F96" s="41"/>
-      <x:c r="G96" s="42"/>
+      <x:c r="F96" s="37"/>
+      <x:c r="G96" s="41"/>
       <x:c r="H96" s="42"/>
-      <x:c r="I96" s="42"/>
-      <x:c r="J96" s="37"/>
-      <x:c r="K96" s="37"/>
+      <x:c r="I96" s="43"/>
+      <x:c r="J96" s="43"/>
+      <x:c r="K96" s="43"/>
       <x:c r="L96" s="37"/>
       <x:c r="M96" s="37"/>
       <x:c r="N96" s="37"/>
       <x:c r="O96" s="37"/>
-      <x:c r="P96" s="39"/>
-      <x:c r="Q96" s="39"/>
-      <x:c r="R96" s="37"/>
-      <x:c r="S96" s="38"/>
-      <x:c r="T96" s="38"/>
+      <x:c r="P96" s="37"/>
+      <x:c r="Q96" s="37"/>
+      <x:c r="R96" s="39"/>
+      <x:c r="S96" s="39"/>
+      <x:c r="T96" s="37"/>
       <x:c r="U96" s="38"/>
+      <x:c r="V96" s="38"/>
+      <x:c r="W96" s="38"/>
     </x:row>
     <x:row r="97" ht="24" customHeight="1">
       <x:c r="A97" s="37"/>
@@ -20259,22 +20463,24 @@
       <x:c r="C97" s="37"/>
       <x:c r="D97" s="37"/>
       <x:c r="E97" s="37"/>
-      <x:c r="F97" s="41"/>
-      <x:c r="G97" s="42"/>
+      <x:c r="F97" s="37"/>
+      <x:c r="G97" s="41"/>
       <x:c r="H97" s="42"/>
-      <x:c r="I97" s="42"/>
-      <x:c r="J97" s="37"/>
-      <x:c r="K97" s="37"/>
+      <x:c r="I97" s="43"/>
+      <x:c r="J97" s="43"/>
+      <x:c r="K97" s="43"/>
       <x:c r="L97" s="37"/>
       <x:c r="M97" s="37"/>
       <x:c r="N97" s="37"/>
       <x:c r="O97" s="37"/>
-      <x:c r="P97" s="39"/>
-      <x:c r="Q97" s="39"/>
-      <x:c r="R97" s="37"/>
-      <x:c r="S97" s="38"/>
-      <x:c r="T97" s="38"/>
+      <x:c r="P97" s="37"/>
+      <x:c r="Q97" s="37"/>
+      <x:c r="R97" s="39"/>
+      <x:c r="S97" s="39"/>
+      <x:c r="T97" s="37"/>
       <x:c r="U97" s="38"/>
+      <x:c r="V97" s="38"/>
+      <x:c r="W97" s="38"/>
     </x:row>
     <x:row r="98" ht="24" customHeight="1">
       <x:c r="A98" s="37"/>
@@ -20282,22 +20488,24 @@
       <x:c r="C98" s="37"/>
       <x:c r="D98" s="37"/>
       <x:c r="E98" s="37"/>
-      <x:c r="F98" s="41"/>
-      <x:c r="G98" s="42"/>
+      <x:c r="F98" s="37"/>
+      <x:c r="G98" s="41"/>
       <x:c r="H98" s="42"/>
-      <x:c r="I98" s="42"/>
-      <x:c r="J98" s="37"/>
-      <x:c r="K98" s="37"/>
+      <x:c r="I98" s="43"/>
+      <x:c r="J98" s="43"/>
+      <x:c r="K98" s="43"/>
       <x:c r="L98" s="37"/>
       <x:c r="M98" s="37"/>
       <x:c r="N98" s="37"/>
       <x:c r="O98" s="37"/>
-      <x:c r="P98" s="39"/>
-      <x:c r="Q98" s="39"/>
-      <x:c r="R98" s="37"/>
-      <x:c r="S98" s="38"/>
-      <x:c r="T98" s="38"/>
+      <x:c r="P98" s="37"/>
+      <x:c r="Q98" s="37"/>
+      <x:c r="R98" s="39"/>
+      <x:c r="S98" s="39"/>
+      <x:c r="T98" s="37"/>
       <x:c r="U98" s="38"/>
+      <x:c r="V98" s="38"/>
+      <x:c r="W98" s="38"/>
     </x:row>
     <x:row r="99" ht="24" customHeight="1">
       <x:c r="A99" s="37"/>
@@ -20305,22 +20513,24 @@
       <x:c r="C99" s="37"/>
       <x:c r="D99" s="37"/>
       <x:c r="E99" s="37"/>
-      <x:c r="F99" s="41"/>
-      <x:c r="G99" s="42"/>
+      <x:c r="F99" s="37"/>
+      <x:c r="G99" s="41"/>
       <x:c r="H99" s="42"/>
-      <x:c r="I99" s="42"/>
-      <x:c r="J99" s="37"/>
-      <x:c r="K99" s="37"/>
+      <x:c r="I99" s="43"/>
+      <x:c r="J99" s="43"/>
+      <x:c r="K99" s="43"/>
       <x:c r="L99" s="37"/>
       <x:c r="M99" s="37"/>
       <x:c r="N99" s="37"/>
       <x:c r="O99" s="37"/>
-      <x:c r="P99" s="39"/>
-      <x:c r="Q99" s="39"/>
-      <x:c r="R99" s="37"/>
-      <x:c r="S99" s="38"/>
-      <x:c r="T99" s="38"/>
+      <x:c r="P99" s="37"/>
+      <x:c r="Q99" s="37"/>
+      <x:c r="R99" s="39"/>
+      <x:c r="S99" s="39"/>
+      <x:c r="T99" s="37"/>
       <x:c r="U99" s="38"/>
+      <x:c r="V99" s="38"/>
+      <x:c r="W99" s="38"/>
     </x:row>
     <x:row r="100" ht="24" customHeight="1">
       <x:c r="A100" s="37"/>
@@ -20328,22 +20538,24 @@
       <x:c r="C100" s="37"/>
       <x:c r="D100" s="37"/>
       <x:c r="E100" s="37"/>
-      <x:c r="F100" s="41"/>
-      <x:c r="G100" s="42"/>
+      <x:c r="F100" s="37"/>
+      <x:c r="G100" s="41"/>
       <x:c r="H100" s="42"/>
-      <x:c r="I100" s="42"/>
-      <x:c r="J100" s="37"/>
-      <x:c r="K100" s="37"/>
+      <x:c r="I100" s="43"/>
+      <x:c r="J100" s="43"/>
+      <x:c r="K100" s="43"/>
       <x:c r="L100" s="37"/>
       <x:c r="M100" s="37"/>
       <x:c r="N100" s="37"/>
       <x:c r="O100" s="37"/>
-      <x:c r="P100" s="39"/>
-      <x:c r="Q100" s="39"/>
-      <x:c r="R100" s="37"/>
-      <x:c r="S100" s="38"/>
-      <x:c r="T100" s="38"/>
+      <x:c r="P100" s="37"/>
+      <x:c r="Q100" s="37"/>
+      <x:c r="R100" s="39"/>
+      <x:c r="S100" s="39"/>
+      <x:c r="T100" s="37"/>
       <x:c r="U100" s="38"/>
+      <x:c r="V100" s="38"/>
+      <x:c r="W100" s="38"/>
     </x:row>
     <x:row r="101" ht="24" customHeight="1">
       <x:c r="A101" s="37"/>
@@ -20351,22 +20563,24 @@
       <x:c r="C101" s="37"/>
       <x:c r="D101" s="37"/>
       <x:c r="E101" s="37"/>
-      <x:c r="F101" s="41"/>
-      <x:c r="G101" s="42"/>
+      <x:c r="F101" s="37"/>
+      <x:c r="G101" s="41"/>
       <x:c r="H101" s="42"/>
-      <x:c r="I101" s="42"/>
-      <x:c r="J101" s="37"/>
-      <x:c r="K101" s="37"/>
+      <x:c r="I101" s="43"/>
+      <x:c r="J101" s="43"/>
+      <x:c r="K101" s="43"/>
       <x:c r="L101" s="37"/>
       <x:c r="M101" s="37"/>
       <x:c r="N101" s="37"/>
       <x:c r="O101" s="37"/>
-      <x:c r="P101" s="39"/>
-      <x:c r="Q101" s="39"/>
-      <x:c r="R101" s="37"/>
-      <x:c r="S101" s="38"/>
-      <x:c r="T101" s="38"/>
+      <x:c r="P101" s="37"/>
+      <x:c r="Q101" s="37"/>
+      <x:c r="R101" s="39"/>
+      <x:c r="S101" s="39"/>
+      <x:c r="T101" s="37"/>
       <x:c r="U101" s="38"/>
+      <x:c r="V101" s="38"/>
+      <x:c r="W101" s="38"/>
     </x:row>
     <x:row r="102" ht="24" customHeight="1">
       <x:c r="A102" s="37"/>
@@ -20374,22 +20588,24 @@
       <x:c r="C102" s="37"/>
       <x:c r="D102" s="37"/>
       <x:c r="E102" s="37"/>
-      <x:c r="F102" s="41"/>
-      <x:c r="G102" s="42"/>
+      <x:c r="F102" s="37"/>
+      <x:c r="G102" s="41"/>
       <x:c r="H102" s="42"/>
-      <x:c r="I102" s="42"/>
-      <x:c r="J102" s="37"/>
-      <x:c r="K102" s="37"/>
+      <x:c r="I102" s="43"/>
+      <x:c r="J102" s="43"/>
+      <x:c r="K102" s="43"/>
       <x:c r="L102" s="37"/>
       <x:c r="M102" s="37"/>
       <x:c r="N102" s="37"/>
       <x:c r="O102" s="37"/>
-      <x:c r="P102" s="39"/>
-      <x:c r="Q102" s="39"/>
-      <x:c r="R102" s="37"/>
-      <x:c r="S102" s="38"/>
-      <x:c r="T102" s="38"/>
+      <x:c r="P102" s="37"/>
+      <x:c r="Q102" s="37"/>
+      <x:c r="R102" s="39"/>
+      <x:c r="S102" s="39"/>
+      <x:c r="T102" s="37"/>
       <x:c r="U102" s="38"/>
+      <x:c r="V102" s="38"/>
+      <x:c r="W102" s="38"/>
     </x:row>
     <x:row r="103" ht="24" customHeight="1">
       <x:c r="A103" s="37"/>
@@ -20397,22 +20613,24 @@
       <x:c r="C103" s="37"/>
       <x:c r="D103" s="37"/>
       <x:c r="E103" s="37"/>
-      <x:c r="F103" s="41"/>
-      <x:c r="G103" s="42"/>
+      <x:c r="F103" s="37"/>
+      <x:c r="G103" s="41"/>
       <x:c r="H103" s="42"/>
-      <x:c r="I103" s="42"/>
-      <x:c r="J103" s="37"/>
-      <x:c r="K103" s="37"/>
+      <x:c r="I103" s="43"/>
+      <x:c r="J103" s="43"/>
+      <x:c r="K103" s="43"/>
       <x:c r="L103" s="37"/>
       <x:c r="M103" s="37"/>
       <x:c r="N103" s="37"/>
       <x:c r="O103" s="37"/>
-      <x:c r="P103" s="39"/>
-      <x:c r="Q103" s="39"/>
-      <x:c r="R103" s="37"/>
-      <x:c r="S103" s="38"/>
-      <x:c r="T103" s="38"/>
+      <x:c r="P103" s="37"/>
+      <x:c r="Q103" s="37"/>
+      <x:c r="R103" s="39"/>
+      <x:c r="S103" s="39"/>
+      <x:c r="T103" s="37"/>
       <x:c r="U103" s="38"/>
+      <x:c r="V103" s="38"/>
+      <x:c r="W103" s="38"/>
     </x:row>
     <x:row r="104" ht="24" customHeight="1">
       <x:c r="A104" s="37"/>
@@ -20420,43 +20638,48 @@
       <x:c r="C104" s="37"/>
       <x:c r="D104" s="37"/>
       <x:c r="E104" s="37"/>
-      <x:c r="F104" s="41"/>
-      <x:c r="G104" s="42"/>
+      <x:c r="F104" s="37"/>
+      <x:c r="G104" s="41"/>
       <x:c r="H104" s="42"/>
-      <x:c r="I104" s="42"/>
-      <x:c r="J104" s="37"/>
-      <x:c r="K104" s="37"/>
+      <x:c r="I104" s="43"/>
+      <x:c r="J104" s="43"/>
+      <x:c r="K104" s="43"/>
       <x:c r="L104" s="37"/>
       <x:c r="M104" s="37"/>
       <x:c r="N104" s="37"/>
       <x:c r="O104" s="37"/>
-      <x:c r="P104" s="39"/>
-      <x:c r="Q104" s="39"/>
-      <x:c r="R104" s="37"/>
-      <x:c r="S104" s="38"/>
-      <x:c r="T104" s="38"/>
+      <x:c r="P104" s="37"/>
+      <x:c r="Q104" s="37"/>
+      <x:c r="R104" s="39"/>
+      <x:c r="S104" s="39"/>
+      <x:c r="T104" s="37"/>
       <x:c r="U104" s="38"/>
+      <x:c r="V104" s="38"/>
+      <x:c r="W104" s="38"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:U1"/>
-    <x:mergeCell ref="A2:U2"/>
-    <x:mergeCell ref="A3:U3"/>
+    <x:mergeCell ref="A1:W1"/>
+    <x:mergeCell ref="A2:W2"/>
+    <x:mergeCell ref="A3:W3"/>
   </x:mergeCells>
-  <x:dataValidations count="3">
+  <x:dataValidations count="4">
     <x:dataValidation type="list" sqref="D5:D104">
       <x:formula1>"trip,group,individual"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="L5:L104">
+    <x:dataValidation type="list" sqref="F5:F104">
+      <x:formula1>"fixed,per_traveler,percentage_of_individual"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="N5:N104">
       <x:formula1>"through_hs,external"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="M5:M104">
+    <x:dataValidation type="list" sqref="O5:O104">
       <x:formula1>"planned,committed,partially_paid,paid,canceled"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re58207e7fabb4a42"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5219ab4a30e94e80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20551,7 +20774,7 @@
       <x:c r="A5" s="37"/>
       <x:c r="B5" s="37"/>
       <x:c r="C5" s="37"/>
-      <x:c r="D5" s="42"/>
+      <x:c r="D5" s="43"/>
       <x:c r="E5" s="37"/>
       <x:c r="F5" s="37"/>
       <x:c r="G5" s="38"/>
@@ -20562,7 +20785,7 @@
       <x:c r="A6" s="37"/>
       <x:c r="B6" s="37"/>
       <x:c r="C6" s="37"/>
-      <x:c r="D6" s="42"/>
+      <x:c r="D6" s="43"/>
       <x:c r="E6" s="37"/>
       <x:c r="F6" s="37"/>
       <x:c r="G6" s="38"/>
@@ -20573,7 +20796,7 @@
       <x:c r="A7" s="37"/>
       <x:c r="B7" s="37"/>
       <x:c r="C7" s="37"/>
-      <x:c r="D7" s="42"/>
+      <x:c r="D7" s="43"/>
       <x:c r="E7" s="37"/>
       <x:c r="F7" s="37"/>
       <x:c r="G7" s="38"/>
@@ -20584,7 +20807,7 @@
       <x:c r="A8" s="37"/>
       <x:c r="B8" s="37"/>
       <x:c r="C8" s="37"/>
-      <x:c r="D8" s="42"/>
+      <x:c r="D8" s="43"/>
       <x:c r="E8" s="37"/>
       <x:c r="F8" s="37"/>
       <x:c r="G8" s="38"/>
@@ -20595,7 +20818,7 @@
       <x:c r="A9" s="37"/>
       <x:c r="B9" s="37"/>
       <x:c r="C9" s="37"/>
-      <x:c r="D9" s="42"/>
+      <x:c r="D9" s="43"/>
       <x:c r="E9" s="37"/>
       <x:c r="F9" s="37"/>
       <x:c r="G9" s="38"/>
@@ -20606,7 +20829,7 @@
       <x:c r="A10" s="37"/>
       <x:c r="B10" s="37"/>
       <x:c r="C10" s="37"/>
-      <x:c r="D10" s="42"/>
+      <x:c r="D10" s="43"/>
       <x:c r="E10" s="37"/>
       <x:c r="F10" s="37"/>
       <x:c r="G10" s="38"/>
@@ -20617,7 +20840,7 @@
       <x:c r="A11" s="37"/>
       <x:c r="B11" s="37"/>
       <x:c r="C11" s="37"/>
-      <x:c r="D11" s="42"/>
+      <x:c r="D11" s="43"/>
       <x:c r="E11" s="37"/>
       <x:c r="F11" s="37"/>
       <x:c r="G11" s="38"/>
@@ -20628,7 +20851,7 @@
       <x:c r="A12" s="37"/>
       <x:c r="B12" s="37"/>
       <x:c r="C12" s="37"/>
-      <x:c r="D12" s="42"/>
+      <x:c r="D12" s="43"/>
       <x:c r="E12" s="37"/>
       <x:c r="F12" s="37"/>
       <x:c r="G12" s="38"/>
@@ -20639,7 +20862,7 @@
       <x:c r="A13" s="37"/>
       <x:c r="B13" s="37"/>
       <x:c r="C13" s="37"/>
-      <x:c r="D13" s="42"/>
+      <x:c r="D13" s="43"/>
       <x:c r="E13" s="37"/>
       <x:c r="F13" s="37"/>
       <x:c r="G13" s="38"/>
@@ -20650,7 +20873,7 @@
       <x:c r="A14" s="37"/>
       <x:c r="B14" s="37"/>
       <x:c r="C14" s="37"/>
-      <x:c r="D14" s="42"/>
+      <x:c r="D14" s="43"/>
       <x:c r="E14" s="37"/>
       <x:c r="F14" s="37"/>
       <x:c r="G14" s="38"/>
@@ -20661,7 +20884,7 @@
       <x:c r="A15" s="37"/>
       <x:c r="B15" s="37"/>
       <x:c r="C15" s="37"/>
-      <x:c r="D15" s="42"/>
+      <x:c r="D15" s="43"/>
       <x:c r="E15" s="37"/>
       <x:c r="F15" s="37"/>
       <x:c r="G15" s="38"/>
@@ -20672,7 +20895,7 @@
       <x:c r="A16" s="37"/>
       <x:c r="B16" s="37"/>
       <x:c r="C16" s="37"/>
-      <x:c r="D16" s="42"/>
+      <x:c r="D16" s="43"/>
       <x:c r="E16" s="37"/>
       <x:c r="F16" s="37"/>
       <x:c r="G16" s="38"/>
@@ -20683,7 +20906,7 @@
       <x:c r="A17" s="37"/>
       <x:c r="B17" s="37"/>
       <x:c r="C17" s="37"/>
-      <x:c r="D17" s="42"/>
+      <x:c r="D17" s="43"/>
       <x:c r="E17" s="37"/>
       <x:c r="F17" s="37"/>
       <x:c r="G17" s="38"/>
@@ -20694,7 +20917,7 @@
       <x:c r="A18" s="37"/>
       <x:c r="B18" s="37"/>
       <x:c r="C18" s="37"/>
-      <x:c r="D18" s="42"/>
+      <x:c r="D18" s="43"/>
       <x:c r="E18" s="37"/>
       <x:c r="F18" s="37"/>
       <x:c r="G18" s="38"/>
@@ -20705,7 +20928,7 @@
       <x:c r="A19" s="37"/>
       <x:c r="B19" s="37"/>
       <x:c r="C19" s="37"/>
-      <x:c r="D19" s="42"/>
+      <x:c r="D19" s="43"/>
       <x:c r="E19" s="37"/>
       <x:c r="F19" s="37"/>
       <x:c r="G19" s="38"/>
@@ -20716,7 +20939,7 @@
       <x:c r="A20" s="37"/>
       <x:c r="B20" s="37"/>
       <x:c r="C20" s="37"/>
-      <x:c r="D20" s="42"/>
+      <x:c r="D20" s="43"/>
       <x:c r="E20" s="37"/>
       <x:c r="F20" s="37"/>
       <x:c r="G20" s="38"/>
@@ -20727,7 +20950,7 @@
       <x:c r="A21" s="37"/>
       <x:c r="B21" s="37"/>
       <x:c r="C21" s="37"/>
-      <x:c r="D21" s="42"/>
+      <x:c r="D21" s="43"/>
       <x:c r="E21" s="37"/>
       <x:c r="F21" s="37"/>
       <x:c r="G21" s="38"/>
@@ -20738,7 +20961,7 @@
       <x:c r="A22" s="37"/>
       <x:c r="B22" s="37"/>
       <x:c r="C22" s="37"/>
-      <x:c r="D22" s="42"/>
+      <x:c r="D22" s="43"/>
       <x:c r="E22" s="37"/>
       <x:c r="F22" s="37"/>
       <x:c r="G22" s="38"/>
@@ -20749,7 +20972,7 @@
       <x:c r="A23" s="37"/>
       <x:c r="B23" s="37"/>
       <x:c r="C23" s="37"/>
-      <x:c r="D23" s="42"/>
+      <x:c r="D23" s="43"/>
       <x:c r="E23" s="37"/>
       <x:c r="F23" s="37"/>
       <x:c r="G23" s="38"/>
@@ -20760,7 +20983,7 @@
       <x:c r="A24" s="37"/>
       <x:c r="B24" s="37"/>
       <x:c r="C24" s="37"/>
-      <x:c r="D24" s="42"/>
+      <x:c r="D24" s="43"/>
       <x:c r="E24" s="37"/>
       <x:c r="F24" s="37"/>
       <x:c r="G24" s="38"/>
@@ -20771,7 +20994,7 @@
       <x:c r="A25" s="37"/>
       <x:c r="B25" s="37"/>
       <x:c r="C25" s="37"/>
-      <x:c r="D25" s="42"/>
+      <x:c r="D25" s="43"/>
       <x:c r="E25" s="37"/>
       <x:c r="F25" s="37"/>
       <x:c r="G25" s="38"/>
@@ -20782,7 +21005,7 @@
       <x:c r="A26" s="37"/>
       <x:c r="B26" s="37"/>
       <x:c r="C26" s="37"/>
-      <x:c r="D26" s="42"/>
+      <x:c r="D26" s="43"/>
       <x:c r="E26" s="37"/>
       <x:c r="F26" s="37"/>
       <x:c r="G26" s="38"/>
@@ -20793,7 +21016,7 @@
       <x:c r="A27" s="37"/>
       <x:c r="B27" s="37"/>
       <x:c r="C27" s="37"/>
-      <x:c r="D27" s="42"/>
+      <x:c r="D27" s="43"/>
       <x:c r="E27" s="37"/>
       <x:c r="F27" s="37"/>
       <x:c r="G27" s="38"/>
@@ -20804,7 +21027,7 @@
       <x:c r="A28" s="37"/>
       <x:c r="B28" s="37"/>
       <x:c r="C28" s="37"/>
-      <x:c r="D28" s="42"/>
+      <x:c r="D28" s="43"/>
       <x:c r="E28" s="37"/>
       <x:c r="F28" s="37"/>
       <x:c r="G28" s="38"/>
@@ -20815,7 +21038,7 @@
       <x:c r="A29" s="37"/>
       <x:c r="B29" s="37"/>
       <x:c r="C29" s="37"/>
-      <x:c r="D29" s="42"/>
+      <x:c r="D29" s="43"/>
       <x:c r="E29" s="37"/>
       <x:c r="F29" s="37"/>
       <x:c r="G29" s="38"/>
@@ -20826,7 +21049,7 @@
       <x:c r="A30" s="37"/>
       <x:c r="B30" s="37"/>
       <x:c r="C30" s="37"/>
-      <x:c r="D30" s="42"/>
+      <x:c r="D30" s="43"/>
       <x:c r="E30" s="37"/>
       <x:c r="F30" s="37"/>
       <x:c r="G30" s="38"/>
@@ -20837,7 +21060,7 @@
       <x:c r="A31" s="37"/>
       <x:c r="B31" s="37"/>
       <x:c r="C31" s="37"/>
-      <x:c r="D31" s="42"/>
+      <x:c r="D31" s="43"/>
       <x:c r="E31" s="37"/>
       <x:c r="F31" s="37"/>
       <x:c r="G31" s="38"/>
@@ -20848,7 +21071,7 @@
       <x:c r="A32" s="37"/>
       <x:c r="B32" s="37"/>
       <x:c r="C32" s="37"/>
-      <x:c r="D32" s="42"/>
+      <x:c r="D32" s="43"/>
       <x:c r="E32" s="37"/>
       <x:c r="F32" s="37"/>
       <x:c r="G32" s="38"/>
@@ -20859,7 +21082,7 @@
       <x:c r="A33" s="37"/>
       <x:c r="B33" s="37"/>
       <x:c r="C33" s="37"/>
-      <x:c r="D33" s="42"/>
+      <x:c r="D33" s="43"/>
       <x:c r="E33" s="37"/>
       <x:c r="F33" s="37"/>
       <x:c r="G33" s="38"/>
@@ -20870,7 +21093,7 @@
       <x:c r="A34" s="37"/>
       <x:c r="B34" s="37"/>
       <x:c r="C34" s="37"/>
-      <x:c r="D34" s="42"/>
+      <x:c r="D34" s="43"/>
       <x:c r="E34" s="37"/>
       <x:c r="F34" s="37"/>
       <x:c r="G34" s="38"/>
@@ -20881,7 +21104,7 @@
       <x:c r="A35" s="37"/>
       <x:c r="B35" s="37"/>
       <x:c r="C35" s="37"/>
-      <x:c r="D35" s="42"/>
+      <x:c r="D35" s="43"/>
       <x:c r="E35" s="37"/>
       <x:c r="F35" s="37"/>
       <x:c r="G35" s="38"/>
@@ -20892,7 +21115,7 @@
       <x:c r="A36" s="37"/>
       <x:c r="B36" s="37"/>
       <x:c r="C36" s="37"/>
-      <x:c r="D36" s="42"/>
+      <x:c r="D36" s="43"/>
       <x:c r="E36" s="37"/>
       <x:c r="F36" s="37"/>
       <x:c r="G36" s="38"/>
@@ -20903,7 +21126,7 @@
       <x:c r="A37" s="37"/>
       <x:c r="B37" s="37"/>
       <x:c r="C37" s="37"/>
-      <x:c r="D37" s="42"/>
+      <x:c r="D37" s="43"/>
       <x:c r="E37" s="37"/>
       <x:c r="F37" s="37"/>
       <x:c r="G37" s="38"/>
@@ -20914,7 +21137,7 @@
       <x:c r="A38" s="37"/>
       <x:c r="B38" s="37"/>
       <x:c r="C38" s="37"/>
-      <x:c r="D38" s="42"/>
+      <x:c r="D38" s="43"/>
       <x:c r="E38" s="37"/>
       <x:c r="F38" s="37"/>
       <x:c r="G38" s="38"/>
@@ -20925,7 +21148,7 @@
       <x:c r="A39" s="37"/>
       <x:c r="B39" s="37"/>
       <x:c r="C39" s="37"/>
-      <x:c r="D39" s="42"/>
+      <x:c r="D39" s="43"/>
       <x:c r="E39" s="37"/>
       <x:c r="F39" s="37"/>
       <x:c r="G39" s="38"/>
@@ -20936,7 +21159,7 @@
       <x:c r="A40" s="37"/>
       <x:c r="B40" s="37"/>
       <x:c r="C40" s="37"/>
-      <x:c r="D40" s="42"/>
+      <x:c r="D40" s="43"/>
       <x:c r="E40" s="37"/>
       <x:c r="F40" s="37"/>
       <x:c r="G40" s="38"/>
@@ -20947,7 +21170,7 @@
       <x:c r="A41" s="37"/>
       <x:c r="B41" s="37"/>
       <x:c r="C41" s="37"/>
-      <x:c r="D41" s="42"/>
+      <x:c r="D41" s="43"/>
       <x:c r="E41" s="37"/>
       <x:c r="F41" s="37"/>
       <x:c r="G41" s="38"/>
@@ -20958,7 +21181,7 @@
       <x:c r="A42" s="37"/>
       <x:c r="B42" s="37"/>
       <x:c r="C42" s="37"/>
-      <x:c r="D42" s="42"/>
+      <x:c r="D42" s="43"/>
       <x:c r="E42" s="37"/>
       <x:c r="F42" s="37"/>
       <x:c r="G42" s="38"/>
@@ -20969,7 +21192,7 @@
       <x:c r="A43" s="37"/>
       <x:c r="B43" s="37"/>
       <x:c r="C43" s="37"/>
-      <x:c r="D43" s="42"/>
+      <x:c r="D43" s="43"/>
       <x:c r="E43" s="37"/>
       <x:c r="F43" s="37"/>
       <x:c r="G43" s="38"/>
@@ -20980,7 +21203,7 @@
       <x:c r="A44" s="37"/>
       <x:c r="B44" s="37"/>
       <x:c r="C44" s="37"/>
-      <x:c r="D44" s="42"/>
+      <x:c r="D44" s="43"/>
       <x:c r="E44" s="37"/>
       <x:c r="F44" s="37"/>
       <x:c r="G44" s="38"/>
@@ -20991,7 +21214,7 @@
       <x:c r="A45" s="37"/>
       <x:c r="B45" s="37"/>
       <x:c r="C45" s="37"/>
-      <x:c r="D45" s="42"/>
+      <x:c r="D45" s="43"/>
       <x:c r="E45" s="37"/>
       <x:c r="F45" s="37"/>
       <x:c r="G45" s="38"/>
@@ -21002,7 +21225,7 @@
       <x:c r="A46" s="37"/>
       <x:c r="B46" s="37"/>
       <x:c r="C46" s="37"/>
-      <x:c r="D46" s="42"/>
+      <x:c r="D46" s="43"/>
       <x:c r="E46" s="37"/>
       <x:c r="F46" s="37"/>
       <x:c r="G46" s="38"/>
@@ -21013,7 +21236,7 @@
       <x:c r="A47" s="37"/>
       <x:c r="B47" s="37"/>
       <x:c r="C47" s="37"/>
-      <x:c r="D47" s="42"/>
+      <x:c r="D47" s="43"/>
       <x:c r="E47" s="37"/>
       <x:c r="F47" s="37"/>
       <x:c r="G47" s="38"/>
@@ -21024,7 +21247,7 @@
       <x:c r="A48" s="37"/>
       <x:c r="B48" s="37"/>
       <x:c r="C48" s="37"/>
-      <x:c r="D48" s="42"/>
+      <x:c r="D48" s="43"/>
       <x:c r="E48" s="37"/>
       <x:c r="F48" s="37"/>
       <x:c r="G48" s="38"/>
@@ -21035,7 +21258,7 @@
       <x:c r="A49" s="37"/>
       <x:c r="B49" s="37"/>
       <x:c r="C49" s="37"/>
-      <x:c r="D49" s="42"/>
+      <x:c r="D49" s="43"/>
       <x:c r="E49" s="37"/>
       <x:c r="F49" s="37"/>
       <x:c r="G49" s="38"/>
@@ -21046,7 +21269,7 @@
       <x:c r="A50" s="37"/>
       <x:c r="B50" s="37"/>
       <x:c r="C50" s="37"/>
-      <x:c r="D50" s="42"/>
+      <x:c r="D50" s="43"/>
       <x:c r="E50" s="37"/>
       <x:c r="F50" s="37"/>
       <x:c r="G50" s="38"/>
@@ -21057,7 +21280,7 @@
       <x:c r="A51" s="37"/>
       <x:c r="B51" s="37"/>
       <x:c r="C51" s="37"/>
-      <x:c r="D51" s="42"/>
+      <x:c r="D51" s="43"/>
       <x:c r="E51" s="37"/>
       <x:c r="F51" s="37"/>
       <x:c r="G51" s="38"/>
@@ -21068,7 +21291,7 @@
       <x:c r="A52" s="37"/>
       <x:c r="B52" s="37"/>
       <x:c r="C52" s="37"/>
-      <x:c r="D52" s="42"/>
+      <x:c r="D52" s="43"/>
       <x:c r="E52" s="37"/>
       <x:c r="F52" s="37"/>
       <x:c r="G52" s="38"/>
@@ -21079,7 +21302,7 @@
       <x:c r="A53" s="37"/>
       <x:c r="B53" s="37"/>
       <x:c r="C53" s="37"/>
-      <x:c r="D53" s="42"/>
+      <x:c r="D53" s="43"/>
       <x:c r="E53" s="37"/>
       <x:c r="F53" s="37"/>
       <x:c r="G53" s="38"/>
@@ -21090,7 +21313,7 @@
       <x:c r="A54" s="37"/>
       <x:c r="B54" s="37"/>
       <x:c r="C54" s="37"/>
-      <x:c r="D54" s="42"/>
+      <x:c r="D54" s="43"/>
       <x:c r="E54" s="37"/>
       <x:c r="F54" s="37"/>
       <x:c r="G54" s="38"/>
@@ -21101,7 +21324,7 @@
       <x:c r="A55" s="37"/>
       <x:c r="B55" s="37"/>
       <x:c r="C55" s="37"/>
-      <x:c r="D55" s="42"/>
+      <x:c r="D55" s="43"/>
       <x:c r="E55" s="37"/>
       <x:c r="F55" s="37"/>
       <x:c r="G55" s="38"/>
@@ -21112,7 +21335,7 @@
       <x:c r="A56" s="37"/>
       <x:c r="B56" s="37"/>
       <x:c r="C56" s="37"/>
-      <x:c r="D56" s="42"/>
+      <x:c r="D56" s="43"/>
       <x:c r="E56" s="37"/>
       <x:c r="F56" s="37"/>
       <x:c r="G56" s="38"/>
@@ -21123,7 +21346,7 @@
       <x:c r="A57" s="37"/>
       <x:c r="B57" s="37"/>
       <x:c r="C57" s="37"/>
-      <x:c r="D57" s="42"/>
+      <x:c r="D57" s="43"/>
       <x:c r="E57" s="37"/>
       <x:c r="F57" s="37"/>
       <x:c r="G57" s="38"/>
@@ -21134,7 +21357,7 @@
       <x:c r="A58" s="37"/>
       <x:c r="B58" s="37"/>
       <x:c r="C58" s="37"/>
-      <x:c r="D58" s="42"/>
+      <x:c r="D58" s="43"/>
       <x:c r="E58" s="37"/>
       <x:c r="F58" s="37"/>
       <x:c r="G58" s="38"/>
@@ -21145,7 +21368,7 @@
       <x:c r="A59" s="37"/>
       <x:c r="B59" s="37"/>
       <x:c r="C59" s="37"/>
-      <x:c r="D59" s="42"/>
+      <x:c r="D59" s="43"/>
       <x:c r="E59" s="37"/>
       <x:c r="F59" s="37"/>
       <x:c r="G59" s="38"/>
@@ -21156,7 +21379,7 @@
       <x:c r="A60" s="37"/>
       <x:c r="B60" s="37"/>
       <x:c r="C60" s="37"/>
-      <x:c r="D60" s="42"/>
+      <x:c r="D60" s="43"/>
       <x:c r="E60" s="37"/>
       <x:c r="F60" s="37"/>
       <x:c r="G60" s="38"/>
@@ -21167,7 +21390,7 @@
       <x:c r="A61" s="37"/>
       <x:c r="B61" s="37"/>
       <x:c r="C61" s="37"/>
-      <x:c r="D61" s="42"/>
+      <x:c r="D61" s="43"/>
       <x:c r="E61" s="37"/>
       <x:c r="F61" s="37"/>
       <x:c r="G61" s="38"/>
@@ -21178,7 +21401,7 @@
       <x:c r="A62" s="37"/>
       <x:c r="B62" s="37"/>
       <x:c r="C62" s="37"/>
-      <x:c r="D62" s="42"/>
+      <x:c r="D62" s="43"/>
       <x:c r="E62" s="37"/>
       <x:c r="F62" s="37"/>
       <x:c r="G62" s="38"/>
@@ -21189,7 +21412,7 @@
       <x:c r="A63" s="37"/>
       <x:c r="B63" s="37"/>
       <x:c r="C63" s="37"/>
-      <x:c r="D63" s="42"/>
+      <x:c r="D63" s="43"/>
       <x:c r="E63" s="37"/>
       <x:c r="F63" s="37"/>
       <x:c r="G63" s="38"/>
@@ -21200,7 +21423,7 @@
       <x:c r="A64" s="37"/>
       <x:c r="B64" s="37"/>
       <x:c r="C64" s="37"/>
-      <x:c r="D64" s="42"/>
+      <x:c r="D64" s="43"/>
       <x:c r="E64" s="37"/>
       <x:c r="F64" s="37"/>
       <x:c r="G64" s="38"/>
@@ -21211,7 +21434,7 @@
       <x:c r="A65" s="37"/>
       <x:c r="B65" s="37"/>
       <x:c r="C65" s="37"/>
-      <x:c r="D65" s="42"/>
+      <x:c r="D65" s="43"/>
       <x:c r="E65" s="37"/>
       <x:c r="F65" s="37"/>
       <x:c r="G65" s="38"/>
@@ -21222,7 +21445,7 @@
       <x:c r="A66" s="37"/>
       <x:c r="B66" s="37"/>
       <x:c r="C66" s="37"/>
-      <x:c r="D66" s="42"/>
+      <x:c r="D66" s="43"/>
       <x:c r="E66" s="37"/>
       <x:c r="F66" s="37"/>
       <x:c r="G66" s="38"/>
@@ -21233,7 +21456,7 @@
       <x:c r="A67" s="37"/>
       <x:c r="B67" s="37"/>
       <x:c r="C67" s="37"/>
-      <x:c r="D67" s="42"/>
+      <x:c r="D67" s="43"/>
       <x:c r="E67" s="37"/>
       <x:c r="F67" s="37"/>
       <x:c r="G67" s="38"/>
@@ -21244,7 +21467,7 @@
       <x:c r="A68" s="37"/>
       <x:c r="B68" s="37"/>
       <x:c r="C68" s="37"/>
-      <x:c r="D68" s="42"/>
+      <x:c r="D68" s="43"/>
       <x:c r="E68" s="37"/>
       <x:c r="F68" s="37"/>
       <x:c r="G68" s="38"/>
@@ -21255,7 +21478,7 @@
       <x:c r="A69" s="37"/>
       <x:c r="B69" s="37"/>
       <x:c r="C69" s="37"/>
-      <x:c r="D69" s="42"/>
+      <x:c r="D69" s="43"/>
       <x:c r="E69" s="37"/>
       <x:c r="F69" s="37"/>
       <x:c r="G69" s="38"/>
@@ -21266,7 +21489,7 @@
       <x:c r="A70" s="37"/>
       <x:c r="B70" s="37"/>
       <x:c r="C70" s="37"/>
-      <x:c r="D70" s="42"/>
+      <x:c r="D70" s="43"/>
       <x:c r="E70" s="37"/>
       <x:c r="F70" s="37"/>
       <x:c r="G70" s="38"/>
@@ -21277,7 +21500,7 @@
       <x:c r="A71" s="37"/>
       <x:c r="B71" s="37"/>
       <x:c r="C71" s="37"/>
-      <x:c r="D71" s="42"/>
+      <x:c r="D71" s="43"/>
       <x:c r="E71" s="37"/>
       <x:c r="F71" s="37"/>
       <x:c r="G71" s="38"/>
@@ -21288,7 +21511,7 @@
       <x:c r="A72" s="37"/>
       <x:c r="B72" s="37"/>
       <x:c r="C72" s="37"/>
-      <x:c r="D72" s="42"/>
+      <x:c r="D72" s="43"/>
       <x:c r="E72" s="37"/>
       <x:c r="F72" s="37"/>
       <x:c r="G72" s="38"/>
@@ -21299,7 +21522,7 @@
       <x:c r="A73" s="37"/>
       <x:c r="B73" s="37"/>
       <x:c r="C73" s="37"/>
-      <x:c r="D73" s="42"/>
+      <x:c r="D73" s="43"/>
       <x:c r="E73" s="37"/>
       <x:c r="F73" s="37"/>
       <x:c r="G73" s="38"/>
@@ -21310,7 +21533,7 @@
       <x:c r="A74" s="37"/>
       <x:c r="B74" s="37"/>
       <x:c r="C74" s="37"/>
-      <x:c r="D74" s="42"/>
+      <x:c r="D74" s="43"/>
       <x:c r="E74" s="37"/>
       <x:c r="F74" s="37"/>
       <x:c r="G74" s="38"/>
@@ -21321,7 +21544,7 @@
       <x:c r="A75" s="37"/>
       <x:c r="B75" s="37"/>
       <x:c r="C75" s="37"/>
-      <x:c r="D75" s="42"/>
+      <x:c r="D75" s="43"/>
       <x:c r="E75" s="37"/>
       <x:c r="F75" s="37"/>
       <x:c r="G75" s="38"/>
@@ -21332,7 +21555,7 @@
       <x:c r="A76" s="37"/>
       <x:c r="B76" s="37"/>
       <x:c r="C76" s="37"/>
-      <x:c r="D76" s="42"/>
+      <x:c r="D76" s="43"/>
       <x:c r="E76" s="37"/>
       <x:c r="F76" s="37"/>
       <x:c r="G76" s="38"/>
@@ -21343,7 +21566,7 @@
       <x:c r="A77" s="37"/>
       <x:c r="B77" s="37"/>
       <x:c r="C77" s="37"/>
-      <x:c r="D77" s="42"/>
+      <x:c r="D77" s="43"/>
       <x:c r="E77" s="37"/>
       <x:c r="F77" s="37"/>
       <x:c r="G77" s="38"/>
@@ -21354,7 +21577,7 @@
       <x:c r="A78" s="37"/>
       <x:c r="B78" s="37"/>
       <x:c r="C78" s="37"/>
-      <x:c r="D78" s="42"/>
+      <x:c r="D78" s="43"/>
       <x:c r="E78" s="37"/>
       <x:c r="F78" s="37"/>
       <x:c r="G78" s="38"/>
@@ -21365,7 +21588,7 @@
       <x:c r="A79" s="37"/>
       <x:c r="B79" s="37"/>
       <x:c r="C79" s="37"/>
-      <x:c r="D79" s="42"/>
+      <x:c r="D79" s="43"/>
       <x:c r="E79" s="37"/>
       <x:c r="F79" s="37"/>
       <x:c r="G79" s="38"/>
@@ -21376,7 +21599,7 @@
       <x:c r="A80" s="37"/>
       <x:c r="B80" s="37"/>
       <x:c r="C80" s="37"/>
-      <x:c r="D80" s="42"/>
+      <x:c r="D80" s="43"/>
       <x:c r="E80" s="37"/>
       <x:c r="F80" s="37"/>
       <x:c r="G80" s="38"/>
@@ -21387,7 +21610,7 @@
       <x:c r="A81" s="37"/>
       <x:c r="B81" s="37"/>
       <x:c r="C81" s="37"/>
-      <x:c r="D81" s="42"/>
+      <x:c r="D81" s="43"/>
       <x:c r="E81" s="37"/>
       <x:c r="F81" s="37"/>
       <x:c r="G81" s="38"/>
@@ -21398,7 +21621,7 @@
       <x:c r="A82" s="37"/>
       <x:c r="B82" s="37"/>
       <x:c r="C82" s="37"/>
-      <x:c r="D82" s="42"/>
+      <x:c r="D82" s="43"/>
       <x:c r="E82" s="37"/>
       <x:c r="F82" s="37"/>
       <x:c r="G82" s="38"/>
@@ -21409,7 +21632,7 @@
       <x:c r="A83" s="37"/>
       <x:c r="B83" s="37"/>
       <x:c r="C83" s="37"/>
-      <x:c r="D83" s="42"/>
+      <x:c r="D83" s="43"/>
       <x:c r="E83" s="37"/>
       <x:c r="F83" s="37"/>
       <x:c r="G83" s="38"/>
@@ -21420,7 +21643,7 @@
       <x:c r="A84" s="37"/>
       <x:c r="B84" s="37"/>
       <x:c r="C84" s="37"/>
-      <x:c r="D84" s="42"/>
+      <x:c r="D84" s="43"/>
       <x:c r="E84" s="37"/>
       <x:c r="F84" s="37"/>
       <x:c r="G84" s="38"/>
@@ -21431,7 +21654,7 @@
       <x:c r="A85" s="37"/>
       <x:c r="B85" s="37"/>
       <x:c r="C85" s="37"/>
-      <x:c r="D85" s="42"/>
+      <x:c r="D85" s="43"/>
       <x:c r="E85" s="37"/>
       <x:c r="F85" s="37"/>
       <x:c r="G85" s="38"/>
@@ -21442,7 +21665,7 @@
       <x:c r="A86" s="37"/>
       <x:c r="B86" s="37"/>
       <x:c r="C86" s="37"/>
-      <x:c r="D86" s="42"/>
+      <x:c r="D86" s="43"/>
       <x:c r="E86" s="37"/>
       <x:c r="F86" s="37"/>
       <x:c r="G86" s="38"/>
@@ -21453,7 +21676,7 @@
       <x:c r="A87" s="37"/>
       <x:c r="B87" s="37"/>
       <x:c r="C87" s="37"/>
-      <x:c r="D87" s="42"/>
+      <x:c r="D87" s="43"/>
       <x:c r="E87" s="37"/>
       <x:c r="F87" s="37"/>
       <x:c r="G87" s="38"/>
@@ -21464,7 +21687,7 @@
       <x:c r="A88" s="37"/>
       <x:c r="B88" s="37"/>
       <x:c r="C88" s="37"/>
-      <x:c r="D88" s="42"/>
+      <x:c r="D88" s="43"/>
       <x:c r="E88" s="37"/>
       <x:c r="F88" s="37"/>
       <x:c r="G88" s="38"/>
@@ -21475,7 +21698,7 @@
       <x:c r="A89" s="37"/>
       <x:c r="B89" s="37"/>
       <x:c r="C89" s="37"/>
-      <x:c r="D89" s="42"/>
+      <x:c r="D89" s="43"/>
       <x:c r="E89" s="37"/>
       <x:c r="F89" s="37"/>
       <x:c r="G89" s="38"/>
@@ -21486,7 +21709,7 @@
       <x:c r="A90" s="37"/>
       <x:c r="B90" s="37"/>
       <x:c r="C90" s="37"/>
-      <x:c r="D90" s="42"/>
+      <x:c r="D90" s="43"/>
       <x:c r="E90" s="37"/>
       <x:c r="F90" s="37"/>
       <x:c r="G90" s="38"/>
@@ -21497,7 +21720,7 @@
       <x:c r="A91" s="37"/>
       <x:c r="B91" s="37"/>
       <x:c r="C91" s="37"/>
-      <x:c r="D91" s="42"/>
+      <x:c r="D91" s="43"/>
       <x:c r="E91" s="37"/>
       <x:c r="F91" s="37"/>
       <x:c r="G91" s="38"/>
@@ -21508,7 +21731,7 @@
       <x:c r="A92" s="37"/>
       <x:c r="B92" s="37"/>
       <x:c r="C92" s="37"/>
-      <x:c r="D92" s="42"/>
+      <x:c r="D92" s="43"/>
       <x:c r="E92" s="37"/>
       <x:c r="F92" s="37"/>
       <x:c r="G92" s="38"/>
@@ -21519,7 +21742,7 @@
       <x:c r="A93" s="37"/>
       <x:c r="B93" s="37"/>
       <x:c r="C93" s="37"/>
-      <x:c r="D93" s="42"/>
+      <x:c r="D93" s="43"/>
       <x:c r="E93" s="37"/>
       <x:c r="F93" s="37"/>
       <x:c r="G93" s="38"/>
@@ -21530,7 +21753,7 @@
       <x:c r="A94" s="37"/>
       <x:c r="B94" s="37"/>
       <x:c r="C94" s="37"/>
-      <x:c r="D94" s="42"/>
+      <x:c r="D94" s="43"/>
       <x:c r="E94" s="37"/>
       <x:c r="F94" s="37"/>
       <x:c r="G94" s="38"/>
@@ -21541,7 +21764,7 @@
       <x:c r="A95" s="37"/>
       <x:c r="B95" s="37"/>
       <x:c r="C95" s="37"/>
-      <x:c r="D95" s="42"/>
+      <x:c r="D95" s="43"/>
       <x:c r="E95" s="37"/>
       <x:c r="F95" s="37"/>
       <x:c r="G95" s="38"/>
@@ -21552,7 +21775,7 @@
       <x:c r="A96" s="37"/>
       <x:c r="B96" s="37"/>
       <x:c r="C96" s="37"/>
-      <x:c r="D96" s="42"/>
+      <x:c r="D96" s="43"/>
       <x:c r="E96" s="37"/>
       <x:c r="F96" s="37"/>
       <x:c r="G96" s="38"/>
@@ -21563,7 +21786,7 @@
       <x:c r="A97" s="37"/>
       <x:c r="B97" s="37"/>
       <x:c r="C97" s="37"/>
-      <x:c r="D97" s="42"/>
+      <x:c r="D97" s="43"/>
       <x:c r="E97" s="37"/>
       <x:c r="F97" s="37"/>
       <x:c r="G97" s="38"/>
@@ -21574,7 +21797,7 @@
       <x:c r="A98" s="37"/>
       <x:c r="B98" s="37"/>
       <x:c r="C98" s="37"/>
-      <x:c r="D98" s="42"/>
+      <x:c r="D98" s="43"/>
       <x:c r="E98" s="37"/>
       <x:c r="F98" s="37"/>
       <x:c r="G98" s="38"/>
@@ -21585,7 +21808,7 @@
       <x:c r="A99" s="37"/>
       <x:c r="B99" s="37"/>
       <x:c r="C99" s="37"/>
-      <x:c r="D99" s="42"/>
+      <x:c r="D99" s="43"/>
       <x:c r="E99" s="37"/>
       <x:c r="F99" s="37"/>
       <x:c r="G99" s="38"/>
@@ -21596,7 +21819,7 @@
       <x:c r="A100" s="37"/>
       <x:c r="B100" s="37"/>
       <x:c r="C100" s="37"/>
-      <x:c r="D100" s="42"/>
+      <x:c r="D100" s="43"/>
       <x:c r="E100" s="37"/>
       <x:c r="F100" s="37"/>
       <x:c r="G100" s="38"/>
@@ -21607,7 +21830,7 @@
       <x:c r="A101" s="37"/>
       <x:c r="B101" s="37"/>
       <x:c r="C101" s="37"/>
-      <x:c r="D101" s="42"/>
+      <x:c r="D101" s="43"/>
       <x:c r="E101" s="37"/>
       <x:c r="F101" s="37"/>
       <x:c r="G101" s="38"/>
@@ -21618,7 +21841,7 @@
       <x:c r="A102" s="37"/>
       <x:c r="B102" s="37"/>
       <x:c r="C102" s="37"/>
-      <x:c r="D102" s="42"/>
+      <x:c r="D102" s="43"/>
       <x:c r="E102" s="37"/>
       <x:c r="F102" s="37"/>
       <x:c r="G102" s="38"/>
@@ -21629,7 +21852,7 @@
       <x:c r="A103" s="37"/>
       <x:c r="B103" s="37"/>
       <x:c r="C103" s="37"/>
-      <x:c r="D103" s="42"/>
+      <x:c r="D103" s="43"/>
       <x:c r="E103" s="37"/>
       <x:c r="F103" s="37"/>
       <x:c r="G103" s="38"/>
@@ -21640,7 +21863,7 @@
       <x:c r="A104" s="37"/>
       <x:c r="B104" s="37"/>
       <x:c r="C104" s="37"/>
-      <x:c r="D104" s="42"/>
+      <x:c r="D104" s="43"/>
       <x:c r="E104" s="37"/>
       <x:c r="F104" s="37"/>
       <x:c r="G104" s="38"/>
@@ -21660,7 +21883,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8ae0fb485b743a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf63b56ce6fa742b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>